--- a/SantanderCS/results/ResultListByTestModel_Final.xlsx
+++ b/SantanderCS/results/ResultListByTestModel_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\big20\git\big20-ML-project2-team3\SantanderCS\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362395B5-921D-4743-9748-F3B47DC40E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6800FD6F-82B2-4F01-9298-AC5B22893C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="825" yWindow="270" windowWidth="27270" windowHeight="14190" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
+    <workbookView xWindow="270" yWindow="345" windowWidth="29100" windowHeight="14190" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,8 +33,365 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>이경주</author>
+    <author>TJ</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{8D5D369D-8366-4231-A9A8-94403A0938A7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이경주</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+rf_clf = RandomForestClassifier(
+    random_state      = 23,
+    n_estimators      = 390,
+    max_depth         = 25,
+    class_weight      = {0:1, 1:2},
+    min_samples_leaf  = 1,
+    min_samples_split = 7,
+    n_jobs            = -1
+)
+xgb_clf = XGBClassifier(
+    random_state      = 23,    
+    n_estimators      = 320,
+    colsample_bytree  = 0.88,
+    gamma             = 0.058, 
+    learning_rate     = 0.13,
+    max_depth         = 6,
+    scale_pos_weight  = 10,
+    min_child_weight  = 2, 
+    subsample         = 0.85,    
+    eval_metric       ='auc',
+    use_label_encoder = False,
+    n_jobs            = -1,
+)
+lgbm_clf = LGBMClassifier(
+    random_state     = 23,
+    n_estimators     = 300,
+    colsample_bytree = 0.73,
+    # max_depth      = -1,
+    learning_rate    = 0.03,
+    num_leaves       = 42,
+    reg_alpha        = 0.61,
+    reg_lambda       = 0.13,
+    subsample        = 0.97,
+    class_weight     = {0:1, 1:10},
+    n_jobs           = -1,
+)
+# 2. Meta model </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">정의
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">meta_model = LogisticRegression(
+    random_state = 23,
+    max_iter     = 1000,
+    class_weight="balanced"
+)
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{324DC687-CECD-4A7B-A224-7F34A5EAE2E7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>이경주</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+rf_clf = RandomForestClassifier(
+    random_state      = 23,
+    n_estimators      = 390,
+    max_depth         = 25,
+    class_weight      = {0:1, 1:2},
+    min_samples_leaf  = 1,
+    min_samples_split = 7,
+    n_jobs            = -1
+)
+xgb_clf = XGBClassifier(
+    random_state      = 23,    
+    n_estimators      = 320,
+    colsample_bytree  = 0.88,
+    gamma             = 0.058, 
+    learning_rate     = 0.13,
+    max_depth         = 6,
+    scale_pos_weight  = 10,
+    min_child_weight  = 2, 
+    subsample         = 0.85,    
+    eval_metric       ='auc',
+    use_label_encoder = False,
+    n_jobs            = -1,
+)
+lgbm_clf = LGBMClassifier(
+    random_state     = 23,
+    n_estimators     = 300,
+    colsample_bytree = 0.73,
+    # max_depth      = -1,
+    learning_rate    = 0.03,
+    num_leaves       = 42,
+    reg_alpha        = 0.61,
+    reg_lambda       = 0.13,
+    subsample        = 0.97,
+    class_weight     = {0:1, 1:10},
+    n_jobs           = -1,
+)
+# 2. Meta model </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">정의
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">meta_model = LogisticRegression(
+    random_state = 23,
+    max_iter     = 1000,
+    class_weight="balanced"
+)
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F37" authorId="1" shapeId="0" xr:uid="{579C2269-480E-4912-B0CB-072783F430D8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>rf_clf = RandomForestClassifier(
+    random_state      = 23,
+    n_estimators      = 390,
+    max_depth         = 25,
+    class_weight      = {0:1, 1:2},
+    min_samples_leaf  = 1,
+    min_samples_split = 7,
+    n_jobs            = -1
+)
+xgb_clf = XGBClassifier(
+    random_state      = 23,    
+    n_estimators      = 320,
+    colsample_bytree  = 0.88,
+    gamma             = 0.058, 
+    learning_rate     = 0.13,
+    max_depth         = 6,
+    scale_pos_weight  = 10,
+    min_child_weight  = 2, 
+    subsample         = 0.85,    
+    eval_metric       ='auc',
+    use_label_encoder = False,
+    n_jobs            = -1,
+)
+lgbm_clf = LGBMClassifier(
+    random_state     = 23,
+    n_estimators     = 300,
+    colsample_bytree = 0.73,
+    # max_depth      = -1,
+    learning_rate    = 0.03,
+    num_leaves       = 42,
+    reg_alpha        = 0.61,
+    reg_lambda       = 0.13,
+    subsample        = 0.97,
+    class_weight     = {0:1, 1:10},
+    n_jobs           = -1,
+)
+meta_model = LogisticRegression(
+    random_state = 23,
+    max_iter     = 1000,
+    C            = 0.029,
+    penalty      = 'l2',
+    solver       = 'lbfgs',
+    class_weight ="balanced"
+    # **lr_best_param
+)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F38" authorId="1" shapeId="0" xr:uid="{C8D3EC9A-2153-4259-AFA4-4BD04BD03312}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">rf_clf = RandomForestClassifier(
+    random_state      = 23,
+    n_estimators      = 390,
+    max_depth         = 25,
+    class_weight      = {0:1, 1:2},
+    min_samples_leaf  = 1,
+    min_samples_split = 7,
+    n_jobs            = -1
+)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+xgb_clf = XGBClassifier(
+    random_state      = 23,    
+    n_estimators      = 320,
+    colsample_bytree  = 0.88,
+    gamma             = 0.058, 
+    learning_rate     = 0.13,
+    max_depth         = 6,
+    scale_pos_weight  = 10,
+    min_child_weight  = 2, 
+    subsample         = 0.85,    
+    eval_metric       ='auc',
+    use_label_encoder = False,
+    n_jobs            = -1,
+)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">np.float64(0.973776538266153)}
+lgbm_clf = LGBMClassifier(
+    random_state = 0,
+    n_estimators = 400,
+    num_leaves = 36,
+    learning_rate = 0.03,
+    subsample = 0.9,
+    colsample_bytree = 0.75,
+    reg_alpha = 0.6,
+    reg_lambda = 0.2,
+    class_weight = {0:1, 1:10},
+    n_jobs = -1
+)
+# 2. Meta model </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">정의
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>meta_model = LogisticRegression(
+    random_state = 23,
+    max_iter     = 1000,
+    class_weight="balanced"
+)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="156">
   <si>
     <t>NO</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -65,10 +422,6 @@
   </si>
   <si>
     <t>담당자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>No of Features</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -90,21 +443,945 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Var3 / Not Scaled</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t> 0.016287</t>
-  </si>
-  <si>
-    <t> 0.008306</t>
-  </si>
-  <si>
     <t>RandomForest_99per_corrTh95_Scaled_ne390_maxDepth25_classWeight12_msl1_mss7.pkl</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>lkj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>split rate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X_train.shape</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stacking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(76020, 96)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Var3 / Scaled /
+log1p(71개 피쳐)
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stacking_model = StackingClassifier(
+    estimators= [('rf', rf_clf), ('xgb', xgb_clf), ('lgbm', lgbm_clf)],
+    final_estimator= meta_model,
+    cv= StratifiedKFold(n_splits=5, shuffle=True, random_state=42),
+    n_jobs          = -1
+)
+* 메모 참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StackingModel_log1p_RF+LGBM-HP+XGB+LR_20251124
+RandomForest 기여도(계수): 1.8603
+XGBoost 기여도(계수): -0.6759
+LightGBM 기여도(계수): 4.8092 
+Stacking 모델 ROC-AUC: 
+Stacking 모델 F1-Score: 
+Stacking 모델 Recall:   0.8853</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Var3 / Not Scaled 
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StackingModel_RF+LGBM+XGB_20251123.pkl
+RandomForest 기여도(계수): 2.0190
+XGBoost 기여도(계수): -2.1154
+LightGBM 기여도(계수): 6.4119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / Not Scaled /
+ZCR &gt; 99% +
+Corr() &gt; 95% 컬럼 삭제/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t> 0.0163</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / Not Scaled 
+/ Log1p(71개 Features)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomForest(99per95corrBestHO)_Log1p_20251124</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(76020, 86)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / ZCR &gt; 99% +
+Corr() &gt; 95% 컬럼 삭제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  random_state = 0,
+  n_estimators = 300,
+  max_depth    = 20, 
+  class_weight = {0:1, 1:2}, # 클래스별 가중치
+  n_jobs       = -1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomForest_95per_HP_ne300_maxDepth20_classWeight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  random_state = 0,
+  n_estimators = 100,
+  max_depth    = 10, 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  class_weight = {0:1, 1:2},</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> # 클래스별 가중치
+  n_jobs       = -1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  random_state = 0,
+  n_estimators = 100,
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  max_depth    = 10,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  n_jobs       = -1 </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomForest_95per_HP_maxDepth10.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(18048, 94)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / Scaled /
+ZCR &gt; 99% +
+Corr() &gt; 95% 컬럼 삭제/
+UnderSampling_Ratio=5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  random_state = 0,
+  n_estimators = 390,
+  max_depth    = 25, 
+  class_weight = {0:1, 1:2}, # 클래스별 가중치
+  min_samples_leaf  = 1, 
+  min_samples_split = 7,
+  n_jobs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomForest_99per_corrTh95UnderSampling10_BestOpt.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / Scaled /
+ZCR &gt; 99% +
+Corr() &gt; 95% 컬럼 삭제/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomForest_99per_corrTh95_NoTScaled_ne390_maxDepth25_classWeight110_msl1_mss7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(33088, 94)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / Scaled /
+ZCR &gt; 99% +
+Corr() &gt; 95% 컬럼 삭제/
+UnderSampling_Ratio=10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomForest_99per_corrTh95UnderSampling5_BestOpt.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(76020, 149)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Var3 / Scaled </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  random_state = 0,
+  n_estimators = 100,
+  max_depth    = 10, 
+  n_jobs       = -1 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomForest_99per_7v3HP_maxDepth10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ random_state = 0,
+  n_estimators = 100,
+  max_depth    = 8, 
+  n_jobs       = -1
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomForest_95per_basic.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(63168, 94)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / Scaled /
+ZCR &gt; 99% +
+Corr() &gt; 95% 컬럼 삭제/
+UnderSampling_Ratio=20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomForest_99per_corrTh95UnderSampling20_BestOpt.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Var3, 
+Zero_Count_Rate &gt; 99% 컬럼 삭제 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomForest_99per_basic7v3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 /Scaled + K-Fold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{  random_state = 0,
+  n_estimators = 390,
+  max_depth    = 25, 
+  class_weight = {0:1, 1:20}, # 클래스별 가중치
+  min_samples_leaf  = 1, 
+  min_samples_split = 7,
+  n_jobs            = -1 # 병렬처리 여부   }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> === Stratified K-Fold 평균 성능 ===
+AUC 평균: 0.8318
+F1 평균: 0.0218
+Recall 평균: 0.0113</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{  random_state = 0,
+  n_estimators = 390,
+  max_depth    = 25, 
+  class_weight = {0:1, 1:10}, # 클래스별 가중치
+  min_samples_leaf  = 1, 
+  min_samples_split = 7,
+  n_jobs            = -1 # 병렬처리 여부   }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> === Stratified K-Fold 평균 성능 ===
+ROC-AUC 평균: 0.8170
+PR-AUC 평균:  0.1608
+F1 평균:      0.2604
+Recall 평균:  0.3860</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / Scaled</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{  random_state = 0,
+    n_estimators=300,
+    max_depth=20,
+    class_weight={0:1, 1:2},  
+    n_jobs = -1  }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RF_100_est300_max20_class1vs2_thr.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{  random_state = 0,
+    n_estimators=300,
+    max_depth=10,
+    class_weight={0:1, 1:2},  
+    n_jobs = -1  }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RF_100_est300_max10_class1vs2_thr.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{  random_state = 0,
+    n_estimators=100,
+    max_depth=10,
+    n_jobs = -1  }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RF_100_est100_max10.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XGBoost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    n_estimators=300,
+    learning_rate=0.05,
+    max_depth=5,
+    subsample=0.8,
+    colsample_bytree=0.8,
+    eval_metric='logloss',
+    random_state=42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XGB_100_est300_lr0.05_max5.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    n_estimators=300,
+    learning_rate=0.05,
+    max_depth=5,
+    subsample=0.8,
+    colsample_bytree=0.8,
+    eval_metric='logloss',
+    random_state=42,
+    Best Threshold: 0.13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XGB_100_est300_lr0.05_max5_thr.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    n_estimators=300,
+    learning_rate=0.05,
+    max_depth=5,
+    subsample=0.8,
+    colsample_bytree=0.8,
+    eval_metric='logloss',
+    random_state=42
+    scale_pos_weight=3,
+    Best Threshold: 0.30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XGB_100_est300_lr0.05_max5_spw3_thr.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{   random_state      = 0,
+    n_estimators      = 100,
+    num_leaves        = 31,
+    min_child_samples = 10,  }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM_100_num31_min10.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{   random_state      = 0,
+    n_estimators      = 100,
+    num_leaves        = 31,
+    min_child_samples = 10,
+    Best Threshold: 0.15  }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM_100_num31_min10_thr.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(76020, 369)</t>
+  </si>
+  <si>
+    <t>(76020, 369)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / StandardScaler</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{  random_state = 0,
+  n_estimators = 1000,
+  learnnig_rate = 0.05, 
+  num_leaves = 15,
+  min_child_samples = 5}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t> 0.0194</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t> 0.0100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lgbm_ejm.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ejm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{colsample_bytree:0.7342,
+ learning_rate: 0.0275,
+ n_estimators: 660,
+ num_leaves: 42,
+ reg_alpha: 0.6128,
+reg_lambda: 0.1263,
+ subsample: 0.9738}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lgbm_HyperOpt_ejm.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LogisticRegression</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / StandardScaler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">penalty: l2
+    class_weight: None,
+    random_state: 0,
+  solver: lbfgs,
+multi_class: auto,
+verbose: Int = 0,
+n_jobs: None,
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lr_ejm.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ n_estimators=500,
+    max_depth=6,
+    learning_rate=0.05,
+    subsample=0.8,
+    colsample_bytree=0.8,
+    random_state=23 }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xgb_ejm.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{colsample_bytree: 0.8828,
+ gamma: 0.0584,
+ learning_rate: 0.1272,
+ max_depth: 6, 
+min_child_weight: 2, 
+n_estimators : 320,
+subsample: 0.8456}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xgb_HyperOpt_ejm.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> {max_depth: 25,
+ min_samples_leaf: 1,
+ min_samples_split: 7,
+ n_estimators: 390}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rf_HyperOpt_ejm.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stacking_model = StackingClassifier(
+    estimators      = [('rf', rf_clf), ('xgb', xgb_clf), ('lgbm', lgbm_clf)],
+    final_estimator = meta_model,
+    cv              = StratifiedKFold(n_splits=5, shuffle=True, random_state=42),
+    n_jobs          = -1
+)*메모참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StackingModel_log1p_RF+LGBM+XGB+LR_20251125-final.pkl
+RandomForest 기여도(계수): 1.8603
+XGBoost 기여도(계수): -0.6759
+LightGBM 기여도(계수): 4.8092
+Stacking 모델 ROC-AUC: 0.9300
+Stacking 모델 F1-Score: 0.2933
+Stacking 모델 Recall:   0.8853</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Var3 / Scaled /
+log변환X
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stacking_model = StackingClassifier(
+    estimators      = [('rf', rf_clf), ('xgb', xgb_clf), ('lgbm', lgbm_clf)],
+    final_estimator = meta_model,
+    cv              = StratifiedKFold(n_splits=5, shuffle=True, random_state=42),
+    n_jobs          = -1
+) *메모참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StackingModel_RF+LGBM+XGB_20251123.pkl
+RandomForest 기여도(계수): 2.3591
+XGBoost 기여도(계수): -2.1535
+LightGBM 기여도(계수): 6.2372
+Stacking 모델 ROC-AUC: 0.9115
+Stacking 모델 F1-Score: 0.2797
+Stacking 모델 Recall:   0.8557</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(
+  random_state      = 0,
+  n_estimators      = 100,
+  num_leaves        = 15,        # 가지 수
+  min_child_samples = 2
+)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lgbm_99per_basic.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(
+        random_state = 0,
+        n_estimators = 400,
+        num_leaves = 36,
+        learning_rate = 0.03,
+        subsample = 0.9,
+        colsample_bytree = 0.75,
+        reg_alpha = 0.6,
+        reg_lambda = 0.2,
+        class_weight = {0:1, 1:10},
+        n_jobs = -1
+    )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM_99per_Corr_weight110.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lgbm_99per_basic7vs3.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(76020, 99)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 /Scaled + FeatureAdd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(
+    random_state      = 0,
+    n_estimators      = 500,
+    num_leaves        = 32,         
+    min_child_samples = 18,             
+    class_weight      = {0:1, 1:5}, 
+    learning_rate     = 0.05, 
+    subsample         = 0.8, 
+    colsample_bytree  = 0.8, 
+    verbose           = -1 
+)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM_99per_FE_scaled_ne500_nl23_mcs18_classweight15_lr05_ss08.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(
+        random_state      = 0,
+        n_estimators      = 500,
+        num_leaves        = 32,   
+        min_child_samples = 18,         
+        class_weight      = {0:1, 1:5}, 
+        learning_rate     = 0.05,
+        subsample         = 0.8,
+        colsample_bytree  = 0.8, 
+        verbose           = -1 
+    )
+    </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM_99per_Corr_weight15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(
+        random_state      = 0,
+        n_estimators      = 300,
+        num_leaves        = 32,        # 가지 수
+        min_child_samples = 24,
+        class_weight = {0:1, 1:2},
+        verbose           = -1
+    )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM_99per_Corr_weight12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(
+    random_state = 0,
+    n_estimators = 400,
+    num_leaves = 36,
+    learning_rate = 0.03,
+    subsample = 0.9,
+    colsample_bytree = 0.75,
+    reg_alpha = 0.6,
+    reg_lambda = 0.2,
+    class_weight = {0:1, 1:10}
+)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM_99per_corrTh95_UnderSampling5_BestOpt.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\LightGBM_99per_corrTh95_UnderSampling10_BestOpt.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM_99per_corrTh95_UnderSampling20_BestOpt.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(
+            random_state = 0,
+            n_estimators = 400,
+            num_leaves = 36,
+            learning_rate = 0.03,
+            subsample = 0.9,
+            colsample_bytree = 0.75,
+            reg_alpha = 0.6,
+            reg_lambda = 0.2,
+            class_weight = {0:1, 1:20}
+        )   </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=== Stratified K-Fold 평균 성능 ===
+ROC-AUC 평균: 0.8125
+PR-AUC 평균:  0.1721
+F1 평균:      0.2414
+Recall 평균:  0.5934</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=== Stratified K-Fold 평균 성능 ===
+ROC-AUC 평균: 0.8177
+PR-AUC 평균:  0.1755
+F1 평균:      0.2674
+Recall 평균:  0.4927</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=== Stratified K-Fold 평균 성능 ===
+ROC-AUC 평균: 0.8217
+PR-AUC 평균:  0.1757
+F1 평균:      0.2615
+Recall 평균:  0.3364</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var3 / Scaled</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xgb = XGBClassifier(
+    n_estimators=500,
+    max_depth=6,
+    learning_rate=0.05,
+    subsample=0.8,
+    colsample_bytree=0.8,
+    random_state=23
+)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\XGBoost_95per_basic.pkl</t>
+  </si>
+  <si>
+    <t>Logistic Regression</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>log_reg = LogisticRegression(
+    max_iter=1000,        # 반복 횟수 충분히 크게
+    solver='lbfgs',       # 최적화 알고리즘
+    random_state=42,
+    n_jobs=-1
+)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\LogisticRegression_95per_basic.pkl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best Hyperparameters: {
+    'colsample_bytree': np.float64(0.7641), 
+    'learning_rate': np.float64(0.0172), 
+    'max_depth': np.float64(6.0), 
+    'n_estimators': np.float64(350.0), 
+    'subsample': np.float64(0.8353)
+}   </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\XGBoost_95per_hyperopt.pkl</t>
+  </si>
+  <si>
+    <t>Best Hyperparameters: {
+    'C': np.float64(1.0445023972192211), 
+    'penalty': np.int64(0)
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\LogisticRegression_95per_hyperopt.pkl</t>
+  </si>
+  <si>
+    <t>models\XGBoost_99per_basic.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\LogisticRegression_99per_basic.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Best Hyperparameters: {
+'colsample_bytree': np.float64(0.6189), 
+'gamma': np.float64(2.1975), 
+'learning_rate': np.float64(0.0145), 
+'max_depth': np.float64(7.0), 
+'min_child_weight': np.float64(6.0), 
+'n_estimators': np.float64(400.0), 
+'subsample': np.float64(0.8353)}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\XGBoost_99per_hyperopt.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Best Hyperparameters: {
+    'C': np.float64(0.02872898758249208), 
+    'class_weight': np.int64(1), 
+    'penalty': np.int64(0)
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\LogisticRegression_99per_hyperopt.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>95% / threshold 0.95</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99% / threshold 0.95</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var3 / Not Scaled</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xgb_clf = XGBClassifier(
+    colsample_bytree=0.6189,
+    gamma=2.1975,
+    learning_rate=0.0145,
+    max_depth=7,
+    min_child_weight=6,
+    n_estimators=400,
+    subsample=0.8353,
+    random_state=42,
+    use_label_encoder=False,
+    eval_metric='logloss'
+)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\XGBoost_99per_hyperopt_th_fe0.95.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>log_clf = LogisticRegression(
+    C=0.0287,
+    class_weight=None,   # class_weight=1은 None과 동일
+    penalty='l2',
+    solver='lbfgs',
+    max_iter=1000,
+    random_state=42
+)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\LogisticRegression_99per_hyperopt_th_fe0.95.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\XGBoost_99per_corrTh95_HyperOpt_Scaled.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\LogisticRegression_99per_corrTh95_HyperOpt_Scaled.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=== Stratified K-Fold 평균 성능 ===
+ROC-AUC 평균: 0.8412
+PR-AUC 평균:  0.1917
+F1 평균:      0.0053
+Recall 평균:  0.0027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=== Stratified K-Fold 평균 성능 ===
+ROC-AUC 평균: 0.6122
+PR-AUC 평균:  0.0581
+F1 평균:      0.0000
+Recall 평균:  0.0000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Best Hyperparameters: {
+    'colsample_bytree': np.float64(0.7010), 
+    'gamma': np.float64(8.0444), 
+    'learning_rate': np.float64(0.0102), 
+    'max_depth': np.float64(5.0), 
+    'min_child_weight': np.float64(8.0), 
+    'n_estimators': np.float64(450.0), 
+    'reg_alpha': np.float64(0.0002), 
+    'reg_lambda': np.float64(2.3460), 
+    'scale_pos_weight': np.float64(5.0), 
+    'subsample': np.float64(0.6896)}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\XGBoost_99per_hyperoptCorr_spw_alpha_lambda.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t># Best Hyperparameters: {
+    # 'C': np.float64(0.0408), 
+    # 'class_weight': np.int64(1), 
+    # 'max_iter': np.float64(500.0), 
+    # 'penalty': np.int64(0), 
+    # 'solver': np.int64(0)}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\LogisticRegression_99perCorr95_L2_liblinear_maxiter500,2000.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\XGBoost_99per_corrTh95_UnderSampling5_BestOpt.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\LogisticRegression_99per_corrTh95_UnderSampling5_BestOpt.pkl</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -112,7 +1389,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,8 +1412,90 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="D2Coding"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -155,8 +1514,25 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -319,13 +1695,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -371,9 +1759,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -386,8 +1771,168 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="보통" xfId="1" builtinId="28"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -699,3336 +2244,5035 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA66AA66-968F-43FC-BD0D-4CB9ADC09730}">
-  <dimension ref="A1:J297"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA66AA66-968F-43FC-BD0D-4CB9ADC09730}">
+  <dimension ref="A1:K297"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="53.75" style="2" customWidth="1"/>
-    <col min="6" max="7" width="9.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="83.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="3" max="3" width="18.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53.75" style="2" customWidth="1"/>
+    <col min="7" max="8" width="9.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="H1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="I1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="J1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="132" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="13">
-        <f>370-149-53</f>
-        <v>168</v>
-      </c>
-      <c r="D2" s="13" t="s">
+      <c r="B2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="22">
+        <v>0.93</v>
+      </c>
+      <c r="H2" s="22">
+        <v>0.29330000000000001</v>
+      </c>
+      <c r="I2" s="23">
+        <v>0.88529999999999998</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.84216899999999995</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:11" ht="132" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="7"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="7"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="7"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="7"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="7"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="7"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="7"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="7"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="7"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="7"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="7"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="7"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="7"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="7"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="7"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="7"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="7"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="7"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="7"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="7"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="4"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="7"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="7"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="7"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="4"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="7"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="4"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="7"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="4"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="7"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="7"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="7"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="7"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="4"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="7"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="4"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="7"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="4"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="7"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="7"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="4"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="7"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="4"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="7"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="4"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="7"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="4"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="7"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="4"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="7"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="4"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="7"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="4"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="6"/>
+      <c r="B3" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="20">
+        <v>0.90310000000000001</v>
+      </c>
+      <c r="H3" s="20">
+        <v>0.2722</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0.83840000000000003</v>
+      </c>
+      <c r="J3" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="36"/>
+    </row>
+    <row r="4" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="25">
+        <v>0.84219999999999995</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="20">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="36"/>
+    </row>
+    <row r="5" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="20">
+        <v>0.84060000000000001</v>
+      </c>
+      <c r="H5" s="20">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="I5" s="20">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="36"/>
+    </row>
+    <row r="6" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="12">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.83960000000000001</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="I6" s="6">
+        <v>6.6E-3</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="36"/>
+    </row>
+    <row r="7" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.83640000000000003</v>
+      </c>
+      <c r="H7" s="6">
+        <v>6.6E-3</v>
+      </c>
+      <c r="I7" s="6">
+        <v>3.3E-3</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="36"/>
+    </row>
+    <row r="8" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A8" s="12">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.83169999999999999</v>
+      </c>
+      <c r="H8" s="6">
+        <v>3.3E-3</v>
+      </c>
+      <c r="I8" s="6">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="36"/>
+    </row>
+    <row r="9" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.8306</v>
+      </c>
+      <c r="H9" s="23">
+        <v>0.49070000000000003</v>
+      </c>
+      <c r="I9" s="23">
+        <v>0.46010000000000001</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="36"/>
+    </row>
+    <row r="10" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="12">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="30">
+        <v>0.82630000000000003</v>
+      </c>
+      <c r="H10" s="23">
+        <v>0.26529999999999998</v>
+      </c>
+      <c r="I10" s="23">
+        <v>0.39529999999999998</v>
+      </c>
+      <c r="J10" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="36"/>
+    </row>
+    <row r="11" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.82550000000000001</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.34689999999999999</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0.29070000000000001</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11" s="36"/>
+    </row>
+    <row r="12" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A12" s="12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="32">
+        <v>0.3</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0.82340000000000002</v>
+      </c>
+      <c r="H12" s="6">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="I12" s="6">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" s="36"/>
+    </row>
+    <row r="13" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0.82310000000000005</v>
+      </c>
+      <c r="H13" s="6">
+        <v>3.3E-3</v>
+      </c>
+      <c r="I13" s="6">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13" s="36"/>
+    </row>
+    <row r="14" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="12">
+        <v>13</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="H14" s="6">
+        <v>4.6699999999999998E-2</v>
+      </c>
+      <c r="I14" s="6">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K14" s="36"/>
+    </row>
+    <row r="15" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0.81840000000000002</v>
+      </c>
+      <c r="H15" s="6">
+        <v>3.3E-3</v>
+      </c>
+      <c r="I15" s="6">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="J15" s="7"/>
+      <c r="K15" s="36"/>
+    </row>
+    <row r="16" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="12">
+        <v>15</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="33">
+        <v>0.3</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="6">
+        <v>0.81589999999999996</v>
+      </c>
+      <c r="H16" s="6">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="I16" s="6">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" s="36"/>
+    </row>
+    <row r="17" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="K17" s="36"/>
+    </row>
+    <row r="18" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="12">
+        <v>17</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="K18" s="36"/>
+    </row>
+    <row r="19" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="38">
+        <v>0.83560000000000001</v>
+      </c>
+      <c r="H19" s="13">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="I19" s="13">
+        <v>0.45019999999999999</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="12">
+        <v>19</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="38">
+        <v>0.82150000000000001</v>
+      </c>
+      <c r="H20" s="13">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="I20" s="13">
+        <v>0.47839999999999999</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="38">
+        <v>0.81240000000000001</v>
+      </c>
+      <c r="H21" s="13">
+        <v>0</v>
+      </c>
+      <c r="I21" s="13">
+        <v>0</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="12">
+        <v>21</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" s="38">
+        <v>0.85089999999999999</v>
+      </c>
+      <c r="H22" s="13">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="I22" s="13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="132" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="38">
+        <v>0.85089999999999999</v>
+      </c>
+      <c r="H23" s="13">
+        <v>0.2974</v>
+      </c>
+      <c r="I23" s="13">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="12">
+        <v>23</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="38">
+        <v>0.85050000000000003</v>
+      </c>
+      <c r="H24" s="13">
+        <v>0.30099999999999999</v>
+      </c>
+      <c r="I24" s="13">
+        <v>0.53159999999999996</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G25" s="38">
+        <v>0.84370000000000001</v>
+      </c>
+      <c r="H25" s="13">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="I25" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="12">
+        <v>25</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" s="38">
+        <v>0.84370000000000001</v>
+      </c>
+      <c r="H26" s="13">
+        <v>0.28870000000000001</v>
+      </c>
+      <c r="I26" s="13">
+        <v>0.45179999999999998</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G27" s="38">
+        <v>0.84370000000000001</v>
+      </c>
+      <c r="H27" s="13">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="I27" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A28" s="12">
+        <v>27</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" s="38">
+        <v>0.84370000000000001</v>
+      </c>
+      <c r="H28" s="13">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="I28" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G29" s="38">
+        <v>0.84370000000000001</v>
+      </c>
+      <c r="H29" s="13">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="I29" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A30" s="12">
+        <v>29</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G30" s="38">
+        <v>0.84370000000000001</v>
+      </c>
+      <c r="H30" s="13">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="I30" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="G31" s="41">
+        <v>0.84</v>
+      </c>
+      <c r="H31" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="I31" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="J31" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="K31" s="43" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="12">
+        <v>31</v>
+      </c>
+      <c r="B32" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E32" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="F32" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="G32" s="48">
+        <v>0.84379999999999999</v>
+      </c>
+      <c r="H32" s="44">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="I32" s="44">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J32" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="K32" s="47"/>
+    </row>
+    <row r="33" spans="1:11" ht="132" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E33" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="F33" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" s="44">
+        <v>0.80510000000000004</v>
+      </c>
+      <c r="H33" s="44">
+        <v>1.29E-2</v>
+      </c>
+      <c r="I33" s="44">
+        <v>6.6E-3</v>
+      </c>
+      <c r="J33" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="K33" s="47"/>
+    </row>
+    <row r="34" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+      <c r="A34" s="12">
+        <v>33</v>
+      </c>
+      <c r="B34" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E34" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="F34" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="G34" s="48">
+        <v>0.84209999999999996</v>
+      </c>
+      <c r="H34" s="44">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="I34" s="44">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="J34" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="K34" s="47"/>
+    </row>
+    <row r="35" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E35" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="G35" s="44">
+        <v>0.83240000000000003</v>
+      </c>
+      <c r="H35" s="44">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="I35" s="44">
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="J35" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="K35" s="47"/>
+    </row>
+    <row r="36" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A36" s="12">
+        <v>35</v>
+      </c>
+      <c r="B36" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E36" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="F36" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="G36" s="44">
+        <v>0.83620000000000005</v>
+      </c>
+      <c r="H36" s="44">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="I36" s="44">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J36" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="K36" s="47"/>
+    </row>
+    <row r="37" spans="1:11" ht="132" x14ac:dyDescent="0.3">
+      <c r="A37" s="4">
+        <v>36</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="G37" s="50">
+        <v>0.93</v>
+      </c>
+      <c r="H37" s="50">
+        <v>0.29330000000000001</v>
+      </c>
+      <c r="I37" s="50">
+        <v>0.88529999999999998</v>
+      </c>
+      <c r="J37" s="51" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="A38" s="12">
+        <v>37</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="F38" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" s="6">
+        <v>0.91149999999999998</v>
+      </c>
+      <c r="H38" s="6">
+        <v>0.2797</v>
+      </c>
+      <c r="I38" s="5">
+        <v>0.85570000000000002</v>
+      </c>
+      <c r="J38" s="51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
+        <v>38</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="G39" s="50">
+        <v>0.84570000000000001</v>
+      </c>
+      <c r="H39" s="50">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="I39" s="50">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="J39" s="52" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="198" x14ac:dyDescent="0.3">
+      <c r="A40" s="12">
+        <v>39</v>
+      </c>
+      <c r="B40" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" s="54">
+        <v>0.2</v>
+      </c>
+      <c r="D40" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="F40" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="58">
+        <v>0.84520600000000001</v>
+      </c>
+      <c r="H40" s="58">
+        <v>0.287053</v>
+      </c>
+      <c r="I40" s="59">
+        <v>0.55980099999999999</v>
+      </c>
+      <c r="J40" s="60" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+      <c r="A41" s="4">
+        <v>40</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="33">
+        <v>0.3</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E41" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="G41" s="6">
+        <v>0.83740000000000003</v>
+      </c>
+      <c r="H41" s="6">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="I41" s="5">
+        <v>8.8999999999999999E-3</v>
+      </c>
+      <c r="J41" s="61" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A42" s="12">
+        <v>41</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E42" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="F42" s="49" t="s">
+        <v>109</v>
+      </c>
+      <c r="G42" s="6">
+        <v>0.83640000000000003</v>
+      </c>
+      <c r="H42" s="6">
+        <v>0.29070000000000001</v>
+      </c>
+      <c r="I42" s="5">
+        <v>0.37040000000000001</v>
+      </c>
+      <c r="J42" s="61" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="198" x14ac:dyDescent="0.3">
+      <c r="A43" s="4">
+        <v>42</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F43" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="G43" s="6">
+        <v>0.83463600000000004</v>
+      </c>
+      <c r="H43" s="6">
+        <v>0.28441</v>
+      </c>
+      <c r="I43" s="5">
+        <v>0.362126</v>
+      </c>
+      <c r="J43" s="61" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="132" x14ac:dyDescent="0.3">
+      <c r="A44" s="12">
+        <v>43</v>
+      </c>
+      <c r="B44" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F44" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="G44" s="6">
+        <v>0.83374000000000004</v>
+      </c>
+      <c r="H44" s="6">
+        <v>4.8411000000000003E-2</v>
+      </c>
+      <c r="I44" s="6">
+        <v>2.6578000000000001E-2</v>
+      </c>
+      <c r="J44" s="52" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A45" s="4">
+        <v>44</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="F45" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="G45" s="6">
+        <v>0.82199999999999995</v>
+      </c>
+      <c r="H45" s="6">
+        <v>0.51739999999999997</v>
+      </c>
+      <c r="I45" s="5">
+        <v>0.64119999999999999</v>
+      </c>
+      <c r="J45" s="61" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A46" s="12">
+        <v>45</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="F46" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="G46" s="6">
+        <v>0.81789999999999996</v>
+      </c>
+      <c r="H46" s="6">
+        <v>0.40849999999999997</v>
+      </c>
+      <c r="I46" s="5">
+        <v>0.54149999999999998</v>
+      </c>
+      <c r="J46" s="61" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A47" s="4">
+        <v>46</v>
+      </c>
+      <c r="B47" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C47" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E47" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F47" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0.81730000000000003</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0.30709999999999998</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0.42520000000000002</v>
+      </c>
+      <c r="J47" s="62" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A48" s="12">
+        <v>47</v>
+      </c>
+      <c r="B48" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D48" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="F48" s="49" t="s">
+        <v>119</v>
+      </c>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
-      <c r="I48" s="7"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="4"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="6"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="63" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A49" s="4">
+        <v>48</v>
+      </c>
+      <c r="B49" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D49" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F49" s="49" t="s">
+        <v>119</v>
+      </c>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
-      <c r="I49" s="7"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="4"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="7"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="4"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="7"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="4"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="7"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="4"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="7"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="4"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="7"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="4"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="7"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="4"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="7"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="4"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="7"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="4"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="7"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="4"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="7"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="4"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="7"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="4"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="7"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="4"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="7"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="4"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="7"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="4"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="7"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="4"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="7"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="4"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="7"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="4"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="7"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="4"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="7"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="4"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="7"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" s="4"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="7"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" s="4"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="7"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="4"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="7"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I49" s="5"/>
+      <c r="J49" s="63" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A50" s="12">
+        <v>49</v>
+      </c>
+      <c r="B50" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D50" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F50" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="63" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+      <c r="A51" s="12">
+        <v>50</v>
+      </c>
+      <c r="B51" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C51" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D51" s="64">
+        <v>86</v>
+      </c>
+      <c r="E51" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F51" s="65" t="s">
+        <v>124</v>
+      </c>
+      <c r="G51" s="66">
+        <v>0.84209999999999996</v>
+      </c>
+      <c r="H51" s="64">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="I51" s="64">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J51" s="67" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="99" x14ac:dyDescent="0.3">
+      <c r="A52" s="4">
+        <v>51</v>
+      </c>
+      <c r="B52" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D52" s="68">
+        <v>86</v>
+      </c>
+      <c r="E52" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F52" s="69" t="s">
+        <v>127</v>
+      </c>
+      <c r="G52" s="68">
+        <v>0.62160000000000004</v>
+      </c>
+      <c r="H52" s="68">
+        <v>0</v>
+      </c>
+      <c r="I52" s="68">
+        <v>0</v>
+      </c>
+      <c r="J52" s="70" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A53" s="12">
+        <v>52</v>
+      </c>
+      <c r="B53" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D53" s="64">
+        <v>86</v>
+      </c>
+      <c r="E53" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F53" s="69" t="s">
+        <v>129</v>
+      </c>
+      <c r="G53" s="68">
+        <v>0.8528</v>
+      </c>
+      <c r="H53" s="68">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="I53" s="68">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="J53" s="70" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="A54" s="12">
+        <v>53</v>
+      </c>
+      <c r="B54" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="C54" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D54" s="68">
+        <v>86</v>
+      </c>
+      <c r="E54" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F54" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="G54" s="68">
+        <v>0.60240000000000005</v>
+      </c>
+      <c r="H54" s="68">
+        <v>0</v>
+      </c>
+      <c r="I54" s="68">
+        <v>0</v>
+      </c>
+      <c r="J54" s="70" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+      <c r="A55" s="4">
+        <v>54</v>
+      </c>
+      <c r="B55" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D55" s="68">
+        <v>149</v>
+      </c>
+      <c r="E55" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F55" s="69" t="s">
+        <v>124</v>
+      </c>
+      <c r="G55" s="68">
+        <v>0.8417</v>
+      </c>
+      <c r="H55" s="68">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="I55" s="68">
+        <v>0.01</v>
+      </c>
+      <c r="J55" s="70" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="99" x14ac:dyDescent="0.3">
+      <c r="A56" s="12">
+        <v>55</v>
+      </c>
+      <c r="B56" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D56" s="68">
+        <v>149</v>
+      </c>
+      <c r="E56" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F56" s="69" t="s">
+        <v>127</v>
+      </c>
+      <c r="G56" s="68">
+        <v>0.62290000000000001</v>
+      </c>
+      <c r="H56" s="68">
+        <v>0</v>
+      </c>
+      <c r="I56" s="68">
+        <v>0</v>
+      </c>
+      <c r="J56" s="70" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+      <c r="A57" s="12">
+        <v>56</v>
+      </c>
+      <c r="B57" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D57" s="68">
+        <v>149</v>
+      </c>
+      <c r="E57" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F57" s="69" t="s">
+        <v>135</v>
+      </c>
+      <c r="G57" s="68">
+        <v>0.85160000000000002</v>
+      </c>
+      <c r="H57" s="68">
+        <v>1.32E-2</v>
+      </c>
+      <c r="I57" s="68">
+        <v>6.6E-3</v>
+      </c>
+      <c r="J57" s="70" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A58" s="4">
+        <v>57</v>
+      </c>
+      <c r="B58" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="C58" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D58" s="68">
+        <v>149</v>
+      </c>
+      <c r="E58" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F58" s="69" t="s">
+        <v>137</v>
+      </c>
+      <c r="G58" s="68">
+        <v>0.64229999999999998</v>
+      </c>
+      <c r="H58" s="68">
+        <v>7.6600000000000001E-2</v>
+      </c>
+      <c r="I58" s="68">
+        <v>0.1096</v>
+      </c>
+      <c r="J58" s="70" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+      <c r="A59" s="12">
+        <v>58</v>
+      </c>
+      <c r="B59" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D59" s="68">
+        <v>86</v>
+      </c>
+      <c r="E59" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F59" s="69" t="s">
+        <v>135</v>
+      </c>
+      <c r="G59" s="68">
+        <v>0.85219999999999996</v>
+      </c>
+      <c r="H59" s="68">
+        <v>6.6E-3</v>
+      </c>
+      <c r="I59" s="68">
+        <v>3.3E-3</v>
+      </c>
+      <c r="J59" s="70" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A60" s="12">
+        <v>59</v>
+      </c>
+      <c r="B60" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D60" s="68">
+        <v>86</v>
+      </c>
+      <c r="E60" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F60" s="69" t="s">
+        <v>137</v>
+      </c>
+      <c r="G60" s="68">
+        <v>0.80769999999999997</v>
+      </c>
+      <c r="H60" s="68">
+        <v>0.16089999999999999</v>
+      </c>
+      <c r="I60" s="68">
+        <v>0.16089999999999999</v>
+      </c>
+      <c r="J60" s="70" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+      <c r="A61" s="4">
+        <v>60</v>
+      </c>
+      <c r="B61" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D61" s="68">
+        <v>149</v>
+      </c>
+      <c r="E61" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F61" s="69" t="s">
+        <v>135</v>
+      </c>
+      <c r="G61" s="68">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="H61" s="68">
+        <v>6.6E-3</v>
+      </c>
+      <c r="I61" s="68">
+        <v>3.3E-3</v>
+      </c>
+      <c r="J61" s="70" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A62" s="12">
+        <v>61</v>
+      </c>
+      <c r="B62" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D62" s="68">
+        <v>149</v>
+      </c>
+      <c r="E62" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F62" s="69" t="s">
+        <v>137</v>
+      </c>
+      <c r="G62" s="68">
+        <v>0.80630000000000002</v>
+      </c>
+      <c r="H62" s="68">
+        <v>0.16170000000000001</v>
+      </c>
+      <c r="I62" s="68">
+        <v>0.77239999999999998</v>
+      </c>
+      <c r="J62" s="70" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="198" x14ac:dyDescent="0.3">
+      <c r="A63" s="12">
+        <v>62</v>
+      </c>
+      <c r="B63" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C63" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D63" s="68">
+        <v>149</v>
+      </c>
+      <c r="E63" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="F63" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="G63" s="68">
+        <v>0.85099999999999998</v>
+      </c>
+      <c r="H63" s="68">
+        <v>3.3E-3</v>
+      </c>
+      <c r="I63" s="68">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="J63" s="70" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+      <c r="A64" s="4">
+        <v>63</v>
+      </c>
+      <c r="B64" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="C64" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D64" s="68">
+        <v>149</v>
+      </c>
+      <c r="E64" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="F64" s="69" t="s">
+        <v>144</v>
+      </c>
+      <c r="G64" s="68">
+        <v>0.61850000000000005</v>
+      </c>
+      <c r="H64" s="68">
+        <v>0</v>
+      </c>
+      <c r="I64" s="68">
+        <v>0</v>
+      </c>
+      <c r="J64" s="70" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="198" x14ac:dyDescent="0.3">
+      <c r="A65" s="12">
+        <v>64</v>
+      </c>
+      <c r="B65" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C65" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D65" s="68">
+        <v>149</v>
+      </c>
+      <c r="E65" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="F65" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="G65" s="68">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="H65" s="68">
+        <v>6.6E-3</v>
+      </c>
+      <c r="I65" s="68">
+        <v>3.3E-3</v>
+      </c>
+      <c r="J65" s="70" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+      <c r="A66" s="12">
+        <v>65</v>
+      </c>
+      <c r="B66" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="C66" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D66" s="68">
+        <v>149</v>
+      </c>
+      <c r="E66" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="F66" s="69" t="s">
+        <v>144</v>
+      </c>
+      <c r="G66" s="68">
+        <v>0.64380000000000004</v>
+      </c>
+      <c r="H66" s="68">
+        <v>7.9500000000000001E-2</v>
+      </c>
+      <c r="I66" s="68">
+        <v>0.1047</v>
+      </c>
+      <c r="J66" s="70" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="198" x14ac:dyDescent="0.3">
+      <c r="A67" s="4">
+        <v>66</v>
+      </c>
+      <c r="B67" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C67" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D67" s="68">
+        <v>149</v>
+      </c>
+      <c r="E67" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="F67" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="G67" s="68">
+        <v>0.84119999999999995</v>
+      </c>
+      <c r="H67" s="68">
+        <v>5.3E-3</v>
+      </c>
+      <c r="I67" s="68">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="J67" s="71" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+      <c r="A68" s="12">
+        <v>67</v>
+      </c>
+      <c r="B68" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="C68" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D68" s="68">
+        <v>149</v>
+      </c>
+      <c r="E68" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="F68" s="69" t="s">
+        <v>144</v>
+      </c>
+      <c r="G68" s="68">
+        <v>0.61219999999999997</v>
+      </c>
+      <c r="H68" s="68">
+        <v>0</v>
+      </c>
+      <c r="I68" s="68">
+        <v>0</v>
+      </c>
+      <c r="J68" s="71" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A69" s="12">
+        <v>68</v>
+      </c>
+      <c r="B69" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C69" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D69" s="68">
+        <v>149</v>
+      </c>
+      <c r="E69" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="F69" s="69" t="s">
+        <v>150</v>
+      </c>
+      <c r="G69" s="68">
+        <v>0.85040000000000004</v>
+      </c>
+      <c r="H69" s="68">
+        <v>0.2923</v>
+      </c>
+      <c r="I69" s="68">
+        <v>0.36709999999999998</v>
+      </c>
+      <c r="J69" s="70" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="99" x14ac:dyDescent="0.3">
+      <c r="A70" s="4">
+        <v>69</v>
+      </c>
+      <c r="B70" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="C70" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D70" s="68">
+        <v>149</v>
+      </c>
+      <c r="E70" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="F70" s="69" t="s">
+        <v>152</v>
+      </c>
+      <c r="G70" s="68">
+        <v>0.65249999999999997</v>
+      </c>
+      <c r="H70" s="68">
+        <v>8.0199999999999994E-2</v>
+      </c>
+      <c r="I70" s="68">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="J70" s="70" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A71" s="12">
+        <v>70</v>
+      </c>
+      <c r="B71" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C71" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D71" s="68">
+        <v>149</v>
+      </c>
+      <c r="E71" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="F71" s="69" t="s">
+        <v>150</v>
+      </c>
+      <c r="G71" s="68">
+        <v>0.84019999999999995</v>
+      </c>
+      <c r="H71" s="68">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="I71" s="68">
+        <v>0.74250000000000005</v>
+      </c>
+      <c r="J71" s="70" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="99" x14ac:dyDescent="0.3">
+      <c r="A72" s="12">
+        <v>71</v>
+      </c>
+      <c r="B72" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="C72" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D72" s="68">
+        <v>149</v>
+      </c>
+      <c r="E72" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="F72" s="69" t="s">
+        <v>152</v>
+      </c>
+      <c r="G72" s="68">
+        <v>0.63870000000000005</v>
+      </c>
+      <c r="H72" s="68">
+        <v>0.1341</v>
+      </c>
+      <c r="I72" s="68">
+        <v>9.1399999999999995E-2</v>
+      </c>
+      <c r="J72" s="70" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="4"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
-      <c r="F73" s="6"/>
+      <c r="F73" s="5"/>
       <c r="G73" s="6"/>
       <c r="H73" s="6"/>
-      <c r="I73" s="7"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I73" s="6"/>
+      <c r="J73" s="7"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="4"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
-      <c r="F74" s="6"/>
+      <c r="F74" s="5"/>
       <c r="G74" s="6"/>
       <c r="H74" s="6"/>
-      <c r="I74" s="7"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I74" s="6"/>
+      <c r="J74" s="7"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
-      <c r="F75" s="6"/>
+      <c r="F75" s="5"/>
       <c r="G75" s="6"/>
       <c r="H75" s="6"/>
-      <c r="I75" s="7"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I75" s="6"/>
+      <c r="J75" s="7"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="4"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
-      <c r="F76" s="6"/>
+      <c r="F76" s="5"/>
       <c r="G76" s="6"/>
       <c r="H76" s="6"/>
-      <c r="I76" s="7"/>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I76" s="6"/>
+      <c r="J76" s="7"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
-      <c r="F77" s="6"/>
+      <c r="F77" s="5"/>
       <c r="G77" s="6"/>
       <c r="H77" s="6"/>
-      <c r="I77" s="7"/>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I77" s="6"/>
+      <c r="J77" s="7"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
-      <c r="F78" s="6"/>
+      <c r="F78" s="5"/>
       <c r="G78" s="6"/>
       <c r="H78" s="6"/>
-      <c r="I78" s="7"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I78" s="6"/>
+      <c r="J78" s="7"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
-      <c r="F79" s="6"/>
+      <c r="F79" s="5"/>
       <c r="G79" s="6"/>
       <c r="H79" s="6"/>
-      <c r="I79" s="7"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I79" s="6"/>
+      <c r="J79" s="7"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="4"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
-      <c r="F80" s="6"/>
+      <c r="F80" s="5"/>
       <c r="G80" s="6"/>
       <c r="H80" s="6"/>
-      <c r="I80" s="7"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I80" s="6"/>
+      <c r="J80" s="7"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="4"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
-      <c r="F81" s="6"/>
+      <c r="F81" s="5"/>
       <c r="G81" s="6"/>
       <c r="H81" s="6"/>
-      <c r="I81" s="7"/>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I81" s="6"/>
+      <c r="J81" s="7"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="4"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
-      <c r="F82" s="6"/>
+      <c r="F82" s="5"/>
       <c r="G82" s="6"/>
       <c r="H82" s="6"/>
-      <c r="I82" s="7"/>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I82" s="6"/>
+      <c r="J82" s="7"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="4"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
-      <c r="F83" s="6"/>
+      <c r="F83" s="5"/>
       <c r="G83" s="6"/>
       <c r="H83" s="6"/>
-      <c r="I83" s="7"/>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I83" s="6"/>
+      <c r="J83" s="7"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="4"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
-      <c r="F84" s="6"/>
+      <c r="F84" s="5"/>
       <c r="G84" s="6"/>
       <c r="H84" s="6"/>
-      <c r="I84" s="7"/>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I84" s="6"/>
+      <c r="J84" s="7"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
-      <c r="F85" s="6"/>
+      <c r="F85" s="5"/>
       <c r="G85" s="6"/>
       <c r="H85" s="6"/>
-      <c r="I85" s="7"/>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I85" s="6"/>
+      <c r="J85" s="7"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="4"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
-      <c r="F86" s="6"/>
+      <c r="F86" s="5"/>
       <c r="G86" s="6"/>
       <c r="H86" s="6"/>
-      <c r="I86" s="7"/>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I86" s="6"/>
+      <c r="J86" s="7"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="4"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
-      <c r="F87" s="6"/>
+      <c r="F87" s="5"/>
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
-      <c r="I87" s="7"/>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I87" s="6"/>
+      <c r="J87" s="7"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="4"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
-      <c r="F88" s="6"/>
+      <c r="F88" s="5"/>
       <c r="G88" s="6"/>
       <c r="H88" s="6"/>
-      <c r="I88" s="7"/>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I88" s="6"/>
+      <c r="J88" s="7"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="4"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
-      <c r="F89" s="6"/>
+      <c r="F89" s="5"/>
       <c r="G89" s="6"/>
       <c r="H89" s="6"/>
-      <c r="I89" s="7"/>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I89" s="6"/>
+      <c r="J89" s="7"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="4"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
-      <c r="F90" s="6"/>
+      <c r="F90" s="5"/>
       <c r="G90" s="6"/>
       <c r="H90" s="6"/>
-      <c r="I90" s="7"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I90" s="6"/>
+      <c r="J90" s="7"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="4"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
-      <c r="F91" s="6"/>
+      <c r="F91" s="5"/>
       <c r="G91" s="6"/>
       <c r="H91" s="6"/>
-      <c r="I91" s="7"/>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I91" s="6"/>
+      <c r="J91" s="7"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="4"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
-      <c r="F92" s="6"/>
+      <c r="F92" s="5"/>
       <c r="G92" s="6"/>
       <c r="H92" s="6"/>
-      <c r="I92" s="7"/>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I92" s="6"/>
+      <c r="J92" s="7"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="4"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
-      <c r="F93" s="6"/>
+      <c r="F93" s="5"/>
       <c r="G93" s="6"/>
       <c r="H93" s="6"/>
-      <c r="I93" s="7"/>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I93" s="6"/>
+      <c r="J93" s="7"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="4"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
-      <c r="F94" s="6"/>
+      <c r="F94" s="5"/>
       <c r="G94" s="6"/>
       <c r="H94" s="6"/>
-      <c r="I94" s="7"/>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I94" s="6"/>
+      <c r="J94" s="7"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="4"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
-      <c r="F95" s="6"/>
+      <c r="F95" s="5"/>
       <c r="G95" s="6"/>
       <c r="H95" s="6"/>
-      <c r="I95" s="7"/>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I95" s="6"/>
+      <c r="J95" s="7"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="4"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
-      <c r="F96" s="6"/>
+      <c r="F96" s="5"/>
       <c r="G96" s="6"/>
       <c r="H96" s="6"/>
-      <c r="I96" s="7"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I96" s="6"/>
+      <c r="J96" s="7"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="4"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
-      <c r="F97" s="6"/>
+      <c r="F97" s="5"/>
       <c r="G97" s="6"/>
       <c r="H97" s="6"/>
-      <c r="I97" s="7"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I97" s="6"/>
+      <c r="J97" s="7"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="4"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
-      <c r="F98" s="6"/>
+      <c r="F98" s="5"/>
       <c r="G98" s="6"/>
       <c r="H98" s="6"/>
-      <c r="I98" s="7"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I98" s="6"/>
+      <c r="J98" s="7"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="4"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
-      <c r="F99" s="6"/>
+      <c r="F99" s="5"/>
       <c r="G99" s="6"/>
       <c r="H99" s="6"/>
-      <c r="I99" s="7"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I99" s="6"/>
+      <c r="J99" s="7"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="4"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
-      <c r="F100" s="6"/>
+      <c r="F100" s="5"/>
       <c r="G100" s="6"/>
       <c r="H100" s="6"/>
-      <c r="I100" s="7"/>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I100" s="6"/>
+      <c r="J100" s="7"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="4"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
-      <c r="F101" s="6"/>
+      <c r="F101" s="5"/>
       <c r="G101" s="6"/>
       <c r="H101" s="6"/>
-      <c r="I101" s="7"/>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I101" s="6"/>
+      <c r="J101" s="7"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="4"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
-      <c r="F102" s="6"/>
+      <c r="F102" s="5"/>
       <c r="G102" s="6"/>
       <c r="H102" s="6"/>
-      <c r="I102" s="7"/>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I102" s="6"/>
+      <c r="J102" s="7"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="4"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
-      <c r="F103" s="6"/>
+      <c r="F103" s="5"/>
       <c r="G103" s="6"/>
       <c r="H103" s="6"/>
-      <c r="I103" s="7"/>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I103" s="6"/>
+      <c r="J103" s="7"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="4"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
       <c r="D104" s="5"/>
       <c r="E104" s="5"/>
-      <c r="F104" s="6"/>
+      <c r="F104" s="5"/>
       <c r="G104" s="6"/>
       <c r="H104" s="6"/>
-      <c r="I104" s="7"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I104" s="6"/>
+      <c r="J104" s="7"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="4"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
       <c r="D105" s="5"/>
       <c r="E105" s="5"/>
-      <c r="F105" s="6"/>
+      <c r="F105" s="5"/>
       <c r="G105" s="6"/>
       <c r="H105" s="6"/>
-      <c r="I105" s="7"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I105" s="6"/>
+      <c r="J105" s="7"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="4"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
       <c r="D106" s="5"/>
       <c r="E106" s="5"/>
-      <c r="F106" s="6"/>
+      <c r="F106" s="5"/>
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
-      <c r="I106" s="7"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I106" s="6"/>
+      <c r="J106" s="7"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="4"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
-      <c r="F107" s="6"/>
+      <c r="F107" s="5"/>
       <c r="G107" s="6"/>
       <c r="H107" s="6"/>
-      <c r="I107" s="7"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I107" s="6"/>
+      <c r="J107" s="7"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="4"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
-      <c r="F108" s="6"/>
+      <c r="F108" s="5"/>
       <c r="G108" s="6"/>
       <c r="H108" s="6"/>
-      <c r="I108" s="7"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I108" s="6"/>
+      <c r="J108" s="7"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="4"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
       <c r="D109" s="5"/>
       <c r="E109" s="5"/>
-      <c r="F109" s="6"/>
+      <c r="F109" s="5"/>
       <c r="G109" s="6"/>
       <c r="H109" s="6"/>
-      <c r="I109" s="7"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I109" s="6"/>
+      <c r="J109" s="7"/>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="4"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
       <c r="D110" s="5"/>
       <c r="E110" s="5"/>
-      <c r="F110" s="6"/>
+      <c r="F110" s="5"/>
       <c r="G110" s="6"/>
       <c r="H110" s="6"/>
-      <c r="I110" s="7"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I110" s="6"/>
+      <c r="J110" s="7"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="4"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
       <c r="D111" s="5"/>
       <c r="E111" s="5"/>
-      <c r="F111" s="6"/>
+      <c r="F111" s="5"/>
       <c r="G111" s="6"/>
       <c r="H111" s="6"/>
-      <c r="I111" s="7"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I111" s="6"/>
+      <c r="J111" s="7"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="4"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
       <c r="D112" s="5"/>
       <c r="E112" s="5"/>
-      <c r="F112" s="6"/>
+      <c r="F112" s="5"/>
       <c r="G112" s="6"/>
       <c r="H112" s="6"/>
-      <c r="I112" s="7"/>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I112" s="6"/>
+      <c r="J112" s="7"/>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="4"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
       <c r="D113" s="5"/>
       <c r="E113" s="5"/>
-      <c r="F113" s="6"/>
+      <c r="F113" s="5"/>
       <c r="G113" s="6"/>
       <c r="H113" s="6"/>
-      <c r="I113" s="7"/>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I113" s="6"/>
+      <c r="J113" s="7"/>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="4"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
       <c r="D114" s="5"/>
       <c r="E114" s="5"/>
-      <c r="F114" s="6"/>
+      <c r="F114" s="5"/>
       <c r="G114" s="6"/>
       <c r="H114" s="6"/>
-      <c r="I114" s="7"/>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I114" s="6"/>
+      <c r="J114" s="7"/>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="4"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
       <c r="D115" s="5"/>
       <c r="E115" s="5"/>
-      <c r="F115" s="6"/>
+      <c r="F115" s="5"/>
       <c r="G115" s="6"/>
       <c r="H115" s="6"/>
-      <c r="I115" s="7"/>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I115" s="6"/>
+      <c r="J115" s="7"/>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="4"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
       <c r="D116" s="5"/>
       <c r="E116" s="5"/>
-      <c r="F116" s="6"/>
+      <c r="F116" s="5"/>
       <c r="G116" s="6"/>
       <c r="H116" s="6"/>
-      <c r="I116" s="7"/>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I116" s="6"/>
+      <c r="J116" s="7"/>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="4"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
       <c r="D117" s="5"/>
       <c r="E117" s="5"/>
-      <c r="F117" s="6"/>
+      <c r="F117" s="5"/>
       <c r="G117" s="6"/>
       <c r="H117" s="6"/>
-      <c r="I117" s="7"/>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I117" s="6"/>
+      <c r="J117" s="7"/>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="4"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
       <c r="D118" s="5"/>
       <c r="E118" s="5"/>
-      <c r="F118" s="6"/>
+      <c r="F118" s="5"/>
       <c r="G118" s="6"/>
       <c r="H118" s="6"/>
-      <c r="I118" s="7"/>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I118" s="6"/>
+      <c r="J118" s="7"/>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="4"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
       <c r="D119" s="5"/>
       <c r="E119" s="5"/>
-      <c r="F119" s="6"/>
+      <c r="F119" s="5"/>
       <c r="G119" s="6"/>
       <c r="H119" s="6"/>
-      <c r="I119" s="7"/>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I119" s="6"/>
+      <c r="J119" s="7"/>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="4"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
-      <c r="F120" s="6"/>
+      <c r="F120" s="5"/>
       <c r="G120" s="6"/>
       <c r="H120" s="6"/>
-      <c r="I120" s="7"/>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I120" s="6"/>
+      <c r="J120" s="7"/>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="4"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
       <c r="D121" s="5"/>
       <c r="E121" s="5"/>
-      <c r="F121" s="6"/>
+      <c r="F121" s="5"/>
       <c r="G121" s="6"/>
       <c r="H121" s="6"/>
-      <c r="I121" s="7"/>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I121" s="6"/>
+      <c r="J121" s="7"/>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="4"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
-      <c r="F122" s="6"/>
+      <c r="F122" s="5"/>
       <c r="G122" s="6"/>
       <c r="H122" s="6"/>
-      <c r="I122" s="7"/>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I122" s="6"/>
+      <c r="J122" s="7"/>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="4"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
       <c r="D123" s="5"/>
       <c r="E123" s="5"/>
-      <c r="F123" s="6"/>
+      <c r="F123" s="5"/>
       <c r="G123" s="6"/>
       <c r="H123" s="6"/>
-      <c r="I123" s="7"/>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I123" s="6"/>
+      <c r="J123" s="7"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="4"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
       <c r="D124" s="5"/>
       <c r="E124" s="5"/>
-      <c r="F124" s="6"/>
+      <c r="F124" s="5"/>
       <c r="G124" s="6"/>
       <c r="H124" s="6"/>
-      <c r="I124" s="7"/>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I124" s="6"/>
+      <c r="J124" s="7"/>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="4"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
       <c r="D125" s="5"/>
       <c r="E125" s="5"/>
-      <c r="F125" s="6"/>
+      <c r="F125" s="5"/>
       <c r="G125" s="6"/>
       <c r="H125" s="6"/>
-      <c r="I125" s="7"/>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I125" s="6"/>
+      <c r="J125" s="7"/>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="4"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
       <c r="D126" s="5"/>
       <c r="E126" s="5"/>
-      <c r="F126" s="6"/>
+      <c r="F126" s="5"/>
       <c r="G126" s="6"/>
       <c r="H126" s="6"/>
-      <c r="I126" s="7"/>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I126" s="6"/>
+      <c r="J126" s="7"/>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="4"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
       <c r="D127" s="5"/>
       <c r="E127" s="5"/>
-      <c r="F127" s="6"/>
+      <c r="F127" s="5"/>
       <c r="G127" s="6"/>
       <c r="H127" s="6"/>
-      <c r="I127" s="7"/>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I127" s="6"/>
+      <c r="J127" s="7"/>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="4"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
       <c r="D128" s="5"/>
       <c r="E128" s="5"/>
-      <c r="F128" s="6"/>
+      <c r="F128" s="5"/>
       <c r="G128" s="6"/>
       <c r="H128" s="6"/>
-      <c r="I128" s="7"/>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I128" s="6"/>
+      <c r="J128" s="7"/>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="4"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
       <c r="D129" s="5"/>
       <c r="E129" s="5"/>
-      <c r="F129" s="6"/>
+      <c r="F129" s="5"/>
       <c r="G129" s="6"/>
       <c r="H129" s="6"/>
-      <c r="I129" s="7"/>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I129" s="6"/>
+      <c r="J129" s="7"/>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="4"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
       <c r="D130" s="5"/>
       <c r="E130" s="5"/>
-      <c r="F130" s="6"/>
+      <c r="F130" s="5"/>
       <c r="G130" s="6"/>
       <c r="H130" s="6"/>
-      <c r="I130" s="7"/>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I130" s="6"/>
+      <c r="J130" s="7"/>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="4"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
       <c r="D131" s="5"/>
       <c r="E131" s="5"/>
-      <c r="F131" s="6"/>
+      <c r="F131" s="5"/>
       <c r="G131" s="6"/>
       <c r="H131" s="6"/>
-      <c r="I131" s="7"/>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I131" s="6"/>
+      <c r="J131" s="7"/>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="4"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
       <c r="D132" s="5"/>
       <c r="E132" s="5"/>
-      <c r="F132" s="6"/>
+      <c r="F132" s="5"/>
       <c r="G132" s="6"/>
       <c r="H132" s="6"/>
-      <c r="I132" s="7"/>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I132" s="6"/>
+      <c r="J132" s="7"/>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="4"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
       <c r="D133" s="5"/>
       <c r="E133" s="5"/>
-      <c r="F133" s="6"/>
+      <c r="F133" s="5"/>
       <c r="G133" s="6"/>
       <c r="H133" s="6"/>
-      <c r="I133" s="7"/>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I133" s="6"/>
+      <c r="J133" s="7"/>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="4"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
       <c r="D134" s="5"/>
       <c r="E134" s="5"/>
-      <c r="F134" s="6"/>
+      <c r="F134" s="5"/>
       <c r="G134" s="6"/>
       <c r="H134" s="6"/>
-      <c r="I134" s="7"/>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I134" s="6"/>
+      <c r="J134" s="7"/>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="4"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
       <c r="D135" s="5"/>
       <c r="E135" s="5"/>
-      <c r="F135" s="6"/>
+      <c r="F135" s="5"/>
       <c r="G135" s="6"/>
       <c r="H135" s="6"/>
-      <c r="I135" s="7"/>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I135" s="6"/>
+      <c r="J135" s="7"/>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="4"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
       <c r="D136" s="5"/>
       <c r="E136" s="5"/>
-      <c r="F136" s="6"/>
+      <c r="F136" s="5"/>
       <c r="G136" s="6"/>
       <c r="H136" s="6"/>
-      <c r="I136" s="7"/>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I136" s="6"/>
+      <c r="J136" s="7"/>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="4"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
       <c r="D137" s="5"/>
       <c r="E137" s="5"/>
-      <c r="F137" s="6"/>
+      <c r="F137" s="5"/>
       <c r="G137" s="6"/>
       <c r="H137" s="6"/>
-      <c r="I137" s="7"/>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I137" s="6"/>
+      <c r="J137" s="7"/>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="4"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
       <c r="D138" s="5"/>
       <c r="E138" s="5"/>
-      <c r="F138" s="6"/>
+      <c r="F138" s="5"/>
       <c r="G138" s="6"/>
       <c r="H138" s="6"/>
-      <c r="I138" s="7"/>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I138" s="6"/>
+      <c r="J138" s="7"/>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="4"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
       <c r="D139" s="5"/>
       <c r="E139" s="5"/>
-      <c r="F139" s="6"/>
+      <c r="F139" s="5"/>
       <c r="G139" s="6"/>
       <c r="H139" s="6"/>
-      <c r="I139" s="7"/>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I139" s="6"/>
+      <c r="J139" s="7"/>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="4"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
       <c r="D140" s="5"/>
       <c r="E140" s="5"/>
-      <c r="F140" s="6"/>
+      <c r="F140" s="5"/>
       <c r="G140" s="6"/>
       <c r="H140" s="6"/>
-      <c r="I140" s="7"/>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I140" s="6"/>
+      <c r="J140" s="7"/>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="4"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
       <c r="D141" s="5"/>
       <c r="E141" s="5"/>
-      <c r="F141" s="6"/>
+      <c r="F141" s="5"/>
       <c r="G141" s="6"/>
       <c r="H141" s="6"/>
-      <c r="I141" s="7"/>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I141" s="6"/>
+      <c r="J141" s="7"/>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="4"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
       <c r="D142" s="5"/>
       <c r="E142" s="5"/>
-      <c r="F142" s="6"/>
+      <c r="F142" s="5"/>
       <c r="G142" s="6"/>
       <c r="H142" s="6"/>
-      <c r="I142" s="7"/>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I142" s="6"/>
+      <c r="J142" s="7"/>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="4"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
       <c r="D143" s="5"/>
       <c r="E143" s="5"/>
-      <c r="F143" s="6"/>
+      <c r="F143" s="5"/>
       <c r="G143" s="6"/>
       <c r="H143" s="6"/>
-      <c r="I143" s="7"/>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I143" s="6"/>
+      <c r="J143" s="7"/>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="4"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
       <c r="D144" s="5"/>
       <c r="E144" s="5"/>
-      <c r="F144" s="6"/>
+      <c r="F144" s="5"/>
       <c r="G144" s="6"/>
       <c r="H144" s="6"/>
-      <c r="I144" s="7"/>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I144" s="6"/>
+      <c r="J144" s="7"/>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="4"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
       <c r="D145" s="5"/>
       <c r="E145" s="5"/>
-      <c r="F145" s="6"/>
+      <c r="F145" s="5"/>
       <c r="G145" s="6"/>
       <c r="H145" s="6"/>
-      <c r="I145" s="7"/>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I145" s="6"/>
+      <c r="J145" s="7"/>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="4"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
       <c r="D146" s="5"/>
       <c r="E146" s="5"/>
-      <c r="F146" s="6"/>
+      <c r="F146" s="5"/>
       <c r="G146" s="6"/>
       <c r="H146" s="6"/>
-      <c r="I146" s="7"/>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I146" s="6"/>
+      <c r="J146" s="7"/>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
       <c r="D147" s="5"/>
       <c r="E147" s="5"/>
-      <c r="F147" s="6"/>
+      <c r="F147" s="5"/>
       <c r="G147" s="6"/>
       <c r="H147" s="6"/>
-      <c r="I147" s="7"/>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I147" s="6"/>
+      <c r="J147" s="7"/>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
       <c r="D148" s="5"/>
       <c r="E148" s="5"/>
-      <c r="F148" s="6"/>
+      <c r="F148" s="5"/>
       <c r="G148" s="6"/>
       <c r="H148" s="6"/>
-      <c r="I148" s="7"/>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I148" s="6"/>
+      <c r="J148" s="7"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="4"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
       <c r="D149" s="5"/>
       <c r="E149" s="5"/>
-      <c r="F149" s="6"/>
+      <c r="F149" s="5"/>
       <c r="G149" s="6"/>
       <c r="H149" s="6"/>
-      <c r="I149" s="7"/>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I149" s="6"/>
+      <c r="J149" s="7"/>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="4"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
       <c r="D150" s="5"/>
       <c r="E150" s="5"/>
-      <c r="F150" s="6"/>
+      <c r="F150" s="5"/>
       <c r="G150" s="6"/>
       <c r="H150" s="6"/>
-      <c r="I150" s="7"/>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I150" s="6"/>
+      <c r="J150" s="7"/>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="4"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
       <c r="D151" s="5"/>
       <c r="E151" s="5"/>
-      <c r="F151" s="6"/>
+      <c r="F151" s="5"/>
       <c r="G151" s="6"/>
       <c r="H151" s="6"/>
-      <c r="I151" s="7"/>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I151" s="6"/>
+      <c r="J151" s="7"/>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="4"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
       <c r="D152" s="5"/>
       <c r="E152" s="5"/>
-      <c r="F152" s="6"/>
+      <c r="F152" s="5"/>
       <c r="G152" s="6"/>
       <c r="H152" s="6"/>
-      <c r="I152" s="7"/>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I152" s="6"/>
+      <c r="J152" s="7"/>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="4"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
       <c r="D153" s="5"/>
       <c r="E153" s="5"/>
-      <c r="F153" s="6"/>
+      <c r="F153" s="5"/>
       <c r="G153" s="6"/>
       <c r="H153" s="6"/>
-      <c r="I153" s="7"/>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I153" s="6"/>
+      <c r="J153" s="7"/>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
       <c r="D154" s="5"/>
       <c r="E154" s="5"/>
-      <c r="F154" s="6"/>
+      <c r="F154" s="5"/>
       <c r="G154" s="6"/>
       <c r="H154" s="6"/>
-      <c r="I154" s="7"/>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I154" s="6"/>
+      <c r="J154" s="7"/>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="4"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
       <c r="D155" s="5"/>
       <c r="E155" s="5"/>
-      <c r="F155" s="6"/>
+      <c r="F155" s="5"/>
       <c r="G155" s="6"/>
       <c r="H155" s="6"/>
-      <c r="I155" s="7"/>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I155" s="6"/>
+      <c r="J155" s="7"/>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="4"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
       <c r="D156" s="5"/>
       <c r="E156" s="5"/>
-      <c r="F156" s="6"/>
+      <c r="F156" s="5"/>
       <c r="G156" s="6"/>
       <c r="H156" s="6"/>
-      <c r="I156" s="7"/>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I156" s="6"/>
+      <c r="J156" s="7"/>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="4"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
       <c r="D157" s="5"/>
       <c r="E157" s="5"/>
-      <c r="F157" s="6"/>
+      <c r="F157" s="5"/>
       <c r="G157" s="6"/>
       <c r="H157" s="6"/>
-      <c r="I157" s="7"/>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I157" s="6"/>
+      <c r="J157" s="7"/>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="4"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
       <c r="D158" s="5"/>
       <c r="E158" s="5"/>
-      <c r="F158" s="6"/>
+      <c r="F158" s="5"/>
       <c r="G158" s="6"/>
       <c r="H158" s="6"/>
-      <c r="I158" s="7"/>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I158" s="6"/>
+      <c r="J158" s="7"/>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="4"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
       <c r="D159" s="5"/>
       <c r="E159" s="5"/>
-      <c r="F159" s="6"/>
+      <c r="F159" s="5"/>
       <c r="G159" s="6"/>
       <c r="H159" s="6"/>
-      <c r="I159" s="7"/>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I159" s="6"/>
+      <c r="J159" s="7"/>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="4"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
       <c r="D160" s="5"/>
       <c r="E160" s="5"/>
-      <c r="F160" s="6"/>
+      <c r="F160" s="5"/>
       <c r="G160" s="6"/>
       <c r="H160" s="6"/>
-      <c r="I160" s="7"/>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I160" s="6"/>
+      <c r="J160" s="7"/>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="4"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
       <c r="D161" s="5"/>
       <c r="E161" s="5"/>
-      <c r="F161" s="6"/>
+      <c r="F161" s="5"/>
       <c r="G161" s="6"/>
       <c r="H161" s="6"/>
-      <c r="I161" s="7"/>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I161" s="6"/>
+      <c r="J161" s="7"/>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="4"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
       <c r="D162" s="5"/>
       <c r="E162" s="5"/>
-      <c r="F162" s="6"/>
+      <c r="F162" s="5"/>
       <c r="G162" s="6"/>
       <c r="H162" s="6"/>
-      <c r="I162" s="7"/>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I162" s="6"/>
+      <c r="J162" s="7"/>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="4"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
       <c r="D163" s="5"/>
       <c r="E163" s="5"/>
-      <c r="F163" s="6"/>
+      <c r="F163" s="5"/>
       <c r="G163" s="6"/>
       <c r="H163" s="6"/>
-      <c r="I163" s="7"/>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I163" s="6"/>
+      <c r="J163" s="7"/>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="4"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
       <c r="D164" s="5"/>
       <c r="E164" s="5"/>
-      <c r="F164" s="6"/>
+      <c r="F164" s="5"/>
       <c r="G164" s="6"/>
       <c r="H164" s="6"/>
-      <c r="I164" s="7"/>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I164" s="6"/>
+      <c r="J164" s="7"/>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="4"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
       <c r="D165" s="5"/>
       <c r="E165" s="5"/>
-      <c r="F165" s="6"/>
+      <c r="F165" s="5"/>
       <c r="G165" s="6"/>
       <c r="H165" s="6"/>
-      <c r="I165" s="7"/>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I165" s="6"/>
+      <c r="J165" s="7"/>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="4"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
       <c r="D166" s="5"/>
       <c r="E166" s="5"/>
-      <c r="F166" s="6"/>
+      <c r="F166" s="5"/>
       <c r="G166" s="6"/>
       <c r="H166" s="6"/>
-      <c r="I166" s="7"/>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I166" s="6"/>
+      <c r="J166" s="7"/>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="4"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
       <c r="D167" s="5"/>
       <c r="E167" s="5"/>
-      <c r="F167" s="6"/>
+      <c r="F167" s="5"/>
       <c r="G167" s="6"/>
       <c r="H167" s="6"/>
-      <c r="I167" s="7"/>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I167" s="6"/>
+      <c r="J167" s="7"/>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="4"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
       <c r="D168" s="5"/>
       <c r="E168" s="5"/>
-      <c r="F168" s="6"/>
+      <c r="F168" s="5"/>
       <c r="G168" s="6"/>
       <c r="H168" s="6"/>
-      <c r="I168" s="7"/>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I168" s="6"/>
+      <c r="J168" s="7"/>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="4"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
       <c r="D169" s="5"/>
       <c r="E169" s="5"/>
-      <c r="F169" s="6"/>
+      <c r="F169" s="5"/>
       <c r="G169" s="6"/>
       <c r="H169" s="6"/>
-      <c r="I169" s="7"/>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I169" s="6"/>
+      <c r="J169" s="7"/>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="4"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
       <c r="D170" s="5"/>
       <c r="E170" s="5"/>
-      <c r="F170" s="6"/>
+      <c r="F170" s="5"/>
       <c r="G170" s="6"/>
       <c r="H170" s="6"/>
-      <c r="I170" s="7"/>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I170" s="6"/>
+      <c r="J170" s="7"/>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="4"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
       <c r="D171" s="5"/>
       <c r="E171" s="5"/>
-      <c r="F171" s="6"/>
+      <c r="F171" s="5"/>
       <c r="G171" s="6"/>
       <c r="H171" s="6"/>
-      <c r="I171" s="7"/>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I171" s="6"/>
+      <c r="J171" s="7"/>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="4"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
       <c r="D172" s="5"/>
       <c r="E172" s="5"/>
-      <c r="F172" s="6"/>
+      <c r="F172" s="5"/>
       <c r="G172" s="6"/>
       <c r="H172" s="6"/>
-      <c r="I172" s="7"/>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I172" s="6"/>
+      <c r="J172" s="7"/>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="4"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
       <c r="D173" s="5"/>
       <c r="E173" s="5"/>
-      <c r="F173" s="6"/>
+      <c r="F173" s="5"/>
       <c r="G173" s="6"/>
       <c r="H173" s="6"/>
-      <c r="I173" s="7"/>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I173" s="6"/>
+      <c r="J173" s="7"/>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="4"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
       <c r="D174" s="5"/>
       <c r="E174" s="5"/>
-      <c r="F174" s="6"/>
+      <c r="F174" s="5"/>
       <c r="G174" s="6"/>
       <c r="H174" s="6"/>
-      <c r="I174" s="7"/>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I174" s="6"/>
+      <c r="J174" s="7"/>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="4"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
       <c r="D175" s="5"/>
       <c r="E175" s="5"/>
-      <c r="F175" s="6"/>
+      <c r="F175" s="5"/>
       <c r="G175" s="6"/>
       <c r="H175" s="6"/>
-      <c r="I175" s="7"/>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I175" s="6"/>
+      <c r="J175" s="7"/>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="4"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
       <c r="D176" s="5"/>
       <c r="E176" s="5"/>
-      <c r="F176" s="6"/>
+      <c r="F176" s="5"/>
       <c r="G176" s="6"/>
       <c r="H176" s="6"/>
-      <c r="I176" s="7"/>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I176" s="6"/>
+      <c r="J176" s="7"/>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" s="4"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
       <c r="D177" s="5"/>
       <c r="E177" s="5"/>
-      <c r="F177" s="6"/>
+      <c r="F177" s="5"/>
       <c r="G177" s="6"/>
       <c r="H177" s="6"/>
-      <c r="I177" s="7"/>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I177" s="6"/>
+      <c r="J177" s="7"/>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="4"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
       <c r="D178" s="5"/>
       <c r="E178" s="5"/>
-      <c r="F178" s="6"/>
+      <c r="F178" s="5"/>
       <c r="G178" s="6"/>
       <c r="H178" s="6"/>
-      <c r="I178" s="7"/>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I178" s="6"/>
+      <c r="J178" s="7"/>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="4"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
       <c r="D179" s="5"/>
       <c r="E179" s="5"/>
-      <c r="F179" s="6"/>
+      <c r="F179" s="5"/>
       <c r="G179" s="6"/>
       <c r="H179" s="6"/>
-      <c r="I179" s="7"/>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I179" s="6"/>
+      <c r="J179" s="7"/>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="4"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
       <c r="D180" s="5"/>
       <c r="E180" s="5"/>
-      <c r="F180" s="6"/>
+      <c r="F180" s="5"/>
       <c r="G180" s="6"/>
       <c r="H180" s="6"/>
-      <c r="I180" s="7"/>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I180" s="6"/>
+      <c r="J180" s="7"/>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="4"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
       <c r="D181" s="5"/>
       <c r="E181" s="5"/>
-      <c r="F181" s="6"/>
+      <c r="F181" s="5"/>
       <c r="G181" s="6"/>
       <c r="H181" s="6"/>
-      <c r="I181" s="7"/>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I181" s="6"/>
+      <c r="J181" s="7"/>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" s="4"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
       <c r="D182" s="5"/>
       <c r="E182" s="5"/>
-      <c r="F182" s="6"/>
+      <c r="F182" s="5"/>
       <c r="G182" s="6"/>
       <c r="H182" s="6"/>
-      <c r="I182" s="7"/>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I182" s="6"/>
+      <c r="J182" s="7"/>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" s="4"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
       <c r="D183" s="5"/>
       <c r="E183" s="5"/>
-      <c r="F183" s="6"/>
+      <c r="F183" s="5"/>
       <c r="G183" s="6"/>
       <c r="H183" s="6"/>
-      <c r="I183" s="7"/>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I183" s="6"/>
+      <c r="J183" s="7"/>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="4"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
       <c r="D184" s="5"/>
       <c r="E184" s="5"/>
-      <c r="F184" s="6"/>
+      <c r="F184" s="5"/>
       <c r="G184" s="6"/>
       <c r="H184" s="6"/>
-      <c r="I184" s="7"/>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I184" s="6"/>
+      <c r="J184" s="7"/>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" s="4"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
       <c r="D185" s="5"/>
       <c r="E185" s="5"/>
-      <c r="F185" s="6"/>
+      <c r="F185" s="5"/>
       <c r="G185" s="6"/>
       <c r="H185" s="6"/>
-      <c r="I185" s="7"/>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I185" s="6"/>
+      <c r="J185" s="7"/>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" s="4"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
       <c r="D186" s="5"/>
       <c r="E186" s="5"/>
-      <c r="F186" s="6"/>
+      <c r="F186" s="5"/>
       <c r="G186" s="6"/>
       <c r="H186" s="6"/>
-      <c r="I186" s="7"/>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I186" s="6"/>
+      <c r="J186" s="7"/>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" s="4"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
       <c r="D187" s="5"/>
       <c r="E187" s="5"/>
-      <c r="F187" s="6"/>
+      <c r="F187" s="5"/>
       <c r="G187" s="6"/>
       <c r="H187" s="6"/>
-      <c r="I187" s="7"/>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I187" s="6"/>
+      <c r="J187" s="7"/>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="4"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
       <c r="D188" s="5"/>
       <c r="E188" s="5"/>
-      <c r="F188" s="6"/>
+      <c r="F188" s="5"/>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
-      <c r="I188" s="7"/>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I188" s="6"/>
+      <c r="J188" s="7"/>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="4"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
       <c r="D189" s="5"/>
       <c r="E189" s="5"/>
-      <c r="F189" s="6"/>
+      <c r="F189" s="5"/>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
-      <c r="I189" s="7"/>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I189" s="6"/>
+      <c r="J189" s="7"/>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="4"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
       <c r="D190" s="5"/>
       <c r="E190" s="5"/>
-      <c r="F190" s="6"/>
+      <c r="F190" s="5"/>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
-      <c r="I190" s="7"/>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I190" s="6"/>
+      <c r="J190" s="7"/>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="4"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
       <c r="D191" s="5"/>
       <c r="E191" s="5"/>
-      <c r="F191" s="6"/>
+      <c r="F191" s="5"/>
       <c r="G191" s="6"/>
       <c r="H191" s="6"/>
-      <c r="I191" s="7"/>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I191" s="6"/>
+      <c r="J191" s="7"/>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="4"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
       <c r="D192" s="5"/>
       <c r="E192" s="5"/>
-      <c r="F192" s="6"/>
+      <c r="F192" s="5"/>
       <c r="G192" s="6"/>
       <c r="H192" s="6"/>
-      <c r="I192" s="7"/>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I192" s="6"/>
+      <c r="J192" s="7"/>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="4"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
       <c r="D193" s="5"/>
       <c r="E193" s="5"/>
-      <c r="F193" s="6"/>
+      <c r="F193" s="5"/>
       <c r="G193" s="6"/>
       <c r="H193" s="6"/>
-      <c r="I193" s="7"/>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I193" s="6"/>
+      <c r="J193" s="7"/>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="4"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
       <c r="D194" s="5"/>
       <c r="E194" s="5"/>
-      <c r="F194" s="6"/>
+      <c r="F194" s="5"/>
       <c r="G194" s="6"/>
       <c r="H194" s="6"/>
-      <c r="I194" s="7"/>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I194" s="6"/>
+      <c r="J194" s="7"/>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="4"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
       <c r="D195" s="5"/>
       <c r="E195" s="5"/>
-      <c r="F195" s="6"/>
+      <c r="F195" s="5"/>
       <c r="G195" s="6"/>
       <c r="H195" s="6"/>
-      <c r="I195" s="7"/>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I195" s="6"/>
+      <c r="J195" s="7"/>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="4"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
       <c r="D196" s="5"/>
       <c r="E196" s="5"/>
-      <c r="F196" s="6"/>
+      <c r="F196" s="5"/>
       <c r="G196" s="6"/>
       <c r="H196" s="6"/>
-      <c r="I196" s="7"/>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I196" s="6"/>
+      <c r="J196" s="7"/>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="4"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
       <c r="D197" s="5"/>
       <c r="E197" s="5"/>
-      <c r="F197" s="6"/>
+      <c r="F197" s="5"/>
       <c r="G197" s="6"/>
       <c r="H197" s="6"/>
-      <c r="I197" s="7"/>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I197" s="6"/>
+      <c r="J197" s="7"/>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="4"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
       <c r="D198" s="5"/>
       <c r="E198" s="5"/>
-      <c r="F198" s="6"/>
+      <c r="F198" s="5"/>
       <c r="G198" s="6"/>
       <c r="H198" s="6"/>
-      <c r="I198" s="7"/>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I198" s="6"/>
+      <c r="J198" s="7"/>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="4"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
       <c r="D199" s="5"/>
       <c r="E199" s="5"/>
-      <c r="F199" s="6"/>
+      <c r="F199" s="5"/>
       <c r="G199" s="6"/>
       <c r="H199" s="6"/>
-      <c r="I199" s="7"/>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I199" s="6"/>
+      <c r="J199" s="7"/>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="4"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
       <c r="D200" s="5"/>
       <c r="E200" s="5"/>
-      <c r="F200" s="6"/>
+      <c r="F200" s="5"/>
       <c r="G200" s="6"/>
       <c r="H200" s="6"/>
-      <c r="I200" s="7"/>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I200" s="6"/>
+      <c r="J200" s="7"/>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="4"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
       <c r="D201" s="5"/>
       <c r="E201" s="5"/>
-      <c r="F201" s="6"/>
+      <c r="F201" s="5"/>
       <c r="G201" s="6"/>
       <c r="H201" s="6"/>
-      <c r="I201" s="7"/>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I201" s="6"/>
+      <c r="J201" s="7"/>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="4"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
       <c r="D202" s="5"/>
       <c r="E202" s="5"/>
-      <c r="F202" s="6"/>
+      <c r="F202" s="5"/>
       <c r="G202" s="6"/>
       <c r="H202" s="6"/>
-      <c r="I202" s="7"/>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I202" s="6"/>
+      <c r="J202" s="7"/>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="4"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
       <c r="D203" s="5"/>
       <c r="E203" s="5"/>
-      <c r="F203" s="6"/>
+      <c r="F203" s="5"/>
       <c r="G203" s="6"/>
       <c r="H203" s="6"/>
-      <c r="I203" s="7"/>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I203" s="6"/>
+      <c r="J203" s="7"/>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="4"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
       <c r="D204" s="5"/>
       <c r="E204" s="5"/>
-      <c r="F204" s="6"/>
+      <c r="F204" s="5"/>
       <c r="G204" s="6"/>
       <c r="H204" s="6"/>
-      <c r="I204" s="7"/>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I204" s="6"/>
+      <c r="J204" s="7"/>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="4"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
       <c r="D205" s="5"/>
       <c r="E205" s="5"/>
-      <c r="F205" s="6"/>
+      <c r="F205" s="5"/>
       <c r="G205" s="6"/>
       <c r="H205" s="6"/>
-      <c r="I205" s="7"/>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I205" s="6"/>
+      <c r="J205" s="7"/>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="4"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
       <c r="D206" s="5"/>
       <c r="E206" s="5"/>
-      <c r="F206" s="6"/>
+      <c r="F206" s="5"/>
       <c r="G206" s="6"/>
       <c r="H206" s="6"/>
-      <c r="I206" s="7"/>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I206" s="6"/>
+      <c r="J206" s="7"/>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="4"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
       <c r="D207" s="5"/>
       <c r="E207" s="5"/>
-      <c r="F207" s="6"/>
+      <c r="F207" s="5"/>
       <c r="G207" s="6"/>
       <c r="H207" s="6"/>
-      <c r="I207" s="7"/>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I207" s="6"/>
+      <c r="J207" s="7"/>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="4"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
       <c r="D208" s="5"/>
       <c r="E208" s="5"/>
-      <c r="F208" s="6"/>
+      <c r="F208" s="5"/>
       <c r="G208" s="6"/>
       <c r="H208" s="6"/>
-      <c r="I208" s="7"/>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I208" s="6"/>
+      <c r="J208" s="7"/>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="4"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
       <c r="D209" s="5"/>
       <c r="E209" s="5"/>
-      <c r="F209" s="6"/>
+      <c r="F209" s="5"/>
       <c r="G209" s="6"/>
       <c r="H209" s="6"/>
-      <c r="I209" s="7"/>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I209" s="6"/>
+      <c r="J209" s="7"/>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="4"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
       <c r="D210" s="5"/>
       <c r="E210" s="5"/>
-      <c r="F210" s="6"/>
+      <c r="F210" s="5"/>
       <c r="G210" s="6"/>
       <c r="H210" s="6"/>
-      <c r="I210" s="7"/>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I210" s="6"/>
+      <c r="J210" s="7"/>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="4"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
       <c r="D211" s="5"/>
       <c r="E211" s="5"/>
-      <c r="F211" s="6"/>
+      <c r="F211" s="5"/>
       <c r="G211" s="6"/>
       <c r="H211" s="6"/>
-      <c r="I211" s="7"/>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I211" s="6"/>
+      <c r="J211" s="7"/>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="4"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
       <c r="D212" s="5"/>
       <c r="E212" s="5"/>
-      <c r="F212" s="6"/>
+      <c r="F212" s="5"/>
       <c r="G212" s="6"/>
       <c r="H212" s="6"/>
-      <c r="I212" s="7"/>
-    </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I212" s="6"/>
+      <c r="J212" s="7"/>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="4"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
       <c r="D213" s="5"/>
       <c r="E213" s="5"/>
-      <c r="F213" s="6"/>
+      <c r="F213" s="5"/>
       <c r="G213" s="6"/>
       <c r="H213" s="6"/>
-      <c r="I213" s="7"/>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I213" s="6"/>
+      <c r="J213" s="7"/>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="4"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
       <c r="D214" s="5"/>
       <c r="E214" s="5"/>
-      <c r="F214" s="6"/>
+      <c r="F214" s="5"/>
       <c r="G214" s="6"/>
       <c r="H214" s="6"/>
-      <c r="I214" s="7"/>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I214" s="6"/>
+      <c r="J214" s="7"/>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="4"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
       <c r="D215" s="5"/>
       <c r="E215" s="5"/>
-      <c r="F215" s="6"/>
+      <c r="F215" s="5"/>
       <c r="G215" s="6"/>
       <c r="H215" s="6"/>
-      <c r="I215" s="7"/>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I215" s="6"/>
+      <c r="J215" s="7"/>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="4"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
       <c r="D216" s="5"/>
       <c r="E216" s="5"/>
-      <c r="F216" s="6"/>
+      <c r="F216" s="5"/>
       <c r="G216" s="6"/>
       <c r="H216" s="6"/>
-      <c r="I216" s="7"/>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I216" s="6"/>
+      <c r="J216" s="7"/>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="4"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
       <c r="D217" s="5"/>
       <c r="E217" s="5"/>
-      <c r="F217" s="6"/>
+      <c r="F217" s="5"/>
       <c r="G217" s="6"/>
       <c r="H217" s="6"/>
-      <c r="I217" s="7"/>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I217" s="6"/>
+      <c r="J217" s="7"/>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="4"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
       <c r="D218" s="5"/>
       <c r="E218" s="5"/>
-      <c r="F218" s="6"/>
+      <c r="F218" s="5"/>
       <c r="G218" s="6"/>
       <c r="H218" s="6"/>
-      <c r="I218" s="7"/>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I218" s="6"/>
+      <c r="J218" s="7"/>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="4"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
       <c r="D219" s="5"/>
       <c r="E219" s="5"/>
-      <c r="F219" s="6"/>
+      <c r="F219" s="5"/>
       <c r="G219" s="6"/>
       <c r="H219" s="6"/>
-      <c r="I219" s="7"/>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I219" s="6"/>
+      <c r="J219" s="7"/>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="4"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
       <c r="D220" s="5"/>
       <c r="E220" s="5"/>
-      <c r="F220" s="6"/>
+      <c r="F220" s="5"/>
       <c r="G220" s="6"/>
       <c r="H220" s="6"/>
-      <c r="I220" s="7"/>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I220" s="6"/>
+      <c r="J220" s="7"/>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="4"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
       <c r="D221" s="5"/>
       <c r="E221" s="5"/>
-      <c r="F221" s="6"/>
+      <c r="F221" s="5"/>
       <c r="G221" s="6"/>
       <c r="H221" s="6"/>
-      <c r="I221" s="7"/>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I221" s="6"/>
+      <c r="J221" s="7"/>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="4"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
       <c r="D222" s="5"/>
       <c r="E222" s="5"/>
-      <c r="F222" s="6"/>
+      <c r="F222" s="5"/>
       <c r="G222" s="6"/>
       <c r="H222" s="6"/>
-      <c r="I222" s="7"/>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I222" s="6"/>
+      <c r="J222" s="7"/>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="4"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
       <c r="D223" s="5"/>
       <c r="E223" s="5"/>
-      <c r="F223" s="6"/>
+      <c r="F223" s="5"/>
       <c r="G223" s="6"/>
       <c r="H223" s="6"/>
-      <c r="I223" s="7"/>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I223" s="6"/>
+      <c r="J223" s="7"/>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="4"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
       <c r="D224" s="5"/>
       <c r="E224" s="5"/>
-      <c r="F224" s="6"/>
+      <c r="F224" s="5"/>
       <c r="G224" s="6"/>
       <c r="H224" s="6"/>
-      <c r="I224" s="7"/>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I224" s="6"/>
+      <c r="J224" s="7"/>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="4"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
       <c r="D225" s="5"/>
       <c r="E225" s="5"/>
-      <c r="F225" s="6"/>
+      <c r="F225" s="5"/>
       <c r="G225" s="6"/>
       <c r="H225" s="6"/>
-      <c r="I225" s="7"/>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I225" s="6"/>
+      <c r="J225" s="7"/>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="4"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
       <c r="D226" s="5"/>
       <c r="E226" s="5"/>
-      <c r="F226" s="6"/>
+      <c r="F226" s="5"/>
       <c r="G226" s="6"/>
       <c r="H226" s="6"/>
-      <c r="I226" s="7"/>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I226" s="6"/>
+      <c r="J226" s="7"/>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="4"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
       <c r="D227" s="5"/>
       <c r="E227" s="5"/>
-      <c r="F227" s="6"/>
+      <c r="F227" s="5"/>
       <c r="G227" s="6"/>
       <c r="H227" s="6"/>
-      <c r="I227" s="7"/>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I227" s="6"/>
+      <c r="J227" s="7"/>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="4"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
       <c r="D228" s="5"/>
       <c r="E228" s="5"/>
-      <c r="F228" s="6"/>
+      <c r="F228" s="5"/>
       <c r="G228" s="6"/>
       <c r="H228" s="6"/>
-      <c r="I228" s="7"/>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I228" s="6"/>
+      <c r="J228" s="7"/>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="4"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
       <c r="D229" s="5"/>
       <c r="E229" s="5"/>
-      <c r="F229" s="6"/>
+      <c r="F229" s="5"/>
       <c r="G229" s="6"/>
       <c r="H229" s="6"/>
-      <c r="I229" s="7"/>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I229" s="6"/>
+      <c r="J229" s="7"/>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="4"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
       <c r="D230" s="5"/>
       <c r="E230" s="5"/>
-      <c r="F230" s="6"/>
+      <c r="F230" s="5"/>
       <c r="G230" s="6"/>
       <c r="H230" s="6"/>
-      <c r="I230" s="7"/>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I230" s="6"/>
+      <c r="J230" s="7"/>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="4"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
       <c r="D231" s="5"/>
       <c r="E231" s="5"/>
-      <c r="F231" s="6"/>
+      <c r="F231" s="5"/>
       <c r="G231" s="6"/>
       <c r="H231" s="6"/>
-      <c r="I231" s="7"/>
-    </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I231" s="6"/>
+      <c r="J231" s="7"/>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="4"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
       <c r="D232" s="5"/>
       <c r="E232" s="5"/>
-      <c r="F232" s="6"/>
+      <c r="F232" s="5"/>
       <c r="G232" s="6"/>
       <c r="H232" s="6"/>
-      <c r="I232" s="7"/>
-    </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I232" s="6"/>
+      <c r="J232" s="7"/>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="4"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
       <c r="D233" s="5"/>
       <c r="E233" s="5"/>
-      <c r="F233" s="6"/>
+      <c r="F233" s="5"/>
       <c r="G233" s="6"/>
       <c r="H233" s="6"/>
-      <c r="I233" s="7"/>
-    </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I233" s="6"/>
+      <c r="J233" s="7"/>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="4"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
       <c r="D234" s="5"/>
       <c r="E234" s="5"/>
-      <c r="F234" s="6"/>
+      <c r="F234" s="5"/>
       <c r="G234" s="6"/>
       <c r="H234" s="6"/>
-      <c r="I234" s="7"/>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I234" s="6"/>
+      <c r="J234" s="7"/>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="4"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
       <c r="D235" s="5"/>
       <c r="E235" s="5"/>
-      <c r="F235" s="6"/>
+      <c r="F235" s="5"/>
       <c r="G235" s="6"/>
       <c r="H235" s="6"/>
-      <c r="I235" s="7"/>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I235" s="6"/>
+      <c r="J235" s="7"/>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="4"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
       <c r="D236" s="5"/>
       <c r="E236" s="5"/>
-      <c r="F236" s="6"/>
+      <c r="F236" s="5"/>
       <c r="G236" s="6"/>
       <c r="H236" s="6"/>
-      <c r="I236" s="7"/>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I236" s="6"/>
+      <c r="J236" s="7"/>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="4"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
       <c r="D237" s="5"/>
       <c r="E237" s="5"/>
-      <c r="F237" s="6"/>
+      <c r="F237" s="5"/>
       <c r="G237" s="6"/>
       <c r="H237" s="6"/>
-      <c r="I237" s="7"/>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I237" s="6"/>
+      <c r="J237" s="7"/>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="4"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
       <c r="D238" s="5"/>
       <c r="E238" s="5"/>
-      <c r="F238" s="6"/>
+      <c r="F238" s="5"/>
       <c r="G238" s="6"/>
       <c r="H238" s="6"/>
-      <c r="I238" s="7"/>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I238" s="6"/>
+      <c r="J238" s="7"/>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="4"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
       <c r="D239" s="5"/>
       <c r="E239" s="5"/>
-      <c r="F239" s="6"/>
+      <c r="F239" s="5"/>
       <c r="G239" s="6"/>
       <c r="H239" s="6"/>
-      <c r="I239" s="7"/>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I239" s="6"/>
+      <c r="J239" s="7"/>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="4"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
       <c r="D240" s="5"/>
       <c r="E240" s="5"/>
-      <c r="F240" s="6"/>
+      <c r="F240" s="5"/>
       <c r="G240" s="6"/>
       <c r="H240" s="6"/>
-      <c r="I240" s="7"/>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I240" s="6"/>
+      <c r="J240" s="7"/>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="4"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
       <c r="D241" s="5"/>
       <c r="E241" s="5"/>
-      <c r="F241" s="6"/>
+      <c r="F241" s="5"/>
       <c r="G241" s="6"/>
       <c r="H241" s="6"/>
-      <c r="I241" s="7"/>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I241" s="6"/>
+      <c r="J241" s="7"/>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="4"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
       <c r="D242" s="5"/>
       <c r="E242" s="5"/>
-      <c r="F242" s="6"/>
+      <c r="F242" s="5"/>
       <c r="G242" s="6"/>
       <c r="H242" s="6"/>
-      <c r="I242" s="7"/>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I242" s="6"/>
+      <c r="J242" s="7"/>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="4"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
       <c r="D243" s="5"/>
       <c r="E243" s="5"/>
-      <c r="F243" s="6"/>
+      <c r="F243" s="5"/>
       <c r="G243" s="6"/>
       <c r="H243" s="6"/>
-      <c r="I243" s="7"/>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I243" s="6"/>
+      <c r="J243" s="7"/>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="4"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
       <c r="D244" s="5"/>
       <c r="E244" s="5"/>
-      <c r="F244" s="6"/>
+      <c r="F244" s="5"/>
       <c r="G244" s="6"/>
       <c r="H244" s="6"/>
-      <c r="I244" s="7"/>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I244" s="6"/>
+      <c r="J244" s="7"/>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="4"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
       <c r="D245" s="5"/>
       <c r="E245" s="5"/>
-      <c r="F245" s="6"/>
+      <c r="F245" s="5"/>
       <c r="G245" s="6"/>
       <c r="H245" s="6"/>
-      <c r="I245" s="7"/>
-    </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I245" s="6"/>
+      <c r="J245" s="7"/>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="4"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
       <c r="D246" s="5"/>
       <c r="E246" s="5"/>
-      <c r="F246" s="6"/>
+      <c r="F246" s="5"/>
       <c r="G246" s="6"/>
       <c r="H246" s="6"/>
-      <c r="I246" s="7"/>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I246" s="6"/>
+      <c r="J246" s="7"/>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="4"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
       <c r="D247" s="5"/>
       <c r="E247" s="5"/>
-      <c r="F247" s="6"/>
+      <c r="F247" s="5"/>
       <c r="G247" s="6"/>
       <c r="H247" s="6"/>
-      <c r="I247" s="7"/>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I247" s="6"/>
+      <c r="J247" s="7"/>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="4"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
       <c r="D248" s="5"/>
       <c r="E248" s="5"/>
-      <c r="F248" s="6"/>
+      <c r="F248" s="5"/>
       <c r="G248" s="6"/>
       <c r="H248" s="6"/>
-      <c r="I248" s="7"/>
-    </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I248" s="6"/>
+      <c r="J248" s="7"/>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="4"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
       <c r="D249" s="5"/>
       <c r="E249" s="5"/>
-      <c r="F249" s="6"/>
+      <c r="F249" s="5"/>
       <c r="G249" s="6"/>
       <c r="H249" s="6"/>
-      <c r="I249" s="7"/>
-    </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I249" s="6"/>
+      <c r="J249" s="7"/>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="4"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
       <c r="D250" s="5"/>
       <c r="E250" s="5"/>
-      <c r="F250" s="6"/>
+      <c r="F250" s="5"/>
       <c r="G250" s="6"/>
       <c r="H250" s="6"/>
-      <c r="I250" s="7"/>
-    </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I250" s="6"/>
+      <c r="J250" s="7"/>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="4"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
       <c r="D251" s="5"/>
       <c r="E251" s="5"/>
-      <c r="F251" s="6"/>
+      <c r="F251" s="5"/>
       <c r="G251" s="6"/>
       <c r="H251" s="6"/>
-      <c r="I251" s="7"/>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I251" s="6"/>
+      <c r="J251" s="7"/>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="4"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
       <c r="D252" s="5"/>
       <c r="E252" s="5"/>
-      <c r="F252" s="6"/>
+      <c r="F252" s="5"/>
       <c r="G252" s="6"/>
       <c r="H252" s="6"/>
-      <c r="I252" s="7"/>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I252" s="6"/>
+      <c r="J252" s="7"/>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="4"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
       <c r="D253" s="5"/>
       <c r="E253" s="5"/>
-      <c r="F253" s="6"/>
+      <c r="F253" s="5"/>
       <c r="G253" s="6"/>
       <c r="H253" s="6"/>
-      <c r="I253" s="7"/>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I253" s="6"/>
+      <c r="J253" s="7"/>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="4"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
       <c r="D254" s="5"/>
       <c r="E254" s="5"/>
-      <c r="F254" s="6"/>
+      <c r="F254" s="5"/>
       <c r="G254" s="6"/>
       <c r="H254" s="6"/>
-      <c r="I254" s="7"/>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I254" s="6"/>
+      <c r="J254" s="7"/>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="4"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
       <c r="D255" s="5"/>
       <c r="E255" s="5"/>
-      <c r="F255" s="6"/>
+      <c r="F255" s="5"/>
       <c r="G255" s="6"/>
       <c r="H255" s="6"/>
-      <c r="I255" s="7"/>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I255" s="6"/>
+      <c r="J255" s="7"/>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="4"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
       <c r="D256" s="5"/>
       <c r="E256" s="5"/>
-      <c r="F256" s="6"/>
+      <c r="F256" s="5"/>
       <c r="G256" s="6"/>
       <c r="H256" s="6"/>
-      <c r="I256" s="7"/>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I256" s="6"/>
+      <c r="J256" s="7"/>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="4"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
       <c r="D257" s="5"/>
       <c r="E257" s="5"/>
-      <c r="F257" s="6"/>
+      <c r="F257" s="5"/>
       <c r="G257" s="6"/>
       <c r="H257" s="6"/>
-      <c r="I257" s="7"/>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I257" s="6"/>
+      <c r="J257" s="7"/>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="4"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
       <c r="D258" s="5"/>
       <c r="E258" s="5"/>
-      <c r="F258" s="6"/>
+      <c r="F258" s="5"/>
       <c r="G258" s="6"/>
       <c r="H258" s="6"/>
-      <c r="I258" s="7"/>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I258" s="6"/>
+      <c r="J258" s="7"/>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="4"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
       <c r="D259" s="5"/>
       <c r="E259" s="5"/>
-      <c r="F259" s="6"/>
+      <c r="F259" s="5"/>
       <c r="G259" s="6"/>
       <c r="H259" s="6"/>
-      <c r="I259" s="7"/>
-    </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I259" s="6"/>
+      <c r="J259" s="7"/>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" s="4"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
       <c r="D260" s="5"/>
       <c r="E260" s="5"/>
-      <c r="F260" s="6"/>
+      <c r="F260" s="5"/>
       <c r="G260" s="6"/>
       <c r="H260" s="6"/>
-      <c r="I260" s="7"/>
-    </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I260" s="6"/>
+      <c r="J260" s="7"/>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="4"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
       <c r="D261" s="5"/>
       <c r="E261" s="5"/>
-      <c r="F261" s="6"/>
+      <c r="F261" s="5"/>
       <c r="G261" s="6"/>
       <c r="H261" s="6"/>
-      <c r="I261" s="7"/>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I261" s="6"/>
+      <c r="J261" s="7"/>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="4"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
       <c r="D262" s="5"/>
       <c r="E262" s="5"/>
-      <c r="F262" s="6"/>
+      <c r="F262" s="5"/>
       <c r="G262" s="6"/>
       <c r="H262" s="6"/>
-      <c r="I262" s="7"/>
-    </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I262" s="6"/>
+      <c r="J262" s="7"/>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" s="4"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
       <c r="D263" s="5"/>
       <c r="E263" s="5"/>
-      <c r="F263" s="6"/>
+      <c r="F263" s="5"/>
       <c r="G263" s="6"/>
       <c r="H263" s="6"/>
-      <c r="I263" s="7"/>
-    </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I263" s="6"/>
+      <c r="J263" s="7"/>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="4"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
       <c r="D264" s="5"/>
       <c r="E264" s="5"/>
-      <c r="F264" s="6"/>
+      <c r="F264" s="5"/>
       <c r="G264" s="6"/>
       <c r="H264" s="6"/>
-      <c r="I264" s="7"/>
-    </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I264" s="6"/>
+      <c r="J264" s="7"/>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="4"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
       <c r="D265" s="5"/>
       <c r="E265" s="5"/>
-      <c r="F265" s="6"/>
+      <c r="F265" s="5"/>
       <c r="G265" s="6"/>
       <c r="H265" s="6"/>
-      <c r="I265" s="7"/>
-    </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I265" s="6"/>
+      <c r="J265" s="7"/>
+    </row>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="4"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
       <c r="D266" s="5"/>
       <c r="E266" s="5"/>
-      <c r="F266" s="6"/>
+      <c r="F266" s="5"/>
       <c r="G266" s="6"/>
       <c r="H266" s="6"/>
-      <c r="I266" s="7"/>
-    </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I266" s="6"/>
+      <c r="J266" s="7"/>
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="4"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
       <c r="D267" s="5"/>
       <c r="E267" s="5"/>
-      <c r="F267" s="6"/>
+      <c r="F267" s="5"/>
       <c r="G267" s="6"/>
       <c r="H267" s="6"/>
-      <c r="I267" s="7"/>
-    </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I267" s="6"/>
+      <c r="J267" s="7"/>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="4"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
       <c r="D268" s="5"/>
       <c r="E268" s="5"/>
-      <c r="F268" s="6"/>
+      <c r="F268" s="5"/>
       <c r="G268" s="6"/>
       <c r="H268" s="6"/>
-      <c r="I268" s="7"/>
-    </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I268" s="6"/>
+      <c r="J268" s="7"/>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="4"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
       <c r="D269" s="5"/>
       <c r="E269" s="5"/>
-      <c r="F269" s="6"/>
+      <c r="F269" s="5"/>
       <c r="G269" s="6"/>
       <c r="H269" s="6"/>
-      <c r="I269" s="7"/>
-    </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I269" s="6"/>
+      <c r="J269" s="7"/>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="4"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
       <c r="D270" s="5"/>
       <c r="E270" s="5"/>
-      <c r="F270" s="6"/>
+      <c r="F270" s="5"/>
       <c r="G270" s="6"/>
       <c r="H270" s="6"/>
-      <c r="I270" s="7"/>
-    </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I270" s="6"/>
+      <c r="J270" s="7"/>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="4"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
       <c r="D271" s="5"/>
       <c r="E271" s="5"/>
-      <c r="F271" s="6"/>
+      <c r="F271" s="5"/>
       <c r="G271" s="6"/>
       <c r="H271" s="6"/>
-      <c r="I271" s="7"/>
-    </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I271" s="6"/>
+      <c r="J271" s="7"/>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="4"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
       <c r="D272" s="5"/>
       <c r="E272" s="5"/>
-      <c r="F272" s="6"/>
+      <c r="F272" s="5"/>
       <c r="G272" s="6"/>
       <c r="H272" s="6"/>
-      <c r="I272" s="7"/>
-    </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I272" s="6"/>
+      <c r="J272" s="7"/>
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="4"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
       <c r="D273" s="5"/>
       <c r="E273" s="5"/>
-      <c r="F273" s="6"/>
+      <c r="F273" s="5"/>
       <c r="G273" s="6"/>
       <c r="H273" s="6"/>
-      <c r="I273" s="7"/>
-    </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I273" s="6"/>
+      <c r="J273" s="7"/>
+    </row>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="4"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
       <c r="D274" s="5"/>
       <c r="E274" s="5"/>
-      <c r="F274" s="6"/>
+      <c r="F274" s="5"/>
       <c r="G274" s="6"/>
       <c r="H274" s="6"/>
-      <c r="I274" s="7"/>
-    </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I274" s="6"/>
+      <c r="J274" s="7"/>
+    </row>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="4"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
       <c r="D275" s="5"/>
       <c r="E275" s="5"/>
-      <c r="F275" s="6"/>
+      <c r="F275" s="5"/>
       <c r="G275" s="6"/>
       <c r="H275" s="6"/>
-      <c r="I275" s="7"/>
-    </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I275" s="6"/>
+      <c r="J275" s="7"/>
+    </row>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="4"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
       <c r="D276" s="5"/>
       <c r="E276" s="5"/>
-      <c r="F276" s="6"/>
+      <c r="F276" s="5"/>
       <c r="G276" s="6"/>
       <c r="H276" s="6"/>
-      <c r="I276" s="7"/>
-    </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I276" s="6"/>
+      <c r="J276" s="7"/>
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="4"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
       <c r="D277" s="5"/>
       <c r="E277" s="5"/>
-      <c r="F277" s="6"/>
+      <c r="F277" s="5"/>
       <c r="G277" s="6"/>
       <c r="H277" s="6"/>
-      <c r="I277" s="7"/>
-    </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I277" s="6"/>
+      <c r="J277" s="7"/>
+    </row>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="4"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
       <c r="D278" s="5"/>
       <c r="E278" s="5"/>
-      <c r="F278" s="6"/>
+      <c r="F278" s="5"/>
       <c r="G278" s="6"/>
       <c r="H278" s="6"/>
-      <c r="I278" s="7"/>
-    </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I278" s="6"/>
+      <c r="J278" s="7"/>
+    </row>
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="4"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
       <c r="D279" s="5"/>
       <c r="E279" s="5"/>
-      <c r="F279" s="6"/>
+      <c r="F279" s="5"/>
       <c r="G279" s="6"/>
       <c r="H279" s="6"/>
-      <c r="I279" s="7"/>
-    </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I279" s="6"/>
+      <c r="J279" s="7"/>
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="4"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
       <c r="D280" s="5"/>
       <c r="E280" s="5"/>
-      <c r="F280" s="6"/>
+      <c r="F280" s="5"/>
       <c r="G280" s="6"/>
       <c r="H280" s="6"/>
-      <c r="I280" s="7"/>
-    </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I280" s="6"/>
+      <c r="J280" s="7"/>
+    </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="4"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
       <c r="D281" s="5"/>
       <c r="E281" s="5"/>
-      <c r="F281" s="6"/>
+      <c r="F281" s="5"/>
       <c r="G281" s="6"/>
       <c r="H281" s="6"/>
-      <c r="I281" s="7"/>
-    </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I281" s="6"/>
+      <c r="J281" s="7"/>
+    </row>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="4"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
       <c r="D282" s="5"/>
       <c r="E282" s="5"/>
-      <c r="F282" s="6"/>
+      <c r="F282" s="5"/>
       <c r="G282" s="6"/>
       <c r="H282" s="6"/>
-      <c r="I282" s="7"/>
-    </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I282" s="6"/>
+      <c r="J282" s="7"/>
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="4"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
       <c r="D283" s="5"/>
       <c r="E283" s="5"/>
-      <c r="F283" s="6"/>
+      <c r="F283" s="5"/>
       <c r="G283" s="6"/>
       <c r="H283" s="6"/>
-      <c r="I283" s="7"/>
-    </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I283" s="6"/>
+      <c r="J283" s="7"/>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="4"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
       <c r="D284" s="5"/>
       <c r="E284" s="5"/>
-      <c r="F284" s="6"/>
+      <c r="F284" s="5"/>
       <c r="G284" s="6"/>
       <c r="H284" s="6"/>
-      <c r="I284" s="7"/>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I284" s="6"/>
+      <c r="J284" s="7"/>
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="4"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
       <c r="D285" s="5"/>
       <c r="E285" s="5"/>
-      <c r="F285" s="6"/>
+      <c r="F285" s="5"/>
       <c r="G285" s="6"/>
       <c r="H285" s="6"/>
-      <c r="I285" s="7"/>
-    </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I285" s="6"/>
+      <c r="J285" s="7"/>
+    </row>
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="4"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
       <c r="D286" s="5"/>
       <c r="E286" s="5"/>
-      <c r="F286" s="6"/>
+      <c r="F286" s="5"/>
       <c r="G286" s="6"/>
       <c r="H286" s="6"/>
-      <c r="I286" s="7"/>
-    </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I286" s="6"/>
+      <c r="J286" s="7"/>
+    </row>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="4"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
       <c r="D287" s="5"/>
       <c r="E287" s="5"/>
-      <c r="F287" s="6"/>
+      <c r="F287" s="5"/>
       <c r="G287" s="6"/>
       <c r="H287" s="6"/>
-      <c r="I287" s="7"/>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I287" s="6"/>
+      <c r="J287" s="7"/>
+    </row>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="4"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
       <c r="D288" s="5"/>
       <c r="E288" s="5"/>
-      <c r="F288" s="6"/>
+      <c r="F288" s="5"/>
       <c r="G288" s="6"/>
       <c r="H288" s="6"/>
-      <c r="I288" s="7"/>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I288" s="6"/>
+      <c r="J288" s="7"/>
+    </row>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="4"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
       <c r="D289" s="5"/>
       <c r="E289" s="5"/>
-      <c r="F289" s="6"/>
+      <c r="F289" s="5"/>
       <c r="G289" s="6"/>
       <c r="H289" s="6"/>
-      <c r="I289" s="7"/>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I289" s="6"/>
+      <c r="J289" s="7"/>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="4"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
       <c r="D290" s="5"/>
       <c r="E290" s="5"/>
-      <c r="F290" s="6"/>
+      <c r="F290" s="5"/>
       <c r="G290" s="6"/>
       <c r="H290" s="6"/>
-      <c r="I290" s="7"/>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I290" s="6"/>
+      <c r="J290" s="7"/>
+    </row>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="4"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
       <c r="D291" s="5"/>
       <c r="E291" s="5"/>
-      <c r="F291" s="6"/>
+      <c r="F291" s="5"/>
       <c r="G291" s="6"/>
       <c r="H291" s="6"/>
-      <c r="I291" s="7"/>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I291" s="6"/>
+      <c r="J291" s="7"/>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="4"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
       <c r="D292" s="5"/>
       <c r="E292" s="5"/>
-      <c r="F292" s="6"/>
+      <c r="F292" s="5"/>
       <c r="G292" s="6"/>
       <c r="H292" s="6"/>
-      <c r="I292" s="7"/>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I292" s="6"/>
+      <c r="J292" s="7"/>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="4"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
       <c r="D293" s="5"/>
       <c r="E293" s="5"/>
-      <c r="F293" s="6"/>
+      <c r="F293" s="5"/>
       <c r="G293" s="6"/>
       <c r="H293" s="6"/>
-      <c r="I293" s="7"/>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I293" s="6"/>
+      <c r="J293" s="7"/>
+    </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="4"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
       <c r="D294" s="5"/>
       <c r="E294" s="5"/>
-      <c r="F294" s="6"/>
+      <c r="F294" s="5"/>
       <c r="G294" s="6"/>
       <c r="H294" s="6"/>
-      <c r="I294" s="7"/>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I294" s="6"/>
+      <c r="J294" s="7"/>
+    </row>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="4"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
       <c r="D295" s="5"/>
       <c r="E295" s="5"/>
-      <c r="F295" s="6"/>
+      <c r="F295" s="5"/>
       <c r="G295" s="6"/>
       <c r="H295" s="6"/>
-      <c r="I295" s="7"/>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I295" s="6"/>
+      <c r="J295" s="7"/>
+    </row>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="4"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
       <c r="D296" s="5"/>
       <c r="E296" s="5"/>
-      <c r="F296" s="6"/>
+      <c r="F296" s="5"/>
       <c r="G296" s="6"/>
       <c r="H296" s="6"/>
-      <c r="I296" s="7"/>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I296" s="6"/>
+      <c r="J296" s="7"/>
+    </row>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="8"/>
       <c r="B297" s="9"/>
       <c r="C297" s="9"/>
       <c r="D297" s="9"/>
       <c r="E297" s="9"/>
-      <c r="F297" s="10"/>
+      <c r="F297" s="9"/>
       <c r="G297" s="10"/>
       <c r="H297" s="10"/>
-      <c r="I297" s="11"/>
+      <c r="I297" s="10"/>
+      <c r="J297" s="11"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="K2:K18"/>
+    <mergeCell ref="K31:K36"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/SantanderCS/results/ResultListByTestModel_Final.xlsx
+++ b/SantanderCS/results/ResultListByTestModel_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\big20\git\big20-ML-project2-team3\SantanderCS\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6800FD6F-82B2-4F01-9298-AC5B22893C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32511A3E-67E0-4413-A763-77FBB6E1BD1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="345" windowWidth="29100" windowHeight="14190" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
+    <workbookView xWindow="0" yWindow="345" windowWidth="28800" windowHeight="14190" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -391,7 +391,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="157">
   <si>
     <t>NO</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1384,12 +1384,25 @@
     <t>models\LogisticRegression_99per_corrTh95_UnderSampling5_BestOpt.pkl</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Best Hyperparameters: {
+    'colsample_bytree': np.float64(0.7010), 
+    'gamma': np.float64(8.0444), 
+    'learning_rate': np.float64(0.0102), 
+    'max_depth': np.float64(5.0), 
+    'min_child_weight': np.float64(8.0), 
+    'n_estimators': np.float64(450.0), 
+    'reg_alpha': np.float64(0.0002), 
+    'reg_lambda': np.float64(2.3460), 
+    'scale_pos_weight': np.float64(5.0), 
+    'subsample': np.float64(0.6896)}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1494,8 +1507,16 @@
       <charset val="129"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1529,6 +1550,11 @@
       <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1705,15 +1731,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1822,117 +1851,136 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="7" borderId="6" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="보통" xfId="1" builtinId="28"/>
+    <cellStyle name="좋음" xfId="2" builtinId="26"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2327,7 +2375,7 @@
       <c r="J2" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="67" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2362,7 +2410,7 @@
       <c r="J3" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="36"/>
+      <c r="K3" s="68"/>
     </row>
     <row r="4" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
@@ -2395,7 +2443,7 @@
       <c r="J4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="36"/>
+      <c r="K4" s="68"/>
     </row>
     <row r="5" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
@@ -2428,7 +2476,7 @@
       <c r="J5" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="36"/>
+      <c r="K5" s="68"/>
     </row>
     <row r="6" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
@@ -2461,7 +2509,7 @@
       <c r="J6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="36"/>
+      <c r="K6" s="68"/>
     </row>
     <row r="7" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
@@ -2494,7 +2542,7 @@
       <c r="J7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="36"/>
+      <c r="K7" s="68"/>
     </row>
     <row r="8" spans="1:11" ht="66" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
@@ -2527,7 +2575,7 @@
       <c r="J8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K8" s="36"/>
+      <c r="K8" s="68"/>
     </row>
     <row r="9" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
@@ -2560,7 +2608,7 @@
       <c r="J9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="K9" s="36"/>
+      <c r="K9" s="68"/>
     </row>
     <row r="10" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
@@ -2593,7 +2641,7 @@
       <c r="J10" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="K10" s="36"/>
+      <c r="K10" s="68"/>
     </row>
     <row r="11" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
@@ -2626,7 +2674,7 @@
       <c r="J11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="K11" s="36"/>
+      <c r="K11" s="68"/>
     </row>
     <row r="12" spans="1:11" ht="66" x14ac:dyDescent="0.3">
       <c r="A12" s="12">
@@ -2659,7 +2707,7 @@
       <c r="J12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K12" s="36"/>
+      <c r="K12" s="68"/>
     </row>
     <row r="13" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
@@ -2692,7 +2740,7 @@
       <c r="J13" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="K13" s="36"/>
+      <c r="K13" s="68"/>
     </row>
     <row r="14" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A14" s="12">
@@ -2725,7 +2773,7 @@
       <c r="J14" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="K14" s="36"/>
+      <c r="K14" s="68"/>
     </row>
     <row r="15" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
@@ -2756,7 +2804,7 @@
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="J15" s="7"/>
-      <c r="K15" s="36"/>
+      <c r="K15" s="68"/>
     </row>
     <row r="16" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A16" s="12">
@@ -2789,7 +2837,7 @@
       <c r="J16" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="K16" s="36"/>
+      <c r="K16" s="68"/>
     </row>
     <row r="17" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
@@ -2816,7 +2864,7 @@
       <c r="J17" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="K17" s="36"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A18" s="12">
@@ -2843,7 +2891,7 @@
       <c r="J18" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="K18" s="36"/>
+      <c r="K18" s="68"/>
     </row>
     <row r="19" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
@@ -2864,7 +2912,7 @@
       <c r="F19" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="38">
+      <c r="G19" s="36">
         <v>0.83560000000000001</v>
       </c>
       <c r="H19" s="13">
@@ -2899,7 +2947,7 @@
       <c r="F20" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="G20" s="38">
+      <c r="G20" s="36">
         <v>0.82150000000000001</v>
       </c>
       <c r="H20" s="13">
@@ -2931,7 +2979,7 @@
       <c r="F21" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="38">
+      <c r="G21" s="36">
         <v>0.81240000000000001</v>
       </c>
       <c r="H21" s="13">
@@ -2963,7 +3011,7 @@
       <c r="F22" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="G22" s="38">
+      <c r="G22" s="36">
         <v>0.85089999999999999</v>
       </c>
       <c r="H22" s="13">
@@ -2995,7 +3043,7 @@
       <c r="F23" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G23" s="38">
+      <c r="G23" s="36">
         <v>0.85089999999999999</v>
       </c>
       <c r="H23" s="13">
@@ -3027,7 +3075,7 @@
       <c r="F24" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="G24" s="38">
+      <c r="G24" s="36">
         <v>0.85050000000000003</v>
       </c>
       <c r="H24" s="13">
@@ -3059,7 +3107,7 @@
       <c r="F25" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G25" s="38">
+      <c r="G25" s="36">
         <v>0.84370000000000001</v>
       </c>
       <c r="H25" s="13">
@@ -3091,7 +3139,7 @@
       <c r="F26" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="G26" s="38">
+      <c r="G26" s="36">
         <v>0.84370000000000001</v>
       </c>
       <c r="H26" s="13">
@@ -3123,7 +3171,7 @@
       <c r="F27" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G27" s="38">
+      <c r="G27" s="36">
         <v>0.84370000000000001</v>
       </c>
       <c r="H27" s="13">
@@ -3155,7 +3203,7 @@
       <c r="F28" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G28" s="38">
+      <c r="G28" s="36">
         <v>0.84370000000000001</v>
       </c>
       <c r="H28" s="13">
@@ -3187,7 +3235,7 @@
       <c r="F29" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G29" s="38">
+      <c r="G29" s="36">
         <v>0.84370000000000001</v>
       </c>
       <c r="H29" s="13">
@@ -3219,7 +3267,7 @@
       <c r="F30" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G30" s="38">
+      <c r="G30" s="36">
         <v>0.84370000000000001</v>
       </c>
       <c r="H30" s="13">
@@ -3236,7 +3284,7 @@
       <c r="A31" s="4">
         <v>30</v>
       </c>
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="37" t="s">
         <v>72</v>
       </c>
       <c r="C31" s="6">
@@ -3245,25 +3293,25 @@
       <c r="D31" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="E31" s="39" t="s">
+      <c r="E31" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="F31" s="40" t="s">
+      <c r="F31" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="G31" s="41">
+      <c r="G31" s="39">
         <v>0.84</v>
       </c>
-      <c r="H31" s="39" t="s">
+      <c r="H31" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="I31" s="39" t="s">
+      <c r="I31" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="J31" s="42" t="s">
+      <c r="J31" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="K31" s="43" t="s">
+      <c r="K31" s="69" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3271,7 +3319,7 @@
       <c r="A32" s="12">
         <v>31</v>
       </c>
-      <c r="B32" s="44" t="s">
+      <c r="B32" s="41" t="s">
         <v>72</v>
       </c>
       <c r="C32" s="6">
@@ -3280,31 +3328,31 @@
       <c r="D32" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="E32" s="44" t="s">
+      <c r="E32" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="F32" s="45" t="s">
+      <c r="F32" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="G32" s="48">
+      <c r="G32" s="44">
         <v>0.84379999999999999</v>
       </c>
-      <c r="H32" s="44">
+      <c r="H32" s="41">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="I32" s="44">
+      <c r="I32" s="41">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J32" s="46" t="s">
+      <c r="J32" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="K32" s="47"/>
+      <c r="K32" s="70"/>
     </row>
     <row r="33" spans="1:11" ht="132" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
-      <c r="B33" s="44" t="s">
+      <c r="B33" s="41" t="s">
         <v>87</v>
       </c>
       <c r="C33" s="6">
@@ -3313,31 +3361,31 @@
       <c r="D33" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="E33" s="44" t="s">
+      <c r="E33" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="45" t="s">
+      <c r="F33" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="G33" s="44">
+      <c r="G33" s="41">
         <v>0.80510000000000004</v>
       </c>
-      <c r="H33" s="44">
+      <c r="H33" s="41">
         <v>1.29E-2</v>
       </c>
-      <c r="I33" s="44">
+      <c r="I33" s="41">
         <v>6.6E-3</v>
       </c>
-      <c r="J33" s="46" t="s">
+      <c r="J33" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="K33" s="47"/>
+      <c r="K33" s="70"/>
     </row>
     <row r="34" spans="1:11" ht="99" x14ac:dyDescent="0.3">
       <c r="A34" s="12">
         <v>33</v>
       </c>
-      <c r="B34" s="44" t="s">
+      <c r="B34" s="41" t="s">
         <v>65</v>
       </c>
       <c r="C34" s="6">
@@ -3346,31 +3394,31 @@
       <c r="D34" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="E34" s="44" t="s">
+      <c r="E34" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="F34" s="45" t="s">
+      <c r="F34" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="G34" s="48">
+      <c r="G34" s="44">
         <v>0.84209999999999996</v>
       </c>
-      <c r="H34" s="44">
+      <c r="H34" s="41">
         <v>1.6299999999999999E-2</v>
       </c>
-      <c r="I34" s="44">
+      <c r="I34" s="41">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="J34" s="46" t="s">
+      <c r="J34" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="K34" s="47"/>
+      <c r="K34" s="70"/>
     </row>
     <row r="35" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
-      <c r="B35" s="44" t="s">
+      <c r="B35" s="41" t="s">
         <v>65</v>
       </c>
       <c r="C35" s="6">
@@ -3379,31 +3427,31 @@
       <c r="D35" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="E35" s="44" t="s">
+      <c r="E35" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="F35" s="45" t="s">
+      <c r="F35" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="G35" s="44">
+      <c r="G35" s="41">
         <v>0.83240000000000003</v>
       </c>
-      <c r="H35" s="44">
+      <c r="H35" s="41">
         <v>2.2499999999999999E-2</v>
       </c>
-      <c r="I35" s="44">
+      <c r="I35" s="41">
         <v>1.1599999999999999E-2</v>
       </c>
-      <c r="J35" s="46" t="s">
+      <c r="J35" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="K35" s="47"/>
+      <c r="K35" s="70"/>
     </row>
     <row r="36" spans="1:11" ht="66" x14ac:dyDescent="0.3">
       <c r="A36" s="12">
         <v>35</v>
       </c>
-      <c r="B36" s="44" t="s">
+      <c r="B36" s="41" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="6">
@@ -3412,55 +3460,55 @@
       <c r="D36" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="E36" s="44" t="s">
+      <c r="E36" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="F36" s="45" t="s">
+      <c r="F36" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="G36" s="44">
+      <c r="G36" s="41">
         <v>0.83620000000000005</v>
       </c>
-      <c r="H36" s="44">
+      <c r="H36" s="41">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="I36" s="44">
+      <c r="I36" s="41">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J36" s="46" t="s">
+      <c r="J36" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="K36" s="47"/>
+      <c r="K36" s="70"/>
     </row>
     <row r="37" spans="1:11" ht="132" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="72">
         <v>0.2</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="E37" s="29" t="s">
+      <c r="E37" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="F37" s="49" t="s">
+      <c r="F37" s="75" t="s">
         <v>97</v>
       </c>
-      <c r="G37" s="50">
+      <c r="G37" s="72">
         <v>0.93</v>
       </c>
-      <c r="H37" s="50">
+      <c r="H37" s="72">
         <v>0.29330000000000001</v>
       </c>
-      <c r="I37" s="50">
+      <c r="I37" s="72">
         <v>0.88529999999999998</v>
       </c>
-      <c r="J37" s="51" t="s">
+      <c r="J37" s="76" t="s">
         <v>98</v>
       </c>
     </row>
@@ -3468,31 +3516,31 @@
       <c r="A38" s="12">
         <v>37</v>
       </c>
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="72">
         <v>0.2</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="E38" s="29" t="s">
+      <c r="E38" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="F38" s="49" t="s">
+      <c r="F38" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="G38" s="6">
+      <c r="G38" s="72">
         <v>0.91149999999999998</v>
       </c>
-      <c r="H38" s="6">
+      <c r="H38" s="72">
         <v>0.2797</v>
       </c>
-      <c r="I38" s="5">
+      <c r="I38" s="73">
         <v>0.85570000000000002</v>
       </c>
-      <c r="J38" s="51" t="s">
+      <c r="J38" s="76" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3515,16 +3563,16 @@
       <c r="F39" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="G39" s="50">
+      <c r="G39" s="46">
         <v>0.84570000000000001</v>
       </c>
-      <c r="H39" s="50">
+      <c r="H39" s="46">
         <v>1.5299999999999999E-2</v>
       </c>
-      <c r="I39" s="50">
+      <c r="I39" s="46">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="J39" s="52" t="s">
+      <c r="J39" s="47" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3532,31 +3580,31 @@
       <c r="A40" s="12">
         <v>39</v>
       </c>
-      <c r="B40" s="53" t="s">
+      <c r="B40" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="C40" s="54">
+      <c r="C40" s="49">
         <v>0.2</v>
       </c>
-      <c r="D40" s="55" t="s">
+      <c r="D40" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="E40" s="56" t="s">
+      <c r="E40" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="F40" s="57" t="s">
+      <c r="F40" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G40" s="58">
+      <c r="G40" s="53">
         <v>0.84520600000000001</v>
       </c>
-      <c r="H40" s="58">
+      <c r="H40" s="53">
         <v>0.287053</v>
       </c>
-      <c r="I40" s="59">
+      <c r="I40" s="54">
         <v>0.55980099999999999</v>
       </c>
-      <c r="J40" s="60" t="s">
+      <c r="J40" s="55" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3576,7 +3624,7 @@
       <c r="E41" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="F41" s="49" t="s">
+      <c r="F41" s="45" t="s">
         <v>102</v>
       </c>
       <c r="G41" s="6">
@@ -3588,7 +3636,7 @@
       <c r="I41" s="5">
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="J41" s="61" t="s">
+      <c r="J41" s="56" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3608,7 +3656,7 @@
       <c r="E42" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="F42" s="49" t="s">
+      <c r="F42" s="45" t="s">
         <v>109</v>
       </c>
       <c r="G42" s="6">
@@ -3620,7 +3668,7 @@
       <c r="I42" s="5">
         <v>0.37040000000000001</v>
       </c>
-      <c r="J42" s="61" t="s">
+      <c r="J42" s="56" t="s">
         <v>110</v>
       </c>
     </row>
@@ -3640,7 +3688,7 @@
       <c r="E43" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F43" s="49" t="s">
+      <c r="F43" s="45" t="s">
         <v>111</v>
       </c>
       <c r="G43" s="6">
@@ -3652,7 +3700,7 @@
       <c r="I43" s="5">
         <v>0.362126</v>
       </c>
-      <c r="J43" s="61" t="s">
+      <c r="J43" s="56" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3684,7 +3732,7 @@
       <c r="I44" s="6">
         <v>2.6578000000000001E-2</v>
       </c>
-      <c r="J44" s="52" t="s">
+      <c r="J44" s="47" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3704,7 +3752,7 @@
       <c r="E45" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="F45" s="49" t="s">
+      <c r="F45" s="45" t="s">
         <v>115</v>
       </c>
       <c r="G45" s="6">
@@ -3716,7 +3764,7 @@
       <c r="I45" s="5">
         <v>0.64119999999999999</v>
       </c>
-      <c r="J45" s="61" t="s">
+      <c r="J45" s="56" t="s">
         <v>116</v>
       </c>
     </row>
@@ -3736,7 +3784,7 @@
       <c r="E46" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="F46" s="49" t="s">
+      <c r="F46" s="45" t="s">
         <v>115</v>
       </c>
       <c r="G46" s="6">
@@ -3748,7 +3796,7 @@
       <c r="I46" s="5">
         <v>0.54149999999999998</v>
       </c>
-      <c r="J46" s="61" t="s">
+      <c r="J46" s="56" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3768,7 +3816,7 @@
       <c r="E47" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="F47" s="49" t="s">
+      <c r="F47" s="45" t="s">
         <v>115</v>
       </c>
       <c r="G47" s="1">
@@ -3780,7 +3828,7 @@
       <c r="I47" s="2">
         <v>0.42520000000000002</v>
       </c>
-      <c r="J47" s="62" t="s">
+      <c r="J47" s="57" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3800,13 +3848,13 @@
       <c r="E48" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="F48" s="49" t="s">
+      <c r="F48" s="45" t="s">
         <v>119</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
       <c r="I48" s="5"/>
-      <c r="J48" s="63" t="s">
+      <c r="J48" s="58" t="s">
         <v>120</v>
       </c>
     </row>
@@ -3826,13 +3874,13 @@
       <c r="E49" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F49" s="49" t="s">
+      <c r="F49" s="45" t="s">
         <v>119</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
       <c r="I49" s="5"/>
-      <c r="J49" s="63" t="s">
+      <c r="J49" s="58" t="s">
         <v>121</v>
       </c>
     </row>
@@ -3852,13 +3900,13 @@
       <c r="E50" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F50" s="49" t="s">
+      <c r="F50" s="45" t="s">
         <v>119</v>
       </c>
       <c r="G50" s="20"/>
       <c r="H50" s="20"/>
       <c r="I50" s="5"/>
-      <c r="J50" s="63" t="s">
+      <c r="J50" s="58" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3866,31 +3914,31 @@
       <c r="A51" s="12">
         <v>50</v>
       </c>
-      <c r="B51" s="64" t="s">
+      <c r="B51" s="59" t="s">
         <v>65</v>
       </c>
       <c r="C51" s="6">
         <v>0.2</v>
       </c>
-      <c r="D51" s="64">
+      <c r="D51" s="59">
         <v>86</v>
       </c>
-      <c r="E51" s="64" t="s">
+      <c r="E51" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="F51" s="65" t="s">
+      <c r="F51" s="60" t="s">
         <v>124</v>
       </c>
-      <c r="G51" s="66">
+      <c r="G51" s="61">
         <v>0.84209999999999996</v>
       </c>
-      <c r="H51" s="64">
+      <c r="H51" s="59">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="I51" s="64">
+      <c r="I51" s="59">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J51" s="67" t="s">
+      <c r="J51" s="62" t="s">
         <v>125</v>
       </c>
     </row>
@@ -3898,31 +3946,31 @@
       <c r="A52" s="4">
         <v>51</v>
       </c>
-      <c r="B52" s="68" t="s">
+      <c r="B52" s="63" t="s">
         <v>126</v>
       </c>
       <c r="C52" s="6">
         <v>0.2</v>
       </c>
-      <c r="D52" s="68">
+      <c r="D52" s="63">
         <v>86</v>
       </c>
-      <c r="E52" s="64" t="s">
+      <c r="E52" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="F52" s="69" t="s">
+      <c r="F52" s="64" t="s">
         <v>127</v>
       </c>
-      <c r="G52" s="68">
+      <c r="G52" s="63">
         <v>0.62160000000000004</v>
       </c>
-      <c r="H52" s="68">
+      <c r="H52" s="63">
         <v>0</v>
       </c>
-      <c r="I52" s="68">
+      <c r="I52" s="63">
         <v>0</v>
       </c>
-      <c r="J52" s="70" t="s">
+      <c r="J52" s="65" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3930,31 +3978,31 @@
       <c r="A53" s="12">
         <v>52</v>
       </c>
-      <c r="B53" s="64" t="s">
+      <c r="B53" s="59" t="s">
         <v>65</v>
       </c>
       <c r="C53" s="6">
         <v>0.2</v>
       </c>
-      <c r="D53" s="64">
+      <c r="D53" s="59">
         <v>86</v>
       </c>
-      <c r="E53" s="64" t="s">
+      <c r="E53" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="F53" s="69" t="s">
+      <c r="F53" s="64" t="s">
         <v>129</v>
       </c>
-      <c r="G53" s="68">
+      <c r="G53" s="63">
         <v>0.8528</v>
       </c>
-      <c r="H53" s="68">
+      <c r="H53" s="63">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="I53" s="68">
+      <c r="I53" s="63">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J53" s="70" t="s">
+      <c r="J53" s="65" t="s">
         <v>130</v>
       </c>
     </row>
@@ -3962,31 +4010,31 @@
       <c r="A54" s="12">
         <v>53</v>
       </c>
-      <c r="B54" s="68" t="s">
+      <c r="B54" s="63" t="s">
         <v>126</v>
       </c>
       <c r="C54" s="6">
         <v>0.2</v>
       </c>
-      <c r="D54" s="68">
+      <c r="D54" s="63">
         <v>86</v>
       </c>
-      <c r="E54" s="64" t="s">
+      <c r="E54" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="F54" s="69" t="s">
+      <c r="F54" s="64" t="s">
         <v>131</v>
       </c>
-      <c r="G54" s="68">
+      <c r="G54" s="63">
         <v>0.60240000000000005</v>
       </c>
-      <c r="H54" s="68">
+      <c r="H54" s="63">
         <v>0</v>
       </c>
-      <c r="I54" s="68">
+      <c r="I54" s="63">
         <v>0</v>
       </c>
-      <c r="J54" s="70" t="s">
+      <c r="J54" s="65" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3994,31 +4042,31 @@
       <c r="A55" s="4">
         <v>54</v>
       </c>
-      <c r="B55" s="64" t="s">
+      <c r="B55" s="59" t="s">
         <v>65</v>
       </c>
       <c r="C55" s="6">
         <v>0.2</v>
       </c>
-      <c r="D55" s="68">
+      <c r="D55" s="63">
         <v>149</v>
       </c>
-      <c r="E55" s="64" t="s">
+      <c r="E55" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="F55" s="69" t="s">
+      <c r="F55" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="G55" s="68">
+      <c r="G55" s="63">
         <v>0.8417</v>
       </c>
-      <c r="H55" s="68">
+      <c r="H55" s="63">
         <v>1.9599999999999999E-2</v>
       </c>
-      <c r="I55" s="68">
+      <c r="I55" s="63">
         <v>0.01</v>
       </c>
-      <c r="J55" s="70" t="s">
+      <c r="J55" s="65" t="s">
         <v>133</v>
       </c>
     </row>
@@ -4026,31 +4074,31 @@
       <c r="A56" s="12">
         <v>55</v>
       </c>
-      <c r="B56" s="68" t="s">
+      <c r="B56" s="63" t="s">
         <v>126</v>
       </c>
       <c r="C56" s="6">
         <v>0.2</v>
       </c>
-      <c r="D56" s="68">
+      <c r="D56" s="63">
         <v>149</v>
       </c>
-      <c r="E56" s="64" t="s">
+      <c r="E56" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="F56" s="69" t="s">
+      <c r="F56" s="64" t="s">
         <v>127</v>
       </c>
-      <c r="G56" s="68">
+      <c r="G56" s="63">
         <v>0.62290000000000001</v>
       </c>
-      <c r="H56" s="68">
+      <c r="H56" s="63">
         <v>0</v>
       </c>
-      <c r="I56" s="68">
+      <c r="I56" s="63">
         <v>0</v>
       </c>
-      <c r="J56" s="70" t="s">
+      <c r="J56" s="65" t="s">
         <v>134</v>
       </c>
     </row>
@@ -4058,31 +4106,31 @@
       <c r="A57" s="12">
         <v>56</v>
       </c>
-      <c r="B57" s="64" t="s">
+      <c r="B57" s="59" t="s">
         <v>65</v>
       </c>
       <c r="C57" s="6">
         <v>0.2</v>
       </c>
-      <c r="D57" s="68">
+      <c r="D57" s="63">
         <v>149</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="F57" s="69" t="s">
+      <c r="F57" s="64" t="s">
         <v>135</v>
       </c>
-      <c r="G57" s="68">
+      <c r="G57" s="63">
         <v>0.85160000000000002</v>
       </c>
-      <c r="H57" s="68">
+      <c r="H57" s="63">
         <v>1.32E-2</v>
       </c>
-      <c r="I57" s="68">
+      <c r="I57" s="63">
         <v>6.6E-3</v>
       </c>
-      <c r="J57" s="70" t="s">
+      <c r="J57" s="65" t="s">
         <v>136</v>
       </c>
     </row>
@@ -4090,31 +4138,31 @@
       <c r="A58" s="4">
         <v>57</v>
       </c>
-      <c r="B58" s="68" t="s">
+      <c r="B58" s="63" t="s">
         <v>126</v>
       </c>
       <c r="C58" s="6">
         <v>0.2</v>
       </c>
-      <c r="D58" s="68">
+      <c r="D58" s="63">
         <v>149</v>
       </c>
-      <c r="E58" s="64" t="s">
+      <c r="E58" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="F58" s="69" t="s">
+      <c r="F58" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="G58" s="68">
+      <c r="G58" s="63">
         <v>0.64229999999999998</v>
       </c>
-      <c r="H58" s="68">
+      <c r="H58" s="63">
         <v>7.6600000000000001E-2</v>
       </c>
-      <c r="I58" s="68">
+      <c r="I58" s="63">
         <v>0.1096</v>
       </c>
-      <c r="J58" s="70" t="s">
+      <c r="J58" s="65" t="s">
         <v>138</v>
       </c>
     </row>
@@ -4122,31 +4170,31 @@
       <c r="A59" s="12">
         <v>58</v>
       </c>
-      <c r="B59" s="64" t="s">
+      <c r="B59" s="59" t="s">
         <v>65</v>
       </c>
       <c r="C59" s="6">
         <v>0.2</v>
       </c>
-      <c r="D59" s="68">
+      <c r="D59" s="63">
         <v>86</v>
       </c>
-      <c r="E59" s="64" t="s">
+      <c r="E59" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="F59" s="69" t="s">
+      <c r="F59" s="64" t="s">
         <v>135</v>
       </c>
-      <c r="G59" s="68">
+      <c r="G59" s="63">
         <v>0.85219999999999996</v>
       </c>
-      <c r="H59" s="68">
+      <c r="H59" s="63">
         <v>6.6E-3</v>
       </c>
-      <c r="I59" s="68">
+      <c r="I59" s="63">
         <v>3.3E-3</v>
       </c>
-      <c r="J59" s="70" t="s">
+      <c r="J59" s="65" t="s">
         <v>139</v>
       </c>
     </row>
@@ -4154,31 +4202,31 @@
       <c r="A60" s="12">
         <v>59</v>
       </c>
-      <c r="B60" s="68" t="s">
+      <c r="B60" s="63" t="s">
         <v>126</v>
       </c>
       <c r="C60" s="6">
         <v>0.2</v>
       </c>
-      <c r="D60" s="68">
+      <c r="D60" s="63">
         <v>86</v>
       </c>
-      <c r="E60" s="64" t="s">
+      <c r="E60" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="F60" s="69" t="s">
+      <c r="F60" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="G60" s="68">
+      <c r="G60" s="63">
         <v>0.80769999999999997</v>
       </c>
-      <c r="H60" s="68">
+      <c r="H60" s="63">
         <v>0.16089999999999999</v>
       </c>
-      <c r="I60" s="68">
+      <c r="I60" s="63">
         <v>0.16089999999999999</v>
       </c>
-      <c r="J60" s="70" t="s">
+      <c r="J60" s="65" t="s">
         <v>139</v>
       </c>
     </row>
@@ -4186,31 +4234,31 @@
       <c r="A61" s="4">
         <v>60</v>
       </c>
-      <c r="B61" s="64" t="s">
+      <c r="B61" s="59" t="s">
         <v>65</v>
       </c>
       <c r="C61" s="6">
         <v>0.2</v>
       </c>
-      <c r="D61" s="68">
+      <c r="D61" s="63">
         <v>149</v>
       </c>
-      <c r="E61" s="64" t="s">
+      <c r="E61" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="F61" s="69" t="s">
+      <c r="F61" s="64" t="s">
         <v>135</v>
       </c>
-      <c r="G61" s="68">
+      <c r="G61" s="63">
         <v>0.85199999999999998</v>
       </c>
-      <c r="H61" s="68">
+      <c r="H61" s="63">
         <v>6.6E-3</v>
       </c>
-      <c r="I61" s="68">
+      <c r="I61" s="63">
         <v>3.3E-3</v>
       </c>
-      <c r="J61" s="70" t="s">
+      <c r="J61" s="65" t="s">
         <v>140</v>
       </c>
     </row>
@@ -4218,31 +4266,31 @@
       <c r="A62" s="12">
         <v>61</v>
       </c>
-      <c r="B62" s="68" t="s">
+      <c r="B62" s="63" t="s">
         <v>126</v>
       </c>
       <c r="C62" s="6">
         <v>0.2</v>
       </c>
-      <c r="D62" s="68">
+      <c r="D62" s="63">
         <v>149</v>
       </c>
-      <c r="E62" s="64" t="s">
+      <c r="E62" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="F62" s="69" t="s">
+      <c r="F62" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="G62" s="68">
+      <c r="G62" s="63">
         <v>0.80630000000000002</v>
       </c>
-      <c r="H62" s="68">
+      <c r="H62" s="63">
         <v>0.16170000000000001</v>
       </c>
-      <c r="I62" s="68">
+      <c r="I62" s="63">
         <v>0.77239999999999998</v>
       </c>
-      <c r="J62" s="70" t="s">
+      <c r="J62" s="65" t="s">
         <v>140</v>
       </c>
     </row>
@@ -4250,31 +4298,31 @@
       <c r="A63" s="12">
         <v>62</v>
       </c>
-      <c r="B63" s="64" t="s">
+      <c r="B63" s="59" t="s">
         <v>65</v>
       </c>
       <c r="C63" s="6">
         <v>0.2</v>
       </c>
-      <c r="D63" s="68">
+      <c r="D63" s="63">
         <v>149</v>
       </c>
-      <c r="E63" s="68" t="s">
+      <c r="E63" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="F63" s="69" t="s">
+      <c r="F63" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="G63" s="68">
+      <c r="G63" s="63">
         <v>0.85099999999999998</v>
       </c>
-      <c r="H63" s="68">
+      <c r="H63" s="63">
         <v>3.3E-3</v>
       </c>
-      <c r="I63" s="68">
+      <c r="I63" s="63">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="J63" s="70" t="s">
+      <c r="J63" s="65" t="s">
         <v>143</v>
       </c>
     </row>
@@ -4282,31 +4330,31 @@
       <c r="A64" s="4">
         <v>63</v>
       </c>
-      <c r="B64" s="68" t="s">
+      <c r="B64" s="63" t="s">
         <v>126</v>
       </c>
       <c r="C64" s="6">
         <v>0.2</v>
       </c>
-      <c r="D64" s="68">
+      <c r="D64" s="63">
         <v>149</v>
       </c>
-      <c r="E64" s="68" t="s">
+      <c r="E64" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="F64" s="69" t="s">
+      <c r="F64" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="G64" s="68">
+      <c r="G64" s="63">
         <v>0.61850000000000005</v>
       </c>
-      <c r="H64" s="68">
+      <c r="H64" s="63">
         <v>0</v>
       </c>
-      <c r="I64" s="68">
+      <c r="I64" s="63">
         <v>0</v>
       </c>
-      <c r="J64" s="70" t="s">
+      <c r="J64" s="65" t="s">
         <v>145</v>
       </c>
     </row>
@@ -4314,31 +4362,31 @@
       <c r="A65" s="12">
         <v>64</v>
       </c>
-      <c r="B65" s="64" t="s">
+      <c r="B65" s="59" t="s">
         <v>65</v>
       </c>
       <c r="C65" s="6">
         <v>0.2</v>
       </c>
-      <c r="D65" s="68">
+      <c r="D65" s="63">
         <v>149</v>
       </c>
-      <c r="E65" s="68" t="s">
+      <c r="E65" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="F65" s="69" t="s">
+      <c r="F65" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="G65" s="68">
+      <c r="G65" s="63">
         <v>0.85199999999999998</v>
       </c>
-      <c r="H65" s="68">
+      <c r="H65" s="63">
         <v>6.6E-3</v>
       </c>
-      <c r="I65" s="68">
+      <c r="I65" s="63">
         <v>3.3E-3</v>
       </c>
-      <c r="J65" s="70" t="s">
+      <c r="J65" s="65" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4346,31 +4394,31 @@
       <c r="A66" s="12">
         <v>65</v>
       </c>
-      <c r="B66" s="68" t="s">
+      <c r="B66" s="63" t="s">
         <v>126</v>
       </c>
       <c r="C66" s="6">
         <v>0.2</v>
       </c>
-      <c r="D66" s="68">
+      <c r="D66" s="63">
         <v>149</v>
       </c>
-      <c r="E66" s="68" t="s">
+      <c r="E66" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="F66" s="69" t="s">
+      <c r="F66" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="G66" s="68">
+      <c r="G66" s="63">
         <v>0.64380000000000004</v>
       </c>
-      <c r="H66" s="68">
+      <c r="H66" s="63">
         <v>7.9500000000000001E-2</v>
       </c>
-      <c r="I66" s="68">
+      <c r="I66" s="63">
         <v>0.1047</v>
       </c>
-      <c r="J66" s="70" t="s">
+      <c r="J66" s="65" t="s">
         <v>147</v>
       </c>
     </row>
@@ -4378,31 +4426,31 @@
       <c r="A67" s="4">
         <v>66</v>
       </c>
-      <c r="B67" s="64" t="s">
+      <c r="B67" s="59" t="s">
         <v>65</v>
       </c>
       <c r="C67" s="6">
         <v>0.2</v>
       </c>
-      <c r="D67" s="68">
+      <c r="D67" s="63">
         <v>149</v>
       </c>
-      <c r="E67" s="68" t="s">
+      <c r="E67" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="F67" s="69" t="s">
+      <c r="F67" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="G67" s="68">
+      <c r="G67" s="63">
         <v>0.84119999999999995</v>
       </c>
-      <c r="H67" s="68">
+      <c r="H67" s="63">
         <v>5.3E-3</v>
       </c>
-      <c r="I67" s="68">
+      <c r="I67" s="63">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="J67" s="71" t="s">
+      <c r="J67" s="66" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4410,31 +4458,31 @@
       <c r="A68" s="12">
         <v>67</v>
       </c>
-      <c r="B68" s="68" t="s">
+      <c r="B68" s="63" t="s">
         <v>126</v>
       </c>
       <c r="C68" s="6">
         <v>0.2</v>
       </c>
-      <c r="D68" s="68">
+      <c r="D68" s="63">
         <v>149</v>
       </c>
-      <c r="E68" s="68" t="s">
+      <c r="E68" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="F68" s="69" t="s">
+      <c r="F68" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="G68" s="68">
+      <c r="G68" s="63">
         <v>0.61219999999999997</v>
       </c>
-      <c r="H68" s="68">
+      <c r="H68" s="63">
         <v>0</v>
       </c>
-      <c r="I68" s="68">
+      <c r="I68" s="63">
         <v>0</v>
       </c>
-      <c r="J68" s="71" t="s">
+      <c r="J68" s="66" t="s">
         <v>149</v>
       </c>
     </row>
@@ -4442,127 +4490,127 @@
       <c r="A69" s="12">
         <v>68</v>
       </c>
-      <c r="B69" s="64" t="s">
+      <c r="B69" s="59" t="s">
         <v>65</v>
       </c>
       <c r="C69" s="6">
         <v>0.2</v>
       </c>
-      <c r="D69" s="68">
+      <c r="D69" s="63">
         <v>149</v>
       </c>
-      <c r="E69" s="68" t="s">
+      <c r="E69" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="F69" s="69" t="s">
+      <c r="F69" s="64" t="s">
         <v>150</v>
       </c>
-      <c r="G69" s="68">
+      <c r="G69" s="63">
         <v>0.85040000000000004</v>
       </c>
-      <c r="H69" s="68">
+      <c r="H69" s="63">
         <v>0.2923</v>
       </c>
-      <c r="I69" s="68">
+      <c r="I69" s="63">
         <v>0.36709999999999998</v>
       </c>
-      <c r="J69" s="70" t="s">
+      <c r="J69" s="65" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="99" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" ht="155.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>69</v>
       </c>
-      <c r="B70" s="68" t="s">
+      <c r="B70" t="s">
         <v>126</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C70">
         <v>0.2</v>
       </c>
-      <c r="D70" s="68">
+      <c r="D70">
         <v>149</v>
       </c>
-      <c r="E70" s="68" t="s">
+      <c r="E70" t="s">
         <v>141</v>
       </c>
-      <c r="F70" s="69" t="s">
+      <c r="F70" s="77" t="s">
         <v>152</v>
       </c>
-      <c r="G70" s="68">
+      <c r="G70">
         <v>0.65249999999999997</v>
       </c>
-      <c r="H70" s="68">
+      <c r="H70">
         <v>8.0199999999999994E-2</v>
       </c>
-      <c r="I70" s="68">
+      <c r="I70">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="J70" s="70" t="s">
+      <c r="J70" s="65" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="181.5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" ht="203.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="12">
         <v>70</v>
       </c>
-      <c r="B71" s="64" t="s">
+      <c r="B71" t="s">
         <v>65</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C71">
         <v>0.2</v>
       </c>
-      <c r="D71" s="68">
+      <c r="D71">
         <v>149</v>
       </c>
-      <c r="E71" s="68" t="s">
+      <c r="E71" t="s">
         <v>141</v>
       </c>
-      <c r="F71" s="69" t="s">
-        <v>150</v>
-      </c>
-      <c r="G71" s="68">
+      <c r="F71" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="G71">
         <v>0.84019999999999995</v>
       </c>
-      <c r="H71" s="68">
+      <c r="H71">
         <v>0.53500000000000003</v>
       </c>
-      <c r="I71" s="68">
+      <c r="I71">
         <v>0.74250000000000005</v>
       </c>
-      <c r="J71" s="70" t="s">
+      <c r="J71" s="65" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="99" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" ht="142.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="12">
         <v>71</v>
       </c>
-      <c r="B72" s="68" t="s">
+      <c r="B72" t="s">
         <v>126</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72">
         <v>0.2</v>
       </c>
-      <c r="D72" s="68">
+      <c r="D72">
         <v>149</v>
       </c>
-      <c r="E72" s="68" t="s">
+      <c r="E72" t="s">
         <v>141</v>
       </c>
-      <c r="F72" s="69" t="s">
+      <c r="F72" s="77" t="s">
         <v>152</v>
       </c>
-      <c r="G72" s="68">
+      <c r="G72">
         <v>0.63870000000000005</v>
       </c>
-      <c r="H72" s="68">
+      <c r="H72">
         <v>0.1341</v>
       </c>
-      <c r="I72" s="68">
+      <c r="I72">
         <v>9.1399999999999995E-2</v>
       </c>
-      <c r="J72" s="70" t="s">
+      <c r="J72" s="65" t="s">
         <v>155</v>
       </c>
     </row>

--- a/SantanderCS/results/ResultListByTestModel_Final.xlsx
+++ b/SantanderCS/results/ResultListByTestModel_Final.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\big20\git\big20-ML-project2-team3\SantanderCS\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32511A3E-67E0-4413-A763-77FBB6E1BD1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29D820D-2B6B-44FB-B55C-A68B3F84C5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="345" windowWidth="28800" windowHeight="14190" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$B$297</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -391,7 +394,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="158">
   <si>
     <t>NO</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1284,10 +1287,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>var3 / Not Scaled</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>xgb_clf = XGBClassifier(
     colsample_bytree=0.6189,
     gamma=2.1975,
@@ -1397,12 +1396,20 @@
     'scale_pos_weight': np.float64(5.0), 
     'subsample': np.float64(0.6896)}</t>
   </si>
+  <si>
+    <t xml:space="preserve">Var3 / ZCR &gt; 99% </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / ZCR &gt; 99%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1440,13 +1447,6 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFC00000"/>
-      <name val="D2Coding"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1738,11 +1738,11 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1818,9 +1818,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1851,98 +1848,119 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="7" borderId="6" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1956,26 +1974,29 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="7" borderId="6" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="7" borderId="6" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2293,6 +2314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA66AA66-968F-43FC-BD0D-4CB9ADC09730}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K297"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2344,7 +2366,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="132" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>1</v>
       </c>
@@ -2375,11 +2397,11 @@
       <c r="J2" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="67" t="s">
+      <c r="K2" s="73" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="132" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -2410,42 +2432,42 @@
       <c r="J3" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="68"/>
-    </row>
-    <row r="4" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="K3" s="74"/>
+    </row>
+    <row r="4" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="78">
         <v>0.2</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="78">
         <v>0.84219999999999995</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="20">
+      <c r="I4" s="78">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="68"/>
-    </row>
-    <row r="5" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="K4" s="74"/>
+    </row>
+    <row r="5" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -2473,12 +2495,12 @@
       <c r="I5" s="20">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="J5" s="26" t="s">
+      <c r="J5" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="68"/>
-    </row>
-    <row r="6" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="K5" s="74"/>
+    </row>
+    <row r="6" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>5</v>
       </c>
@@ -2509,9 +2531,9 @@
       <c r="J6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="68"/>
-    </row>
-    <row r="7" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="K6" s="74"/>
+    </row>
+    <row r="7" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2524,7 +2546,7 @@
       <c r="D7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="14" t="s">
@@ -2542,9 +2564,9 @@
       <c r="J7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="68"/>
-    </row>
-    <row r="8" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="K7" s="74"/>
+    </row>
+    <row r="8" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>7</v>
       </c>
@@ -2557,7 +2579,7 @@
       <c r="D8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F8" s="14" t="s">
@@ -2575,9 +2597,9 @@
       <c r="J8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K8" s="68"/>
-    </row>
-    <row r="9" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="K8" s="74"/>
+    </row>
+    <row r="9" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2590,7 +2612,7 @@
       <c r="D9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="26" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="14" t="s">
@@ -2608,9 +2630,9 @@
       <c r="J9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="K9" s="68"/>
-    </row>
-    <row r="10" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="K9" s="74"/>
+    </row>
+    <row r="10" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
         <v>9</v>
       </c>
@@ -2620,16 +2642,16 @@
       <c r="C10" s="20">
         <v>0.2</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="28" t="s">
         <v>37</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="29">
         <v>0.82630000000000003</v>
       </c>
       <c r="H10" s="23">
@@ -2638,12 +2660,12 @@
       <c r="I10" s="23">
         <v>0.39529999999999998</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="K10" s="68"/>
-    </row>
-    <row r="11" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="K10" s="74"/>
+    </row>
+    <row r="11" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2656,7 +2678,7 @@
       <c r="D11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="26" t="s">
         <v>40</v>
       </c>
       <c r="F11" s="14" t="s">
@@ -2674,22 +2696,22 @@
       <c r="J11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="K11" s="68"/>
-    </row>
-    <row r="12" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="K11" s="74"/>
+    </row>
+    <row r="12" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12">
         <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="31">
         <v>0.3</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="26" t="s">
         <v>43</v>
       </c>
       <c r="F12" s="14" t="s">
@@ -2707,9 +2729,9 @@
       <c r="J12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K12" s="68"/>
-    </row>
-    <row r="13" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="K12" s="74"/>
+    </row>
+    <row r="13" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2722,7 +2744,7 @@
       <c r="D13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F13" s="14" t="s">
@@ -2740,9 +2762,9 @@
       <c r="J13" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="K13" s="68"/>
-    </row>
-    <row r="14" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="K13" s="74"/>
+    </row>
+    <row r="14" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12">
         <v>13</v>
       </c>
@@ -2755,7 +2777,7 @@
       <c r="D14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="26" t="s">
         <v>49</v>
       </c>
       <c r="F14" s="14" t="s">
@@ -2773,9 +2795,9 @@
       <c r="J14" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="K14" s="68"/>
-    </row>
-    <row r="15" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="K14" s="74"/>
+    </row>
+    <row r="15" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -2788,7 +2810,7 @@
       <c r="D15" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="26" t="s">
         <v>51</v>
       </c>
       <c r="F15" s="14" t="s">
@@ -2804,22 +2826,22 @@
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="J15" s="7"/>
-      <c r="K15" s="68"/>
-    </row>
-    <row r="16" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="K15" s="74"/>
+    </row>
+    <row r="16" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12">
         <v>15</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="32">
         <v>0.3</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="26" t="s">
         <v>43</v>
       </c>
       <c r="F16" s="14" t="s">
@@ -2837,63 +2859,63 @@
       <c r="J16" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="K16" s="68"/>
-    </row>
-    <row r="17" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="K16" s="74"/>
+    </row>
+    <row r="17" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="27" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="6">
         <v>0.2</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="27" t="s">
         <v>16</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="35" t="s">
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="K17" s="68"/>
-    </row>
-    <row r="18" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="K17" s="74"/>
+    </row>
+    <row r="18" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12">
         <v>17</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="27" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="6">
         <v>0.2</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="27" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F18" s="29" t="s">
+      <c r="F18" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="35" t="s">
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="K18" s="68"/>
-    </row>
-    <row r="19" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="K18" s="74"/>
+    </row>
+    <row r="19" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -2912,7 +2934,7 @@
       <c r="F19" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="35">
         <v>0.83560000000000001</v>
       </c>
       <c r="H19" s="13">
@@ -2928,7 +2950,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12">
         <v>19</v>
       </c>
@@ -2947,7 +2969,7 @@
       <c r="F20" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="35">
         <v>0.82150000000000001</v>
       </c>
       <c r="H20" s="13">
@@ -2960,7 +2982,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -2979,7 +3001,7 @@
       <c r="F21" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="36">
+      <c r="G21" s="35">
         <v>0.81240000000000001</v>
       </c>
       <c r="H21" s="13">
@@ -2992,7 +3014,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12">
         <v>21</v>
       </c>
@@ -3011,7 +3033,7 @@
       <c r="F22" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="35">
         <v>0.85089999999999999</v>
       </c>
       <c r="H22" s="13">
@@ -3024,39 +3046,39 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="132" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="67">
         <v>0.2</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="G23" s="36">
+      <c r="G23" s="77">
         <v>0.85089999999999999</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="77">
         <v>0.2974</v>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="77">
         <v>0.51500000000000001</v>
       </c>
-      <c r="J23" s="15" t="s">
+      <c r="J23" s="80" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="148.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12">
         <v>23</v>
       </c>
@@ -3075,7 +3097,7 @@
       <c r="F24" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="G24" s="36">
+      <c r="G24" s="35">
         <v>0.85050000000000003</v>
       </c>
       <c r="H24" s="13">
@@ -3088,7 +3110,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -3107,7 +3129,7 @@
       <c r="F25" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G25" s="36">
+      <c r="G25" s="35">
         <v>0.84370000000000001</v>
       </c>
       <c r="H25" s="13">
@@ -3120,7 +3142,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12">
         <v>25</v>
       </c>
@@ -3139,7 +3161,7 @@
       <c r="F26" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="G26" s="36">
+      <c r="G26" s="35">
         <v>0.84370000000000001</v>
       </c>
       <c r="H26" s="13">
@@ -3152,7 +3174,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -3171,7 +3193,7 @@
       <c r="F27" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G27" s="36">
+      <c r="G27" s="35">
         <v>0.84370000000000001</v>
       </c>
       <c r="H27" s="13">
@@ -3184,7 +3206,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12">
         <v>27</v>
       </c>
@@ -3203,7 +3225,7 @@
       <c r="F28" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G28" s="36">
+      <c r="G28" s="35">
         <v>0.84370000000000001</v>
       </c>
       <c r="H28" s="13">
@@ -3216,7 +3238,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -3235,7 +3257,7 @@
       <c r="F29" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G29" s="36">
+      <c r="G29" s="35">
         <v>0.84370000000000001</v>
       </c>
       <c r="H29" s="13">
@@ -3248,7 +3270,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12">
         <v>29</v>
       </c>
@@ -3267,7 +3289,7 @@
       <c r="F30" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="35">
         <v>0.84370000000000001</v>
       </c>
       <c r="H30" s="13">
@@ -3280,11 +3302,11 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>30</v>
       </c>
-      <c r="B31" s="37" t="s">
+      <c r="B31" s="36" t="s">
         <v>72</v>
       </c>
       <c r="C31" s="6">
@@ -3293,99 +3315,99 @@
       <c r="D31" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="E31" s="37" t="s">
+      <c r="E31" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="F31" s="38" t="s">
+      <c r="F31" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="G31" s="39">
+      <c r="G31" s="38">
         <v>0.84</v>
       </c>
-      <c r="H31" s="37" t="s">
+      <c r="H31" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="I31" s="37" t="s">
+      <c r="I31" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="J31" s="40" t="s">
+      <c r="J31" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K31" s="69" t="s">
+      <c r="K31" s="75" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12">
         <v>31</v>
       </c>
-      <c r="B32" s="41" t="s">
+      <c r="B32" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="67">
         <v>0.2</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="E32" s="41" t="s">
+      <c r="E32" s="81" t="s">
         <v>79</v>
       </c>
-      <c r="F32" s="42" t="s">
+      <c r="F32" s="82" t="s">
         <v>85</v>
       </c>
-      <c r="G32" s="44">
+      <c r="G32" s="81">
         <v>0.84379999999999999</v>
       </c>
-      <c r="H32" s="41">
+      <c r="H32" s="81">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="I32" s="41">
+      <c r="I32" s="81">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J32" s="43" t="s">
+      <c r="J32" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="K32" s="70"/>
-    </row>
-    <row r="33" spans="1:11" ht="132" x14ac:dyDescent="0.3">
+      <c r="K32" s="76"/>
+    </row>
+    <row r="33" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="67">
         <v>0.2</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="E33" s="41" t="s">
+      <c r="E33" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="42" t="s">
+      <c r="F33" s="82" t="s">
         <v>89</v>
       </c>
-      <c r="G33" s="41">
+      <c r="G33" s="81">
         <v>0.80510000000000004</v>
       </c>
-      <c r="H33" s="41">
+      <c r="H33" s="81">
         <v>1.29E-2</v>
       </c>
-      <c r="I33" s="41">
+      <c r="I33" s="81">
         <v>6.6E-3</v>
       </c>
-      <c r="J33" s="43" t="s">
+      <c r="J33" s="83" t="s">
         <v>90</v>
       </c>
-      <c r="K33" s="70"/>
-    </row>
-    <row r="34" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+      <c r="K33" s="76"/>
+    </row>
+    <row r="34" spans="1:11" ht="99" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="12">
         <v>33</v>
       </c>
-      <c r="B34" s="41" t="s">
+      <c r="B34" s="40" t="s">
         <v>65</v>
       </c>
       <c r="C34" s="6">
@@ -3394,31 +3416,31 @@
       <c r="D34" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="E34" s="41" t="s">
+      <c r="E34" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="F34" s="42" t="s">
+      <c r="F34" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="G34" s="44">
+      <c r="G34" s="43">
         <v>0.84209999999999996</v>
       </c>
-      <c r="H34" s="41">
+      <c r="H34" s="40">
         <v>1.6299999999999999E-2</v>
       </c>
-      <c r="I34" s="41">
+      <c r="I34" s="40">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="J34" s="43" t="s">
+      <c r="J34" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="K34" s="70"/>
-    </row>
-    <row r="35" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="K34" s="76"/>
+    </row>
+    <row r="35" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
-      <c r="B35" s="41" t="s">
+      <c r="B35" s="40" t="s">
         <v>65</v>
       </c>
       <c r="C35" s="6">
@@ -3427,31 +3449,31 @@
       <c r="D35" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="E35" s="41" t="s">
+      <c r="E35" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="F35" s="42" t="s">
+      <c r="F35" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="G35" s="41">
+      <c r="G35" s="40">
         <v>0.83240000000000003</v>
       </c>
-      <c r="H35" s="41">
+      <c r="H35" s="40">
         <v>2.2499999999999999E-2</v>
       </c>
-      <c r="I35" s="41">
+      <c r="I35" s="40">
         <v>1.1599999999999999E-2</v>
       </c>
-      <c r="J35" s="43" t="s">
+      <c r="J35" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="K35" s="70"/>
-    </row>
-    <row r="36" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="K35" s="76"/>
+    </row>
+    <row r="36" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="12">
         <v>35</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="40" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="6">
@@ -3460,95 +3482,95 @@
       <c r="D36" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="E36" s="41" t="s">
+      <c r="E36" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="F36" s="42" t="s">
+      <c r="F36" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="G36" s="41">
+      <c r="G36" s="40">
         <v>0.83620000000000005</v>
       </c>
-      <c r="H36" s="41">
+      <c r="H36" s="40">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="I36" s="41">
+      <c r="I36" s="40">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J36" s="43" t="s">
+      <c r="J36" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="K36" s="70"/>
-    </row>
-    <row r="37" spans="1:11" ht="132" x14ac:dyDescent="0.3">
+      <c r="K36" s="76"/>
+    </row>
+    <row r="37" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
-      <c r="B37" s="71" t="s">
+      <c r="B37" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="72">
+      <c r="C37" s="67">
         <v>0.2</v>
       </c>
-      <c r="D37" s="73" t="s">
+      <c r="D37" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="E37" s="74" t="s">
+      <c r="E37" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="F37" s="75" t="s">
+      <c r="F37" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="G37" s="72">
+      <c r="G37" s="67">
         <v>0.93</v>
       </c>
-      <c r="H37" s="72">
+      <c r="H37" s="67">
         <v>0.29330000000000001</v>
       </c>
-      <c r="I37" s="72">
+      <c r="I37" s="67">
         <v>0.88529999999999998</v>
       </c>
-      <c r="J37" s="76" t="s">
+      <c r="J37" s="71" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="148.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12">
         <v>37</v>
       </c>
-      <c r="B38" s="71" t="s">
+      <c r="B38" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="72">
+      <c r="C38" s="67">
         <v>0.2</v>
       </c>
-      <c r="D38" s="73" t="s">
+      <c r="D38" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="E38" s="74" t="s">
+      <c r="E38" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="F38" s="75" t="s">
+      <c r="F38" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="G38" s="72">
+      <c r="G38" s="67">
         <v>0.91149999999999998</v>
       </c>
-      <c r="H38" s="72">
+      <c r="H38" s="67">
         <v>0.2797</v>
       </c>
-      <c r="I38" s="73">
+      <c r="I38" s="68">
         <v>0.85570000000000002</v>
       </c>
-      <c r="J38" s="76" t="s">
+      <c r="J38" s="71" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="99" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
-      <c r="B39" s="28" t="s">
+      <c r="B39" s="27" t="s">
         <v>72</v>
       </c>
       <c r="C39" s="6">
@@ -3557,74 +3579,74 @@
       <c r="D39" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E39" s="29" t="s">
+      <c r="E39" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F39" s="27" t="s">
+      <c r="F39" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="G39" s="46">
+      <c r="G39" s="45">
         <v>0.84570000000000001</v>
       </c>
-      <c r="H39" s="46">
+      <c r="H39" s="45">
         <v>1.5299999999999999E-2</v>
       </c>
-      <c r="I39" s="46">
+      <c r="I39" s="45">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="J39" s="47" t="s">
+      <c r="J39" s="46" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="198" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="198" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="12">
         <v>39</v>
       </c>
-      <c r="B40" s="48" t="s">
+      <c r="B40" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="C40" s="49">
+      <c r="C40" s="48">
         <v>0.2</v>
       </c>
-      <c r="D40" s="50" t="s">
+      <c r="D40" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="E40" s="51" t="s">
+      <c r="E40" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="F40" s="52" t="s">
+      <c r="F40" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="G40" s="53">
+      <c r="G40" s="52">
         <v>0.84520600000000001</v>
       </c>
-      <c r="H40" s="53">
+      <c r="H40" s="52">
         <v>0.287053</v>
       </c>
-      <c r="I40" s="54">
+      <c r="I40" s="53">
         <v>0.55980099999999999</v>
       </c>
-      <c r="J40" s="55" t="s">
+      <c r="J40" s="54" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="99" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
-      <c r="B41" s="28" t="s">
+      <c r="B41" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="32">
         <v>0.3</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E41" s="27" t="s">
+      <c r="E41" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="F41" s="45" t="s">
+      <c r="F41" s="44" t="s">
         <v>102</v>
       </c>
       <c r="G41" s="6">
@@ -3636,15 +3658,15 @@
       <c r="I41" s="5">
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="J41" s="56" t="s">
+      <c r="J41" s="55" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="181.5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="12">
         <v>41</v>
       </c>
-      <c r="B42" s="28" t="s">
+      <c r="B42" s="27" t="s">
         <v>72</v>
       </c>
       <c r="C42" s="6">
@@ -3653,10 +3675,10 @@
       <c r="D42" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E42" s="28" t="s">
+      <c r="E42" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="F42" s="45" t="s">
+      <c r="F42" s="44" t="s">
         <v>109</v>
       </c>
       <c r="G42" s="6">
@@ -3668,47 +3690,47 @@
       <c r="I42" s="5">
         <v>0.37040000000000001</v>
       </c>
-      <c r="J42" s="56" t="s">
+      <c r="J42" s="55" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="198" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="198" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
-      <c r="B43" s="28" t="s">
+      <c r="B43" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="67">
         <v>0.2</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="F43" s="45" t="s">
+      <c r="F43" s="70" t="s">
         <v>111</v>
       </c>
-      <c r="G43" s="6">
+      <c r="G43" s="67">
         <v>0.83463600000000004</v>
       </c>
-      <c r="H43" s="6">
+      <c r="H43" s="67">
         <v>0.28441</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I43" s="68">
         <v>0.362126</v>
       </c>
-      <c r="J43" s="56" t="s">
+      <c r="J43" s="84" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="132" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12">
         <v>43</v>
       </c>
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="27" t="s">
         <v>72</v>
       </c>
       <c r="C44" s="6">
@@ -3720,7 +3742,7 @@
       <c r="E44" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F44" s="27" t="s">
+      <c r="F44" s="26" t="s">
         <v>113</v>
       </c>
       <c r="G44" s="6">
@@ -3732,15 +3754,15 @@
       <c r="I44" s="6">
         <v>2.6578000000000001E-2</v>
       </c>
-      <c r="J44" s="47" t="s">
+      <c r="J44" s="46" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="181.5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>44</v>
       </c>
-      <c r="B45" s="28" t="s">
+      <c r="B45" s="27" t="s">
         <v>72</v>
       </c>
       <c r="C45" s="6">
@@ -3752,7 +3774,7 @@
       <c r="E45" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="F45" s="45" t="s">
+      <c r="F45" s="44" t="s">
         <v>115</v>
       </c>
       <c r="G45" s="6">
@@ -3764,15 +3786,15 @@
       <c r="I45" s="5">
         <v>0.64119999999999999</v>
       </c>
-      <c r="J45" s="56" t="s">
+      <c r="J45" s="55" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="181.5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="12">
         <v>45</v>
       </c>
-      <c r="B46" s="28" t="s">
+      <c r="B46" s="27" t="s">
         <v>72</v>
       </c>
       <c r="C46" s="6">
@@ -3784,7 +3806,7 @@
       <c r="E46" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="F46" s="45" t="s">
+      <c r="F46" s="44" t="s">
         <v>115</v>
       </c>
       <c r="G46" s="6">
@@ -3796,15 +3818,15 @@
       <c r="I46" s="5">
         <v>0.54149999999999998</v>
       </c>
-      <c r="J46" s="56" t="s">
+      <c r="J46" s="55" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="181.5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>46</v>
       </c>
-      <c r="B47" s="28" t="s">
+      <c r="B47" s="27" t="s">
         <v>72</v>
       </c>
       <c r="C47" s="20">
@@ -3813,10 +3835,10 @@
       <c r="D47" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E47" s="27" t="s">
+      <c r="E47" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="F47" s="45" t="s">
+      <c r="F47" s="44" t="s">
         <v>115</v>
       </c>
       <c r="G47" s="1">
@@ -3828,117 +3850,117 @@
       <c r="I47" s="2">
         <v>0.42520000000000002</v>
       </c>
-      <c r="J47" s="57" t="s">
+      <c r="J47" s="56" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="181.5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="12">
         <v>47</v>
       </c>
-      <c r="B48" s="28" t="s">
+      <c r="B48" s="27" t="s">
         <v>72</v>
       </c>
       <c r="C48" s="6">
         <v>0.2</v>
       </c>
-      <c r="D48" s="28" t="s">
+      <c r="D48" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="E48" s="28" t="s">
+      <c r="E48" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F48" s="45" t="s">
+      <c r="F48" s="44" t="s">
         <v>119</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
       <c r="I48" s="5"/>
-      <c r="J48" s="58" t="s">
+      <c r="J48" s="57" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="181.5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>48</v>
       </c>
-      <c r="B49" s="28" t="s">
+      <c r="B49" s="27" t="s">
         <v>72</v>
       </c>
       <c r="C49" s="6">
         <v>0.2</v>
       </c>
-      <c r="D49" s="28" t="s">
+      <c r="D49" s="27" t="s">
         <v>16</v>
       </c>
       <c r="E49" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F49" s="45" t="s">
+      <c r="F49" s="44" t="s">
         <v>119</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
       <c r="I49" s="5"/>
-      <c r="J49" s="58" t="s">
+      <c r="J49" s="57" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="181.5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12">
         <v>49</v>
       </c>
-      <c r="B50" s="28" t="s">
+      <c r="B50" s="27" t="s">
         <v>72</v>
       </c>
       <c r="C50" s="6">
         <v>0.2</v>
       </c>
-      <c r="D50" s="28" t="s">
+      <c r="D50" s="27" t="s">
         <v>16</v>
       </c>
       <c r="E50" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F50" s="45" t="s">
+      <c r="F50" s="44" t="s">
         <v>119</v>
       </c>
       <c r="G50" s="20"/>
       <c r="H50" s="20"/>
       <c r="I50" s="5"/>
-      <c r="J50" s="58" t="s">
+      <c r="J50" s="57" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12">
         <v>50</v>
       </c>
-      <c r="B51" s="59" t="s">
+      <c r="B51" s="58" t="s">
         <v>65</v>
       </c>
       <c r="C51" s="6">
         <v>0.2</v>
       </c>
-      <c r="D51" s="59">
+      <c r="D51" s="58">
         <v>86</v>
       </c>
-      <c r="E51" s="59" t="s">
+      <c r="E51" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="F51" s="60" t="s">
+      <c r="F51" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="G51" s="61">
+      <c r="G51" s="60">
         <v>0.84209999999999996</v>
       </c>
-      <c r="H51" s="59">
+      <c r="H51" s="58">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="I51" s="59">
+      <c r="I51" s="58">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J51" s="62" t="s">
+      <c r="J51" s="61" t="s">
         <v>125</v>
       </c>
     </row>
@@ -3946,255 +3968,255 @@
       <c r="A52" s="4">
         <v>51</v>
       </c>
-      <c r="B52" s="63" t="s">
-        <v>126</v>
+      <c r="B52" s="62" t="s">
+        <v>87</v>
       </c>
       <c r="C52" s="6">
         <v>0.2</v>
       </c>
-      <c r="D52" s="63">
+      <c r="D52" s="62">
         <v>86</v>
       </c>
-      <c r="E52" s="59" t="s">
+      <c r="E52" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="F52" s="64" t="s">
+      <c r="F52" s="63" t="s">
         <v>127</v>
       </c>
-      <c r="G52" s="63">
+      <c r="G52" s="62">
         <v>0.62160000000000004</v>
       </c>
-      <c r="H52" s="63">
+      <c r="H52" s="62">
         <v>0</v>
       </c>
-      <c r="I52" s="63">
+      <c r="I52" s="62">
         <v>0</v>
       </c>
-      <c r="J52" s="65" t="s">
+      <c r="J52" s="64" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12">
         <v>52</v>
       </c>
-      <c r="B53" s="59" t="s">
+      <c r="B53" s="58" t="s">
         <v>65</v>
       </c>
       <c r="C53" s="6">
         <v>0.2</v>
       </c>
-      <c r="D53" s="59">
+      <c r="D53" s="58">
         <v>86</v>
       </c>
-      <c r="E53" s="59" t="s">
+      <c r="E53" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="F53" s="64" t="s">
+      <c r="F53" s="63" t="s">
         <v>129</v>
       </c>
-      <c r="G53" s="63">
+      <c r="G53" s="62">
         <v>0.8528</v>
       </c>
-      <c r="H53" s="63">
+      <c r="H53" s="62">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="I53" s="63">
+      <c r="I53" s="62">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J53" s="65" t="s">
+      <c r="J53" s="64" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="12">
         <v>53</v>
       </c>
-      <c r="B54" s="63" t="s">
-        <v>126</v>
+      <c r="B54" s="62" t="s">
+        <v>87</v>
       </c>
       <c r="C54" s="6">
         <v>0.2</v>
       </c>
-      <c r="D54" s="63">
+      <c r="D54" s="62">
         <v>86</v>
       </c>
-      <c r="E54" s="59" t="s">
+      <c r="E54" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="F54" s="64" t="s">
+      <c r="F54" s="63" t="s">
         <v>131</v>
       </c>
-      <c r="G54" s="63">
+      <c r="G54" s="62">
         <v>0.60240000000000005</v>
       </c>
-      <c r="H54" s="63">
+      <c r="H54" s="62">
         <v>0</v>
       </c>
-      <c r="I54" s="63">
+      <c r="I54" s="62">
         <v>0</v>
       </c>
-      <c r="J54" s="65" t="s">
+      <c r="J54" s="64" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>54</v>
       </c>
-      <c r="B55" s="59" t="s">
+      <c r="B55" s="58" t="s">
         <v>65</v>
       </c>
       <c r="C55" s="6">
         <v>0.2</v>
       </c>
-      <c r="D55" s="63">
+      <c r="D55" s="62">
         <v>149</v>
       </c>
-      <c r="E55" s="59" t="s">
+      <c r="E55" s="58" t="s">
         <v>123</v>
       </c>
-      <c r="F55" s="64" t="s">
+      <c r="F55" s="63" t="s">
         <v>124</v>
       </c>
-      <c r="G55" s="63">
+      <c r="G55" s="62">
         <v>0.8417</v>
       </c>
-      <c r="H55" s="63">
+      <c r="H55" s="62">
         <v>1.9599999999999999E-2</v>
       </c>
-      <c r="I55" s="63">
+      <c r="I55" s="62">
         <v>0.01</v>
       </c>
-      <c r="J55" s="65" t="s">
+      <c r="J55" s="64" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="99" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" ht="99" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12">
         <v>55</v>
       </c>
-      <c r="B56" s="63" t="s">
-        <v>126</v>
+      <c r="B56" s="62" t="s">
+        <v>87</v>
       </c>
       <c r="C56" s="6">
         <v>0.2</v>
       </c>
-      <c r="D56" s="63">
+      <c r="D56" s="62">
         <v>149</v>
       </c>
       <c r="E56" s="59" t="s">
-        <v>123</v>
-      </c>
-      <c r="F56" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="F56" s="63" t="s">
         <v>127</v>
       </c>
-      <c r="G56" s="63">
+      <c r="G56" s="62">
         <v>0.62290000000000001</v>
       </c>
-      <c r="H56" s="63">
+      <c r="H56" s="62">
         <v>0</v>
       </c>
-      <c r="I56" s="63">
+      <c r="I56" s="62">
         <v>0</v>
       </c>
-      <c r="J56" s="65" t="s">
+      <c r="J56" s="64" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="12">
         <v>56</v>
       </c>
-      <c r="B57" s="59" t="s">
+      <c r="B57" s="58" t="s">
         <v>65</v>
       </c>
       <c r="C57" s="6">
         <v>0.2</v>
       </c>
-      <c r="D57" s="63">
+      <c r="D57" s="62">
         <v>149</v>
       </c>
       <c r="E57" s="59" t="s">
-        <v>123</v>
-      </c>
-      <c r="F57" s="64" t="s">
+        <v>157</v>
+      </c>
+      <c r="F57" s="63" t="s">
         <v>135</v>
       </c>
-      <c r="G57" s="63">
+      <c r="G57" s="62">
         <v>0.85160000000000002</v>
       </c>
-      <c r="H57" s="63">
+      <c r="H57" s="62">
         <v>1.32E-2</v>
       </c>
-      <c r="I57" s="63">
+      <c r="I57" s="62">
         <v>6.6E-3</v>
       </c>
-      <c r="J57" s="65" t="s">
+      <c r="J57" s="64" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>57</v>
       </c>
-      <c r="B58" s="63" t="s">
-        <v>126</v>
+      <c r="B58" s="62" t="s">
+        <v>87</v>
       </c>
       <c r="C58" s="6">
         <v>0.2</v>
       </c>
-      <c r="D58" s="63">
+      <c r="D58" s="62">
         <v>149</v>
       </c>
-      <c r="E58" s="59" t="s">
-        <v>123</v>
-      </c>
-      <c r="F58" s="64" t="s">
+      <c r="E58" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="F58" s="63" t="s">
         <v>137</v>
       </c>
-      <c r="G58" s="63">
+      <c r="G58" s="62">
         <v>0.64229999999999998</v>
       </c>
-      <c r="H58" s="63">
+      <c r="H58" s="62">
         <v>7.6600000000000001E-2</v>
       </c>
-      <c r="I58" s="63">
+      <c r="I58" s="62">
         <v>0.1096</v>
       </c>
-      <c r="J58" s="65" t="s">
+      <c r="J58" s="64" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="12">
         <v>58</v>
       </c>
-      <c r="B59" s="59" t="s">
+      <c r="B59" s="58" t="s">
         <v>65</v>
       </c>
       <c r="C59" s="6">
         <v>0.2</v>
       </c>
-      <c r="D59" s="63">
+      <c r="D59" s="62">
         <v>86</v>
       </c>
       <c r="E59" s="59" t="s">
-        <v>123</v>
-      </c>
-      <c r="F59" s="64" t="s">
+        <v>27</v>
+      </c>
+      <c r="F59" s="63" t="s">
         <v>135</v>
       </c>
-      <c r="G59" s="63">
+      <c r="G59" s="62">
         <v>0.85219999999999996</v>
       </c>
-      <c r="H59" s="63">
+      <c r="H59" s="62">
         <v>6.6E-3</v>
       </c>
-      <c r="I59" s="63">
+      <c r="I59" s="62">
         <v>3.3E-3</v>
       </c>
-      <c r="J59" s="65" t="s">
+      <c r="J59" s="64" t="s">
         <v>139</v>
       </c>
     </row>
@@ -4202,63 +4224,63 @@
       <c r="A60" s="12">
         <v>59</v>
       </c>
-      <c r="B60" s="63" t="s">
-        <v>126</v>
+      <c r="B60" s="62" t="s">
+        <v>87</v>
       </c>
       <c r="C60" s="6">
         <v>0.2</v>
       </c>
-      <c r="D60" s="63">
+      <c r="D60" s="62">
         <v>86</v>
       </c>
       <c r="E60" s="59" t="s">
-        <v>123</v>
-      </c>
-      <c r="F60" s="64" t="s">
+        <v>27</v>
+      </c>
+      <c r="F60" s="63" t="s">
         <v>137</v>
       </c>
-      <c r="G60" s="63">
+      <c r="G60" s="62">
         <v>0.80769999999999997</v>
       </c>
-      <c r="H60" s="63">
+      <c r="H60" s="62">
         <v>0.16089999999999999</v>
       </c>
-      <c r="I60" s="63">
+      <c r="I60" s="62">
         <v>0.16089999999999999</v>
       </c>
-      <c r="J60" s="65" t="s">
+      <c r="J60" s="64" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>60</v>
       </c>
-      <c r="B61" s="59" t="s">
+      <c r="B61" s="58" t="s">
         <v>65</v>
       </c>
       <c r="C61" s="6">
         <v>0.2</v>
       </c>
-      <c r="D61" s="63">
+      <c r="D61" s="62">
         <v>149</v>
       </c>
       <c r="E61" s="59" t="s">
-        <v>123</v>
-      </c>
-      <c r="F61" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="F61" s="63" t="s">
         <v>135</v>
       </c>
-      <c r="G61" s="63">
+      <c r="G61" s="62">
         <v>0.85199999999999998</v>
       </c>
-      <c r="H61" s="63">
+      <c r="H61" s="62">
         <v>6.6E-3</v>
       </c>
-      <c r="I61" s="63">
+      <c r="I61" s="62">
         <v>3.3E-3</v>
       </c>
-      <c r="J61" s="65" t="s">
+      <c r="J61" s="64" t="s">
         <v>140</v>
       </c>
     </row>
@@ -4266,256 +4288,256 @@
       <c r="A62" s="12">
         <v>61</v>
       </c>
-      <c r="B62" s="63" t="s">
-        <v>126</v>
+      <c r="B62" s="62" t="s">
+        <v>87</v>
       </c>
       <c r="C62" s="6">
         <v>0.2</v>
       </c>
-      <c r="D62" s="63">
+      <c r="D62" s="62">
         <v>149</v>
       </c>
       <c r="E62" s="59" t="s">
-        <v>123</v>
-      </c>
-      <c r="F62" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="F62" s="63" t="s">
         <v>137</v>
       </c>
-      <c r="G62" s="63">
+      <c r="G62" s="62">
         <v>0.80630000000000002</v>
       </c>
-      <c r="H62" s="63">
+      <c r="H62" s="62">
         <v>0.16170000000000001</v>
       </c>
-      <c r="I62" s="63">
+      <c r="I62" s="62">
         <v>0.77239999999999998</v>
       </c>
-      <c r="J62" s="65" t="s">
+      <c r="J62" s="64" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="198" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" ht="198" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="12">
         <v>62</v>
       </c>
-      <c r="B63" s="59" t="s">
+      <c r="B63" s="58" t="s">
         <v>65</v>
       </c>
       <c r="C63" s="6">
         <v>0.2</v>
       </c>
-      <c r="D63" s="63">
+      <c r="D63" s="62">
         <v>149</v>
       </c>
       <c r="E63" s="63" t="s">
+        <v>156</v>
+      </c>
+      <c r="F63" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="F63" s="64" t="s">
+      <c r="G63" s="62">
+        <v>0.85099999999999998</v>
+      </c>
+      <c r="H63" s="62">
+        <v>3.3E-3</v>
+      </c>
+      <c r="I63" s="62">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="J63" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="G63" s="63">
-        <v>0.85099999999999998</v>
-      </c>
-      <c r="H63" s="63">
-        <v>3.3E-3</v>
-      </c>
-      <c r="I63" s="63">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="J63" s="65" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>63</v>
       </c>
-      <c r="B64" s="63" t="s">
-        <v>126</v>
+      <c r="B64" s="62" t="s">
+        <v>87</v>
       </c>
       <c r="C64" s="6">
         <v>0.2</v>
       </c>
-      <c r="D64" s="63">
+      <c r="D64" s="62">
         <v>149</v>
       </c>
       <c r="E64" s="63" t="s">
-        <v>141</v>
-      </c>
-      <c r="F64" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="F64" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="G64" s="62">
+        <v>0.61850000000000005</v>
+      </c>
+      <c r="H64" s="62">
+        <v>0</v>
+      </c>
+      <c r="I64" s="62">
+        <v>0</v>
+      </c>
+      <c r="J64" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="G64" s="63">
-        <v>0.61850000000000005</v>
-      </c>
-      <c r="H64" s="63">
-        <v>0</v>
-      </c>
-      <c r="I64" s="63">
-        <v>0</v>
-      </c>
-      <c r="J64" s="65" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="198" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:10" ht="198" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="12">
         <v>64</v>
       </c>
-      <c r="B65" s="59" t="s">
+      <c r="B65" s="58" t="s">
         <v>65</v>
       </c>
       <c r="C65" s="6">
         <v>0.2</v>
       </c>
-      <c r="D65" s="63">
+      <c r="D65" s="62">
         <v>149</v>
       </c>
       <c r="E65" s="63" t="s">
-        <v>123</v>
-      </c>
-      <c r="F65" s="64" t="s">
-        <v>142</v>
-      </c>
-      <c r="G65" s="63">
+        <v>27</v>
+      </c>
+      <c r="F65" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="G65" s="62">
         <v>0.85199999999999998</v>
       </c>
-      <c r="H65" s="63">
+      <c r="H65" s="62">
         <v>6.6E-3</v>
       </c>
-      <c r="I65" s="63">
+      <c r="I65" s="62">
         <v>3.3E-3</v>
       </c>
-      <c r="J65" s="65" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+      <c r="J65" s="64" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12">
         <v>65</v>
       </c>
-      <c r="B66" s="63" t="s">
-        <v>126</v>
+      <c r="B66" s="62" t="s">
+        <v>87</v>
       </c>
       <c r="C66" s="6">
         <v>0.2</v>
       </c>
-      <c r="D66" s="63">
+      <c r="D66" s="62">
         <v>149</v>
       </c>
       <c r="E66" s="63" t="s">
-        <v>123</v>
-      </c>
-      <c r="F66" s="64" t="s">
-        <v>144</v>
-      </c>
-      <c r="G66" s="63">
+        <v>27</v>
+      </c>
+      <c r="F66" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="G66" s="62">
         <v>0.64380000000000004</v>
       </c>
-      <c r="H66" s="63">
+      <c r="H66" s="62">
         <v>7.9500000000000001E-2</v>
       </c>
-      <c r="I66" s="63">
+      <c r="I66" s="62">
         <v>0.1047</v>
       </c>
-      <c r="J66" s="65" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="198" x14ac:dyDescent="0.3">
+      <c r="J66" s="64" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="198" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
-      <c r="B67" s="59" t="s">
+      <c r="B67" s="58" t="s">
         <v>65</v>
       </c>
       <c r="C67" s="6">
         <v>0.2</v>
       </c>
-      <c r="D67" s="63">
+      <c r="D67" s="62">
         <v>149</v>
       </c>
-      <c r="E67" s="63" t="s">
+      <c r="E67" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="F67" s="64" t="s">
-        <v>142</v>
-      </c>
-      <c r="G67" s="63">
+      <c r="F67" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="G67" s="62">
         <v>0.84119999999999995</v>
       </c>
-      <c r="H67" s="63">
+      <c r="H67" s="62">
         <v>5.3E-3</v>
       </c>
-      <c r="I67" s="63">
+      <c r="I67" s="62">
         <v>2.7000000000000001E-3</v>
       </c>
-      <c r="J67" s="66" t="s">
-        <v>148</v>
+      <c r="J67" s="65" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="132" x14ac:dyDescent="0.3">
       <c r="A68" s="12">
         <v>67</v>
       </c>
-      <c r="B68" s="63" t="s">
-        <v>126</v>
+      <c r="B68" s="62" t="s">
+        <v>87</v>
       </c>
       <c r="C68" s="6">
         <v>0.2</v>
       </c>
-      <c r="D68" s="63">
+      <c r="D68" s="62">
         <v>149</v>
       </c>
-      <c r="E68" s="63" t="s">
+      <c r="E68" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="F68" s="64" t="s">
-        <v>144</v>
-      </c>
-      <c r="G68" s="63">
+      <c r="F68" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="G68" s="62">
         <v>0.61219999999999997</v>
       </c>
-      <c r="H68" s="63">
+      <c r="H68" s="62">
         <v>0</v>
       </c>
-      <c r="I68" s="63">
+      <c r="I68" s="62">
         <v>0</v>
       </c>
-      <c r="J68" s="66" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="J68" s="65" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="12">
         <v>68</v>
       </c>
-      <c r="B69" s="59" t="s">
+      <c r="B69" s="58" t="s">
         <v>65</v>
       </c>
       <c r="C69" s="6">
         <v>0.2</v>
       </c>
-      <c r="D69" s="63">
+      <c r="D69" s="62">
         <v>149</v>
       </c>
       <c r="E69" s="63" t="s">
-        <v>141</v>
-      </c>
-      <c r="F69" s="64" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="G69" s="62">
+        <v>0.85040000000000004</v>
+      </c>
+      <c r="H69" s="62">
+        <v>0.2923</v>
+      </c>
+      <c r="I69" s="62">
+        <v>0.36709999999999998</v>
+      </c>
+      <c r="J69" s="64" t="s">
         <v>150</v>
-      </c>
-      <c r="G69" s="63">
-        <v>0.85040000000000004</v>
-      </c>
-      <c r="H69" s="63">
-        <v>0.2923</v>
-      </c>
-      <c r="I69" s="63">
-        <v>0.36709999999999998</v>
-      </c>
-      <c r="J69" s="65" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="155.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4523,7 +4545,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="C70">
         <v>0.2</v>
@@ -4531,11 +4553,11 @@
       <c r="D70">
         <v>149</v>
       </c>
-      <c r="E70" t="s">
-        <v>141</v>
-      </c>
-      <c r="F70" s="77" t="s">
-        <v>152</v>
+      <c r="E70" s="72" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70" s="72" t="s">
+        <v>151</v>
       </c>
       <c r="G70">
         <v>0.65249999999999997</v>
@@ -4546,11 +4568,11 @@
       <c r="I70">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="J70" s="65" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="203.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J70" s="64" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="203.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="12">
         <v>70</v>
       </c>
@@ -4563,11 +4585,11 @@
       <c r="D71">
         <v>149</v>
       </c>
-      <c r="E71" t="s">
-        <v>141</v>
-      </c>
-      <c r="F71" s="77" t="s">
-        <v>156</v>
+      <c r="E71" s="72" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="G71">
         <v>0.84019999999999995</v>
@@ -4578,16 +4600,16 @@
       <c r="I71">
         <v>0.74250000000000005</v>
       </c>
-      <c r="J71" s="65" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="142.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J71" s="64" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="142.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="12">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="C72">
         <v>0.2</v>
@@ -4595,11 +4617,11 @@
       <c r="D72">
         <v>149</v>
       </c>
-      <c r="E72" t="s">
-        <v>141</v>
-      </c>
-      <c r="F72" s="77" t="s">
-        <v>152</v>
+      <c r="E72" s="72" t="s">
+        <v>27</v>
+      </c>
+      <c r="F72" s="72" t="s">
+        <v>151</v>
       </c>
       <c r="G72">
         <v>0.63870000000000005</v>
@@ -4610,11 +4632,11 @@
       <c r="I72">
         <v>9.1399999999999995E-2</v>
       </c>
-      <c r="J72" s="65" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J72" s="64" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -4626,7 +4648,7 @@
       <c r="I73" s="6"/>
       <c r="J73" s="7"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -4638,7 +4660,7 @@
       <c r="I74" s="6"/>
       <c r="J74" s="7"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -4650,7 +4672,7 @@
       <c r="I75" s="6"/>
       <c r="J75" s="7"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -4662,7 +4684,7 @@
       <c r="I76" s="6"/>
       <c r="J76" s="7"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -4674,7 +4696,7 @@
       <c r="I77" s="6"/>
       <c r="J77" s="7"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -4686,7 +4708,7 @@
       <c r="I78" s="6"/>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -4698,7 +4720,7 @@
       <c r="I79" s="6"/>
       <c r="J79" s="7"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -4710,7 +4732,7 @@
       <c r="I80" s="6"/>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -4722,7 +4744,7 @@
       <c r="I81" s="6"/>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -4734,7 +4756,7 @@
       <c r="I82" s="6"/>
       <c r="J82" s="7"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -4746,7 +4768,7 @@
       <c r="I83" s="6"/>
       <c r="J83" s="7"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -4758,7 +4780,7 @@
       <c r="I84" s="6"/>
       <c r="J84" s="7"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -4770,7 +4792,7 @@
       <c r="I85" s="6"/>
       <c r="J85" s="7"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -4782,7 +4804,7 @@
       <c r="I86" s="6"/>
       <c r="J86" s="7"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -4794,7 +4816,7 @@
       <c r="I87" s="6"/>
       <c r="J87" s="7"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -4806,7 +4828,7 @@
       <c r="I88" s="6"/>
       <c r="J88" s="7"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -4818,7 +4840,7 @@
       <c r="I89" s="6"/>
       <c r="J89" s="7"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -4830,7 +4852,7 @@
       <c r="I90" s="6"/>
       <c r="J90" s="7"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -4842,7 +4864,7 @@
       <c r="I91" s="6"/>
       <c r="J91" s="7"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -4854,7 +4876,7 @@
       <c r="I92" s="6"/>
       <c r="J92" s="7"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -4866,7 +4888,7 @@
       <c r="I93" s="6"/>
       <c r="J93" s="7"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -4878,7 +4900,7 @@
       <c r="I94" s="6"/>
       <c r="J94" s="7"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -4890,7 +4912,7 @@
       <c r="I95" s="6"/>
       <c r="J95" s="7"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -4902,7 +4924,7 @@
       <c r="I96" s="6"/>
       <c r="J96" s="7"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -4914,7 +4936,7 @@
       <c r="I97" s="6"/>
       <c r="J97" s="7"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -4926,7 +4948,7 @@
       <c r="I98" s="6"/>
       <c r="J98" s="7"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -4938,7 +4960,7 @@
       <c r="I99" s="6"/>
       <c r="J99" s="7"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -4950,7 +4972,7 @@
       <c r="I100" s="6"/>
       <c r="J100" s="7"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -4962,7 +4984,7 @@
       <c r="I101" s="6"/>
       <c r="J101" s="7"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -4974,7 +4996,7 @@
       <c r="I102" s="6"/>
       <c r="J102" s="7"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -4986,7 +5008,7 @@
       <c r="I103" s="6"/>
       <c r="J103" s="7"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -4998,7 +5020,7 @@
       <c r="I104" s="6"/>
       <c r="J104" s="7"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -5010,7 +5032,7 @@
       <c r="I105" s="6"/>
       <c r="J105" s="7"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -5022,7 +5044,7 @@
       <c r="I106" s="6"/>
       <c r="J106" s="7"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -5034,7 +5056,7 @@
       <c r="I107" s="6"/>
       <c r="J107" s="7"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -5046,7 +5068,7 @@
       <c r="I108" s="6"/>
       <c r="J108" s="7"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -5058,7 +5080,7 @@
       <c r="I109" s="6"/>
       <c r="J109" s="7"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -5070,7 +5092,7 @@
       <c r="I110" s="6"/>
       <c r="J110" s="7"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -5082,7 +5104,7 @@
       <c r="I111" s="6"/>
       <c r="J111" s="7"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -5094,7 +5116,7 @@
       <c r="I112" s="6"/>
       <c r="J112" s="7"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -5106,7 +5128,7 @@
       <c r="I113" s="6"/>
       <c r="J113" s="7"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -5118,7 +5140,7 @@
       <c r="I114" s="6"/>
       <c r="J114" s="7"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -5130,7 +5152,7 @@
       <c r="I115" s="6"/>
       <c r="J115" s="7"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -5142,7 +5164,7 @@
       <c r="I116" s="6"/>
       <c r="J116" s="7"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -5154,7 +5176,7 @@
       <c r="I117" s="6"/>
       <c r="J117" s="7"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -5166,7 +5188,7 @@
       <c r="I118" s="6"/>
       <c r="J118" s="7"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -5178,7 +5200,7 @@
       <c r="I119" s="6"/>
       <c r="J119" s="7"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -5190,7 +5212,7 @@
       <c r="I120" s="6"/>
       <c r="J120" s="7"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -5202,7 +5224,7 @@
       <c r="I121" s="6"/>
       <c r="J121" s="7"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -5214,7 +5236,7 @@
       <c r="I122" s="6"/>
       <c r="J122" s="7"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -5226,7 +5248,7 @@
       <c r="I123" s="6"/>
       <c r="J123" s="7"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -5238,7 +5260,7 @@
       <c r="I124" s="6"/>
       <c r="J124" s="7"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -5250,7 +5272,7 @@
       <c r="I125" s="6"/>
       <c r="J125" s="7"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -5262,7 +5284,7 @@
       <c r="I126" s="6"/>
       <c r="J126" s="7"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -5274,7 +5296,7 @@
       <c r="I127" s="6"/>
       <c r="J127" s="7"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -5286,7 +5308,7 @@
       <c r="I128" s="6"/>
       <c r="J128" s="7"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -5298,7 +5320,7 @@
       <c r="I129" s="6"/>
       <c r="J129" s="7"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -5310,7 +5332,7 @@
       <c r="I130" s="6"/>
       <c r="J130" s="7"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -5322,7 +5344,7 @@
       <c r="I131" s="6"/>
       <c r="J131" s="7"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -5334,7 +5356,7 @@
       <c r="I132" s="6"/>
       <c r="J132" s="7"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -5346,7 +5368,7 @@
       <c r="I133" s="6"/>
       <c r="J133" s="7"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -5358,7 +5380,7 @@
       <c r="I134" s="6"/>
       <c r="J134" s="7"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -5370,7 +5392,7 @@
       <c r="I135" s="6"/>
       <c r="J135" s="7"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -5382,7 +5404,7 @@
       <c r="I136" s="6"/>
       <c r="J136" s="7"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -5394,7 +5416,7 @@
       <c r="I137" s="6"/>
       <c r="J137" s="7"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -5406,7 +5428,7 @@
       <c r="I138" s="6"/>
       <c r="J138" s="7"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -5418,7 +5440,7 @@
       <c r="I139" s="6"/>
       <c r="J139" s="7"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -5430,7 +5452,7 @@
       <c r="I140" s="6"/>
       <c r="J140" s="7"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -5442,7 +5464,7 @@
       <c r="I141" s="6"/>
       <c r="J141" s="7"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -5454,7 +5476,7 @@
       <c r="I142" s="6"/>
       <c r="J142" s="7"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -5466,7 +5488,7 @@
       <c r="I143" s="6"/>
       <c r="J143" s="7"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -5478,7 +5500,7 @@
       <c r="I144" s="6"/>
       <c r="J144" s="7"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -5490,7 +5512,7 @@
       <c r="I145" s="6"/>
       <c r="J145" s="7"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -5502,7 +5524,7 @@
       <c r="I146" s="6"/>
       <c r="J146" s="7"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -5514,7 +5536,7 @@
       <c r="I147" s="6"/>
       <c r="J147" s="7"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -5526,7 +5548,7 @@
       <c r="I148" s="6"/>
       <c r="J148" s="7"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -5538,7 +5560,7 @@
       <c r="I149" s="6"/>
       <c r="J149" s="7"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -5550,7 +5572,7 @@
       <c r="I150" s="6"/>
       <c r="J150" s="7"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -5562,7 +5584,7 @@
       <c r="I151" s="6"/>
       <c r="J151" s="7"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -5574,7 +5596,7 @@
       <c r="I152" s="6"/>
       <c r="J152" s="7"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -5586,7 +5608,7 @@
       <c r="I153" s="6"/>
       <c r="J153" s="7"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -5598,7 +5620,7 @@
       <c r="I154" s="6"/>
       <c r="J154" s="7"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -5610,7 +5632,7 @@
       <c r="I155" s="6"/>
       <c r="J155" s="7"/>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -5622,7 +5644,7 @@
       <c r="I156" s="6"/>
       <c r="J156" s="7"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -5634,7 +5656,7 @@
       <c r="I157" s="6"/>
       <c r="J157" s="7"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -5646,7 +5668,7 @@
       <c r="I158" s="6"/>
       <c r="J158" s="7"/>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -5658,7 +5680,7 @@
       <c r="I159" s="6"/>
       <c r="J159" s="7"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -5670,7 +5692,7 @@
       <c r="I160" s="6"/>
       <c r="J160" s="7"/>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -5682,7 +5704,7 @@
       <c r="I161" s="6"/>
       <c r="J161" s="7"/>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -5694,7 +5716,7 @@
       <c r="I162" s="6"/>
       <c r="J162" s="7"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -5706,7 +5728,7 @@
       <c r="I163" s="6"/>
       <c r="J163" s="7"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="4"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -5718,7 +5740,7 @@
       <c r="I164" s="6"/>
       <c r="J164" s="7"/>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -5730,7 +5752,7 @@
       <c r="I165" s="6"/>
       <c r="J165" s="7"/>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -5742,7 +5764,7 @@
       <c r="I166" s="6"/>
       <c r="J166" s="7"/>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -5754,7 +5776,7 @@
       <c r="I167" s="6"/>
       <c r="J167" s="7"/>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -5766,7 +5788,7 @@
       <c r="I168" s="6"/>
       <c r="J168" s="7"/>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -5778,7 +5800,7 @@
       <c r="I169" s="6"/>
       <c r="J169" s="7"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -5790,7 +5812,7 @@
       <c r="I170" s="6"/>
       <c r="J170" s="7"/>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -5802,7 +5824,7 @@
       <c r="I171" s="6"/>
       <c r="J171" s="7"/>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -5814,7 +5836,7 @@
       <c r="I172" s="6"/>
       <c r="J172" s="7"/>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -5826,7 +5848,7 @@
       <c r="I173" s="6"/>
       <c r="J173" s="7"/>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -5838,7 +5860,7 @@
       <c r="I174" s="6"/>
       <c r="J174" s="7"/>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -5850,7 +5872,7 @@
       <c r="I175" s="6"/>
       <c r="J175" s="7"/>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -5862,7 +5884,7 @@
       <c r="I176" s="6"/>
       <c r="J176" s="7"/>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -5874,7 +5896,7 @@
       <c r="I177" s="6"/>
       <c r="J177" s="7"/>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -5886,7 +5908,7 @@
       <c r="I178" s="6"/>
       <c r="J178" s="7"/>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -5898,7 +5920,7 @@
       <c r="I179" s="6"/>
       <c r="J179" s="7"/>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="4"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -5910,7 +5932,7 @@
       <c r="I180" s="6"/>
       <c r="J180" s="7"/>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -5922,7 +5944,7 @@
       <c r="I181" s="6"/>
       <c r="J181" s="7"/>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -5934,7 +5956,7 @@
       <c r="I182" s="6"/>
       <c r="J182" s="7"/>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -5946,7 +5968,7 @@
       <c r="I183" s="6"/>
       <c r="J183" s="7"/>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -5958,7 +5980,7 @@
       <c r="I184" s="6"/>
       <c r="J184" s="7"/>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -5970,7 +5992,7 @@
       <c r="I185" s="6"/>
       <c r="J185" s="7"/>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -5982,7 +6004,7 @@
       <c r="I186" s="6"/>
       <c r="J186" s="7"/>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -5994,7 +6016,7 @@
       <c r="I187" s="6"/>
       <c r="J187" s="7"/>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -6006,7 +6028,7 @@
       <c r="I188" s="6"/>
       <c r="J188" s="7"/>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -6018,7 +6040,7 @@
       <c r="I189" s="6"/>
       <c r="J189" s="7"/>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -6030,7 +6052,7 @@
       <c r="I190" s="6"/>
       <c r="J190" s="7"/>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="4"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -6042,7 +6064,7 @@
       <c r="I191" s="6"/>
       <c r="J191" s="7"/>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -6054,7 +6076,7 @@
       <c r="I192" s="6"/>
       <c r="J192" s="7"/>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="4"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -6066,7 +6088,7 @@
       <c r="I193" s="6"/>
       <c r="J193" s="7"/>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -6078,7 +6100,7 @@
       <c r="I194" s="6"/>
       <c r="J194" s="7"/>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -6090,7 +6112,7 @@
       <c r="I195" s="6"/>
       <c r="J195" s="7"/>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="4"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -6102,7 +6124,7 @@
       <c r="I196" s="6"/>
       <c r="J196" s="7"/>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -6114,7 +6136,7 @@
       <c r="I197" s="6"/>
       <c r="J197" s="7"/>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -6126,7 +6148,7 @@
       <c r="I198" s="6"/>
       <c r="J198" s="7"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -6138,7 +6160,7 @@
       <c r="I199" s="6"/>
       <c r="J199" s="7"/>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="4"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -6150,7 +6172,7 @@
       <c r="I200" s="6"/>
       <c r="J200" s="7"/>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -6162,7 +6184,7 @@
       <c r="I201" s="6"/>
       <c r="J201" s="7"/>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -6174,7 +6196,7 @@
       <c r="I202" s="6"/>
       <c r="J202" s="7"/>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -6186,7 +6208,7 @@
       <c r="I203" s="6"/>
       <c r="J203" s="7"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="4"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -6198,7 +6220,7 @@
       <c r="I204" s="6"/>
       <c r="J204" s="7"/>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -6210,7 +6232,7 @@
       <c r="I205" s="6"/>
       <c r="J205" s="7"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -6222,7 +6244,7 @@
       <c r="I206" s="6"/>
       <c r="J206" s="7"/>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -6234,7 +6256,7 @@
       <c r="I207" s="6"/>
       <c r="J207" s="7"/>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -6246,7 +6268,7 @@
       <c r="I208" s="6"/>
       <c r="J208" s="7"/>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -6258,7 +6280,7 @@
       <c r="I209" s="6"/>
       <c r="J209" s="7"/>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -6270,7 +6292,7 @@
       <c r="I210" s="6"/>
       <c r="J210" s="7"/>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -6282,7 +6304,7 @@
       <c r="I211" s="6"/>
       <c r="J211" s="7"/>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -6294,7 +6316,7 @@
       <c r="I212" s="6"/>
       <c r="J212" s="7"/>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -6306,7 +6328,7 @@
       <c r="I213" s="6"/>
       <c r="J213" s="7"/>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -6318,7 +6340,7 @@
       <c r="I214" s="6"/>
       <c r="J214" s="7"/>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -6330,7 +6352,7 @@
       <c r="I215" s="6"/>
       <c r="J215" s="7"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -6342,7 +6364,7 @@
       <c r="I216" s="6"/>
       <c r="J216" s="7"/>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -6354,7 +6376,7 @@
       <c r="I217" s="6"/>
       <c r="J217" s="7"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -6366,7 +6388,7 @@
       <c r="I218" s="6"/>
       <c r="J218" s="7"/>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -6378,7 +6400,7 @@
       <c r="I219" s="6"/>
       <c r="J219" s="7"/>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -6390,7 +6412,7 @@
       <c r="I220" s="6"/>
       <c r="J220" s="7"/>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -6402,7 +6424,7 @@
       <c r="I221" s="6"/>
       <c r="J221" s="7"/>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -6414,7 +6436,7 @@
       <c r="I222" s="6"/>
       <c r="J222" s="7"/>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -6426,7 +6448,7 @@
       <c r="I223" s="6"/>
       <c r="J223" s="7"/>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -6438,7 +6460,7 @@
       <c r="I224" s="6"/>
       <c r="J224" s="7"/>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -6450,7 +6472,7 @@
       <c r="I225" s="6"/>
       <c r="J225" s="7"/>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -6462,7 +6484,7 @@
       <c r="I226" s="6"/>
       <c r="J226" s="7"/>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="4"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -6474,7 +6496,7 @@
       <c r="I227" s="6"/>
       <c r="J227" s="7"/>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -6486,7 +6508,7 @@
       <c r="I228" s="6"/>
       <c r="J228" s="7"/>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -6498,7 +6520,7 @@
       <c r="I229" s="6"/>
       <c r="J229" s="7"/>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
@@ -6510,7 +6532,7 @@
       <c r="I230" s="6"/>
       <c r="J230" s="7"/>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -6522,7 +6544,7 @@
       <c r="I231" s="6"/>
       <c r="J231" s="7"/>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -6534,7 +6556,7 @@
       <c r="I232" s="6"/>
       <c r="J232" s="7"/>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -6546,7 +6568,7 @@
       <c r="I233" s="6"/>
       <c r="J233" s="7"/>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
@@ -6558,7 +6580,7 @@
       <c r="I234" s="6"/>
       <c r="J234" s="7"/>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -6570,7 +6592,7 @@
       <c r="I235" s="6"/>
       <c r="J235" s="7"/>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -6582,7 +6604,7 @@
       <c r="I236" s="6"/>
       <c r="J236" s="7"/>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -6594,7 +6616,7 @@
       <c r="I237" s="6"/>
       <c r="J237" s="7"/>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
@@ -6606,7 +6628,7 @@
       <c r="I238" s="6"/>
       <c r="J238" s="7"/>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -6618,7 +6640,7 @@
       <c r="I239" s="6"/>
       <c r="J239" s="7"/>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -6630,7 +6652,7 @@
       <c r="I240" s="6"/>
       <c r="J240" s="7"/>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -6642,7 +6664,7 @@
       <c r="I241" s="6"/>
       <c r="J241" s="7"/>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
@@ -6654,7 +6676,7 @@
       <c r="I242" s="6"/>
       <c r="J242" s="7"/>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -6666,7 +6688,7 @@
       <c r="I243" s="6"/>
       <c r="J243" s="7"/>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
@@ -6678,7 +6700,7 @@
       <c r="I244" s="6"/>
       <c r="J244" s="7"/>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
@@ -6690,7 +6712,7 @@
       <c r="I245" s="6"/>
       <c r="J245" s="7"/>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
@@ -6702,7 +6724,7 @@
       <c r="I246" s="6"/>
       <c r="J246" s="7"/>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -6714,7 +6736,7 @@
       <c r="I247" s="6"/>
       <c r="J247" s="7"/>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -6726,7 +6748,7 @@
       <c r="I248" s="6"/>
       <c r="J248" s="7"/>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -6738,7 +6760,7 @@
       <c r="I249" s="6"/>
       <c r="J249" s="7"/>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
@@ -6750,7 +6772,7 @@
       <c r="I250" s="6"/>
       <c r="J250" s="7"/>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
@@ -6762,7 +6784,7 @@
       <c r="I251" s="6"/>
       <c r="J251" s="7"/>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -6774,7 +6796,7 @@
       <c r="I252" s="6"/>
       <c r="J252" s="7"/>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -6786,7 +6808,7 @@
       <c r="I253" s="6"/>
       <c r="J253" s="7"/>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -6798,7 +6820,7 @@
       <c r="I254" s="6"/>
       <c r="J254" s="7"/>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -6810,7 +6832,7 @@
       <c r="I255" s="6"/>
       <c r="J255" s="7"/>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -6822,7 +6844,7 @@
       <c r="I256" s="6"/>
       <c r="J256" s="7"/>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -6834,7 +6856,7 @@
       <c r="I257" s="6"/>
       <c r="J257" s="7"/>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -6846,7 +6868,7 @@
       <c r="I258" s="6"/>
       <c r="J258" s="7"/>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -6858,7 +6880,7 @@
       <c r="I259" s="6"/>
       <c r="J259" s="7"/>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
@@ -6870,7 +6892,7 @@
       <c r="I260" s="6"/>
       <c r="J260" s="7"/>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
@@ -6882,7 +6904,7 @@
       <c r="I261" s="6"/>
       <c r="J261" s="7"/>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
@@ -6894,7 +6916,7 @@
       <c r="I262" s="6"/>
       <c r="J262" s="7"/>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
@@ -6906,7 +6928,7 @@
       <c r="I263" s="6"/>
       <c r="J263" s="7"/>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -6918,7 +6940,7 @@
       <c r="I264" s="6"/>
       <c r="J264" s="7"/>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -6930,7 +6952,7 @@
       <c r="I265" s="6"/>
       <c r="J265" s="7"/>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -6942,7 +6964,7 @@
       <c r="I266" s="6"/>
       <c r="J266" s="7"/>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
@@ -6954,7 +6976,7 @@
       <c r="I267" s="6"/>
       <c r="J267" s="7"/>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -6966,7 +6988,7 @@
       <c r="I268" s="6"/>
       <c r="J268" s="7"/>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
@@ -6978,7 +7000,7 @@
       <c r="I269" s="6"/>
       <c r="J269" s="7"/>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -6990,7 +7012,7 @@
       <c r="I270" s="6"/>
       <c r="J270" s="7"/>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
@@ -7002,7 +7024,7 @@
       <c r="I271" s="6"/>
       <c r="J271" s="7"/>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
@@ -7014,7 +7036,7 @@
       <c r="I272" s="6"/>
       <c r="J272" s="7"/>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
@@ -7026,7 +7048,7 @@
       <c r="I273" s="6"/>
       <c r="J273" s="7"/>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="4"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
@@ -7038,7 +7060,7 @@
       <c r="I274" s="6"/>
       <c r="J274" s="7"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="4"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
@@ -7050,7 +7072,7 @@
       <c r="I275" s="6"/>
       <c r="J275" s="7"/>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -7062,7 +7084,7 @@
       <c r="I276" s="6"/>
       <c r="J276" s="7"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -7074,7 +7096,7 @@
       <c r="I277" s="6"/>
       <c r="J277" s="7"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
@@ -7086,7 +7108,7 @@
       <c r="I278" s="6"/>
       <c r="J278" s="7"/>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -7098,7 +7120,7 @@
       <c r="I279" s="6"/>
       <c r="J279" s="7"/>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
@@ -7110,7 +7132,7 @@
       <c r="I280" s="6"/>
       <c r="J280" s="7"/>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="4"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
@@ -7122,7 +7144,7 @@
       <c r="I281" s="6"/>
       <c r="J281" s="7"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
@@ -7134,7 +7156,7 @@
       <c r="I282" s="6"/>
       <c r="J282" s="7"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
@@ -7146,7 +7168,7 @@
       <c r="I283" s="6"/>
       <c r="J283" s="7"/>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
@@ -7158,7 +7180,7 @@
       <c r="I284" s="6"/>
       <c r="J284" s="7"/>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -7170,7 +7192,7 @@
       <c r="I285" s="6"/>
       <c r="J285" s="7"/>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -7182,7 +7204,7 @@
       <c r="I286" s="6"/>
       <c r="J286" s="7"/>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="4"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -7194,7 +7216,7 @@
       <c r="I287" s="6"/>
       <c r="J287" s="7"/>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
@@ -7206,7 +7228,7 @@
       <c r="I288" s="6"/>
       <c r="J288" s="7"/>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
@@ -7218,7 +7240,7 @@
       <c r="I289" s="6"/>
       <c r="J289" s="7"/>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
@@ -7230,7 +7252,7 @@
       <c r="I290" s="6"/>
       <c r="J290" s="7"/>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -7242,7 +7264,7 @@
       <c r="I291" s="6"/>
       <c r="J291" s="7"/>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="4"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
@@ -7254,7 +7276,7 @@
       <c r="I292" s="6"/>
       <c r="J292" s="7"/>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="4"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
@@ -7266,7 +7288,7 @@
       <c r="I293" s="6"/>
       <c r="J293" s="7"/>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
@@ -7278,7 +7300,7 @@
       <c r="I294" s="6"/>
       <c r="J294" s="7"/>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
@@ -7290,7 +7312,7 @@
       <c r="I295" s="6"/>
       <c r="J295" s="7"/>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
@@ -7302,7 +7324,7 @@
       <c r="I296" s="6"/>
       <c r="J296" s="7"/>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="8"/>
       <c r="B297" s="9"/>
       <c r="C297" s="9"/>
@@ -7315,6 +7337,13 @@
       <c r="J297" s="11"/>
     </row>
   </sheetData>
+  <autoFilter ref="B1:B297" xr:uid="{BA66AA66-968F-43FC-BD0D-4CB9ADC09730}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Logistic Regression"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="K2:K18"/>
     <mergeCell ref="K31:K36"/>

--- a/SantanderCS/results/ResultListByTestModel_Final.xlsx
+++ b/SantanderCS/results/ResultListByTestModel_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\big20\git\big20-ML-project2-team3\SantanderCS\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29D820D-2B6B-44FB-B55C-A68B3F84C5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B106F089-419F-46FB-AF74-C2F2161724BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="345" windowWidth="28800" windowHeight="14190" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
+    <workbookView xWindow="75" yWindow="210" windowWidth="28935" windowHeight="14190" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -394,7 +394,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="157">
   <si>
     <t>NO</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1203,10 +1203,6 @@
   </si>
   <si>
     <t>models\XGBoost_95per_basic.pkl</t>
-  </si>
-  <si>
-    <t>Logistic Regression</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>log_reg = LogisticRegression(
@@ -3014,7 +3010,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A22" s="12">
         <v>21</v>
       </c>
@@ -3046,7 +3042,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="132" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -3078,7 +3074,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="148.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A24" s="12">
         <v>23</v>
       </c>
@@ -3403,7 +3399,7 @@
       </c>
       <c r="K33" s="76"/>
     </row>
-    <row r="34" spans="1:11" ht="99" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="99" x14ac:dyDescent="0.3">
       <c r="A34" s="12">
         <v>33</v>
       </c>
@@ -3436,7 +3432,7 @@
       </c>
       <c r="K34" s="76"/>
     </row>
-    <row r="35" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -3932,7 +3928,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="132" x14ac:dyDescent="0.3">
       <c r="A51" s="12">
         <v>50</v>
       </c>
@@ -3964,7 +3960,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="99" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" ht="99" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -3981,7 +3977,7 @@
         <v>123</v>
       </c>
       <c r="F52" s="63" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G52" s="62">
         <v>0.62160000000000004</v>
@@ -3993,10 +3989,10 @@
         <v>0</v>
       </c>
       <c r="J52" s="64" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A53" s="12">
         <v>52</v>
       </c>
@@ -4013,7 +4009,7 @@
         <v>123</v>
       </c>
       <c r="F53" s="63" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G53" s="62">
         <v>0.8528</v>
@@ -4025,7 +4021,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="J53" s="64" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="66" hidden="1" x14ac:dyDescent="0.3">
@@ -4045,7 +4041,7 @@
         <v>123</v>
       </c>
       <c r="F54" s="63" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G54" s="62">
         <v>0.60240000000000005</v>
@@ -4057,10 +4053,10 @@
         <v>0</v>
       </c>
       <c r="J54" s="64" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="132" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -4089,7 +4085,7 @@
         <v>0.01</v>
       </c>
       <c r="J55" s="64" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="99" hidden="1" x14ac:dyDescent="0.3">
@@ -4106,10 +4102,10 @@
         <v>149</v>
       </c>
       <c r="E56" s="59" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F56" s="63" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G56" s="62">
         <v>0.62290000000000001</v>
@@ -4121,10 +4117,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="64" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="132" x14ac:dyDescent="0.3">
       <c r="A57" s="12">
         <v>56</v>
       </c>
@@ -4138,10 +4134,10 @@
         <v>149</v>
       </c>
       <c r="E57" s="59" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F57" s="63" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G57" s="62">
         <v>0.85160000000000002</v>
@@ -4153,7 +4149,7 @@
         <v>6.6E-3</v>
       </c>
       <c r="J57" s="64" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
@@ -4170,10 +4166,10 @@
         <v>149</v>
       </c>
       <c r="E58" s="58" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F58" s="63" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G58" s="62">
         <v>0.64229999999999998</v>
@@ -4185,10 +4181,10 @@
         <v>0.1096</v>
       </c>
       <c r="J58" s="64" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="132" x14ac:dyDescent="0.3">
       <c r="A59" s="12">
         <v>58</v>
       </c>
@@ -4205,7 +4201,7 @@
         <v>27</v>
       </c>
       <c r="F59" s="63" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G59" s="62">
         <v>0.85219999999999996</v>
@@ -4217,10 +4213,10 @@
         <v>3.3E-3</v>
       </c>
       <c r="J59" s="64" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="82.5" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="12">
         <v>59</v>
       </c>
@@ -4237,7 +4233,7 @@
         <v>27</v>
       </c>
       <c r="F60" s="63" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G60" s="62">
         <v>0.80769999999999997</v>
@@ -4249,10 +4245,10 @@
         <v>0.16089999999999999</v>
       </c>
       <c r="J60" s="64" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="132" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -4266,10 +4262,10 @@
         <v>149</v>
       </c>
       <c r="E61" s="59" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F61" s="63" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G61" s="62">
         <v>0.85199999999999998</v>
@@ -4281,10 +4277,10 @@
         <v>3.3E-3</v>
       </c>
       <c r="J61" s="64" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="82.5" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="12">
         <v>61</v>
       </c>
@@ -4298,10 +4294,10 @@
         <v>149</v>
       </c>
       <c r="E62" s="59" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F62" s="63" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G62" s="62">
         <v>0.80630000000000002</v>
@@ -4313,10 +4309,10 @@
         <v>0.77239999999999998</v>
       </c>
       <c r="J62" s="64" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="198" hidden="1" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="198" x14ac:dyDescent="0.3">
       <c r="A63" s="12">
         <v>62</v>
       </c>
@@ -4330,10 +4326,10 @@
         <v>149</v>
       </c>
       <c r="E63" s="63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F63" s="63" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G63" s="62">
         <v>0.85099999999999998</v>
@@ -4345,7 +4341,7 @@
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="J63" s="64" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
@@ -4362,10 +4358,10 @@
         <v>149</v>
       </c>
       <c r="E64" s="63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F64" s="63" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G64" s="62">
         <v>0.61850000000000005</v>
@@ -4377,10 +4373,10 @@
         <v>0</v>
       </c>
       <c r="J64" s="64" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="198" hidden="1" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="198" x14ac:dyDescent="0.3">
       <c r="A65" s="12">
         <v>64</v>
       </c>
@@ -4397,7 +4393,7 @@
         <v>27</v>
       </c>
       <c r="F65" s="63" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G65" s="62">
         <v>0.85199999999999998</v>
@@ -4409,7 +4405,7 @@
         <v>3.3E-3</v>
       </c>
       <c r="J65" s="64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
@@ -4429,7 +4425,7 @@
         <v>27</v>
       </c>
       <c r="F66" s="63" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G66" s="62">
         <v>0.64380000000000004</v>
@@ -4441,10 +4437,10 @@
         <v>0.1047</v>
       </c>
       <c r="J66" s="64" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="198" hidden="1" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="198" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -4461,7 +4457,7 @@
         <v>123</v>
       </c>
       <c r="F67" s="63" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G67" s="62">
         <v>0.84119999999999995</v>
@@ -4473,10 +4469,10 @@
         <v>2.7000000000000001E-3</v>
       </c>
       <c r="J67" s="65" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="12">
         <v>67</v>
       </c>
@@ -4493,7 +4489,7 @@
         <v>123</v>
       </c>
       <c r="F68" s="63" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G68" s="62">
         <v>0.61219999999999997</v>
@@ -4505,10 +4501,10 @@
         <v>0</v>
       </c>
       <c r="J68" s="65" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="181.5" x14ac:dyDescent="0.3">
       <c r="A69" s="12">
         <v>68</v>
       </c>
@@ -4525,7 +4521,7 @@
         <v>27</v>
       </c>
       <c r="F69" s="63" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G69" s="62">
         <v>0.85040000000000004</v>
@@ -4537,10 +4533,10 @@
         <v>0.36709999999999998</v>
       </c>
       <c r="J69" s="64" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="155.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="155.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -4557,7 +4553,7 @@
         <v>27</v>
       </c>
       <c r="F70" s="72" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G70">
         <v>0.65249999999999997</v>
@@ -4569,10 +4565,10 @@
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="J70" s="64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="203.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="203.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="12">
         <v>70</v>
       </c>
@@ -4589,7 +4585,7 @@
         <v>27</v>
       </c>
       <c r="F71" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G71">
         <v>0.84019999999999995</v>
@@ -4601,7 +4597,7 @@
         <v>0.74250000000000005</v>
       </c>
       <c r="J71" s="64" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="142.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4621,7 +4617,7 @@
         <v>27</v>
       </c>
       <c r="F72" s="72" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G72">
         <v>0.63870000000000005</v>
@@ -4633,7 +4629,7 @@
         <v>9.1399999999999995E-2</v>
       </c>
       <c r="J72" s="64" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
@@ -7340,7 +7336,7 @@
   <autoFilter ref="B1:B297" xr:uid="{BA66AA66-968F-43FC-BD0D-4CB9ADC09730}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Logistic Regression"/>
+        <filter val="XGBoost"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/SantanderCS/results/ResultListByTestModel_Final.xlsx
+++ b/SantanderCS/results/ResultListByTestModel_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\big20\git\big20-ML-project2-team3\SantanderCS\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B106F089-419F-46FB-AF74-C2F2161724BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DA65EA-9762-4F70-9F38-A4891EFC7555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="75" yWindow="210" windowWidth="28935" windowHeight="14190" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
+    <workbookView xWindow="870" yWindow="1545" windowWidth="26760" windowHeight="11385" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1405,7 +1405,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1958,6 +1958,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="7" borderId="6" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1969,30 +1993,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="7" borderId="6" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2312,7 +2312,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA66AA66-968F-43FC-BD0D-4CB9ADC09730}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:K297"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.125" style="2" customWidth="1"/>
@@ -2327,7 +2327,7 @@
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="132" hidden="1">
       <c r="A2" s="12">
         <v>1</v>
       </c>
@@ -2393,11 +2393,11 @@
       <c r="J2" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="73" t="s">
+      <c r="K2" s="81" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="132" hidden="1">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -2428,42 +2428,42 @@
       <c r="J3" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="74"/>
-    </row>
-    <row r="4" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K3" s="82"/>
+    </row>
+    <row r="4" spans="1:11" ht="115.5">
       <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="78">
+      <c r="C4" s="74">
         <v>0.2</v>
       </c>
-      <c r="D4" s="77" t="s">
+      <c r="D4" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="79" t="s">
+      <c r="E4" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="79" t="s">
+      <c r="F4" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="78">
+      <c r="G4" s="74">
         <v>0.84219999999999995</v>
       </c>
-      <c r="H4" s="77" t="s">
+      <c r="H4" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="78">
+      <c r="I4" s="74">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="J4" s="80" t="s">
+      <c r="J4" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="74"/>
-    </row>
-    <row r="5" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K4" s="82"/>
+    </row>
+    <row r="5" spans="1:11" ht="115.5">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -2494,9 +2494,9 @@
       <c r="J5" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="74"/>
-    </row>
-    <row r="6" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K5" s="82"/>
+    </row>
+    <row r="6" spans="1:11" ht="82.5">
       <c r="A6" s="12">
         <v>5</v>
       </c>
@@ -2527,9 +2527,9 @@
       <c r="J6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="74"/>
-    </row>
-    <row r="7" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K6" s="82"/>
+    </row>
+    <row r="7" spans="1:11" ht="82.5">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2560,9 +2560,9 @@
       <c r="J7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="74"/>
-    </row>
-    <row r="8" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K7" s="82"/>
+    </row>
+    <row r="8" spans="1:11" ht="66">
       <c r="A8" s="12">
         <v>7</v>
       </c>
@@ -2593,9 +2593,9 @@
       <c r="J8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K8" s="74"/>
-    </row>
-    <row r="9" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K8" s="82"/>
+    </row>
+    <row r="9" spans="1:11" ht="115.5">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2626,9 +2626,9 @@
       <c r="J9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="K9" s="74"/>
-    </row>
-    <row r="10" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K9" s="82"/>
+    </row>
+    <row r="10" spans="1:11" ht="115.5">
       <c r="A10" s="12">
         <v>9</v>
       </c>
@@ -2659,9 +2659,9 @@
       <c r="J10" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="K10" s="74"/>
-    </row>
-    <row r="11" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K10" s="82"/>
+    </row>
+    <row r="11" spans="1:11" ht="115.5">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2692,9 +2692,9 @@
       <c r="J11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="K11" s="74"/>
-    </row>
-    <row r="12" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K11" s="82"/>
+    </row>
+    <row r="12" spans="1:11" ht="66">
       <c r="A12" s="12">
         <v>11</v>
       </c>
@@ -2725,9 +2725,9 @@
       <c r="J12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K12" s="74"/>
-    </row>
-    <row r="13" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="82"/>
+    </row>
+    <row r="13" spans="1:11" ht="82.5">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2758,9 +2758,9 @@
       <c r="J13" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="K13" s="74"/>
-    </row>
-    <row r="14" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="82"/>
+    </row>
+    <row r="14" spans="1:11" ht="115.5">
       <c r="A14" s="12">
         <v>13</v>
       </c>
@@ -2791,9 +2791,9 @@
       <c r="J14" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="K14" s="74"/>
-    </row>
-    <row r="15" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K14" s="82"/>
+    </row>
+    <row r="15" spans="1:11" ht="82.5">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -2822,9 +2822,9 @@
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="J15" s="7"/>
-      <c r="K15" s="74"/>
-    </row>
-    <row r="16" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K15" s="82"/>
+    </row>
+    <row r="16" spans="1:11" ht="82.5">
       <c r="A16" s="12">
         <v>15</v>
       </c>
@@ -2855,9 +2855,9 @@
       <c r="J16" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="K16" s="74"/>
-    </row>
-    <row r="17" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K16" s="82"/>
+    </row>
+    <row r="17" spans="1:11" ht="115.5">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -2882,9 +2882,9 @@
       <c r="J17" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="K17" s="74"/>
-    </row>
-    <row r="18" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K17" s="82"/>
+    </row>
+    <row r="18" spans="1:11" ht="115.5">
       <c r="A18" s="12">
         <v>17</v>
       </c>
@@ -2909,9 +2909,9 @@
       <c r="J18" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="K18" s="74"/>
-    </row>
-    <row r="19" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K18" s="82"/>
+    </row>
+    <row r="19" spans="1:11" ht="82.5">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="82.5">
       <c r="A20" s="12">
         <v>19</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="66">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="115.5" hidden="1">
       <c r="A22" s="12">
         <v>21</v>
       </c>
@@ -3042,39 +3042,39 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="132" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="132" hidden="1">
       <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" s="77" t="s">
+      <c r="B23" s="73" t="s">
         <v>65</v>
       </c>
       <c r="C23" s="67">
         <v>0.2</v>
       </c>
-      <c r="D23" s="77" t="s">
+      <c r="D23" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="77" t="s">
+      <c r="E23" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="F23" s="79" t="s">
+      <c r="F23" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="G23" s="77">
+      <c r="G23" s="73">
         <v>0.85089999999999999</v>
       </c>
-      <c r="H23" s="77">
+      <c r="H23" s="73">
         <v>0.2974</v>
       </c>
-      <c r="I23" s="77">
+      <c r="I23" s="73">
         <v>0.51500000000000001</v>
       </c>
-      <c r="J23" s="80" t="s">
+      <c r="J23" s="76" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="148.5" hidden="1">
       <c r="A24" s="12">
         <v>23</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="66" hidden="1">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="82.5" hidden="1">
       <c r="A26" s="12">
         <v>25</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="66" hidden="1">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="66" hidden="1">
       <c r="A28" s="12">
         <v>27</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="66" hidden="1">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="66" hidden="1">
       <c r="A30" s="12">
         <v>29</v>
       </c>
@@ -3298,7 +3298,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="82.5" hidden="1">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -3329,77 +3329,77 @@
       <c r="J31" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="K31" s="75" t="s">
+      <c r="K31" s="83" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="115.5" hidden="1">
       <c r="A32" s="12">
         <v>31</v>
       </c>
-      <c r="B32" s="81" t="s">
+      <c r="B32" s="77" t="s">
         <v>72</v>
       </c>
       <c r="C32" s="67">
         <v>0.2</v>
       </c>
-      <c r="D32" s="77" t="s">
+      <c r="D32" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="E32" s="81" t="s">
+      <c r="E32" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="F32" s="82" t="s">
+      <c r="F32" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="G32" s="81">
+      <c r="G32" s="77">
         <v>0.84379999999999999</v>
       </c>
-      <c r="H32" s="81">
+      <c r="H32" s="77">
         <v>9.9000000000000008E-3</v>
       </c>
-      <c r="I32" s="81">
+      <c r="I32" s="77">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J32" s="83" t="s">
+      <c r="J32" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="K32" s="76"/>
-    </row>
-    <row r="33" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K32" s="84"/>
+    </row>
+    <row r="33" spans="1:11" ht="132" hidden="1">
       <c r="A33" s="4">
         <v>32</v>
       </c>
-      <c r="B33" s="81" t="s">
+      <c r="B33" s="77" t="s">
         <v>87</v>
       </c>
       <c r="C33" s="67">
         <v>0.2</v>
       </c>
-      <c r="D33" s="77" t="s">
+      <c r="D33" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="E33" s="81" t="s">
+      <c r="E33" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="82" t="s">
+      <c r="F33" s="78" t="s">
         <v>89</v>
       </c>
-      <c r="G33" s="81">
+      <c r="G33" s="77">
         <v>0.80510000000000004</v>
       </c>
-      <c r="H33" s="81">
+      <c r="H33" s="77">
         <v>1.29E-2</v>
       </c>
-      <c r="I33" s="81">
+      <c r="I33" s="77">
         <v>6.6E-3</v>
       </c>
-      <c r="J33" s="83" t="s">
+      <c r="J33" s="79" t="s">
         <v>90</v>
       </c>
-      <c r="K33" s="76"/>
-    </row>
-    <row r="34" spans="1:11" ht="99" x14ac:dyDescent="0.3">
+      <c r="K33" s="84"/>
+    </row>
+    <row r="34" spans="1:11" ht="99" hidden="1">
       <c r="A34" s="12">
         <v>33</v>
       </c>
@@ -3430,9 +3430,9 @@
       <c r="J34" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="K34" s="76"/>
-    </row>
-    <row r="35" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="K34" s="84"/>
+    </row>
+    <row r="35" spans="1:11" ht="115.5" hidden="1">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -3463,9 +3463,9 @@
       <c r="J35" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="K35" s="76"/>
-    </row>
-    <row r="36" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K35" s="84"/>
+    </row>
+    <row r="36" spans="1:11" ht="66">
       <c r="A36" s="12">
         <v>35</v>
       </c>
@@ -3496,9 +3496,9 @@
       <c r="J36" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="K36" s="76"/>
-    </row>
-    <row r="37" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K36" s="84"/>
+    </row>
+    <row r="37" spans="1:11" ht="132" hidden="1">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="148.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="148.5" hidden="1">
       <c r="A38" s="12">
         <v>37</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="99" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="99" hidden="1">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="198" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="198" hidden="1">
       <c r="A40" s="12">
         <v>39</v>
       </c>
@@ -3626,7 +3626,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="99" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="99" hidden="1">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="181.5" hidden="1">
       <c r="A42" s="12">
         <v>41</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="198" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="198" hidden="1">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -3703,7 +3703,7 @@
       <c r="D43" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="E43" s="79" t="s">
+      <c r="E43" s="75" t="s">
         <v>37</v>
       </c>
       <c r="F43" s="70" t="s">
@@ -3718,11 +3718,11 @@
       <c r="I43" s="68">
         <v>0.362126</v>
       </c>
-      <c r="J43" s="84" t="s">
+      <c r="J43" s="80" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="132" hidden="1">
       <c r="A44" s="12">
         <v>43</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="181.5" hidden="1">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="181.5" hidden="1">
       <c r="A46" s="12">
         <v>45</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="181.5" hidden="1">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="181.5" hidden="1">
       <c r="A48" s="12">
         <v>47</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="181.5" hidden="1">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -3902,7 +3902,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="181.5" hidden="1">
       <c r="A50" s="12">
         <v>49</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="132" hidden="1">
       <c r="A51" s="12">
         <v>50</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="99" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" ht="99" hidden="1">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="115.5" hidden="1">
       <c r="A53" s="12">
         <v>52</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="66" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" ht="66" hidden="1">
       <c r="A54" s="12">
         <v>53</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="132" hidden="1">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -4088,7 +4088,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="99" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" ht="99" hidden="1">
       <c r="A56" s="12">
         <v>55</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" ht="132" hidden="1">
       <c r="A57" s="12">
         <v>56</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" ht="82.5" hidden="1">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="132" hidden="1">
       <c r="A59" s="12">
         <v>58</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" ht="82.5" hidden="1">
       <c r="A60" s="12">
         <v>59</v>
       </c>
@@ -4248,7 +4248,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="132" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" ht="132" hidden="1">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" ht="82.5" hidden="1">
       <c r="A62" s="12">
         <v>61</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="198" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" ht="198" hidden="1">
       <c r="A63" s="12">
         <v>62</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" ht="132" hidden="1">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="198" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" ht="198" hidden="1">
       <c r="A65" s="12">
         <v>64</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" ht="132" hidden="1">
       <c r="A66" s="12">
         <v>65</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="198" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" ht="198" hidden="1">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -4472,7 +4472,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" ht="132" hidden="1">
       <c r="A68" s="12">
         <v>67</v>
       </c>
@@ -4504,7 +4504,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="181.5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" ht="181.5" hidden="1">
       <c r="A69" s="12">
         <v>68</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="155.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" ht="155.25" hidden="1" customHeight="1">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -4568,7 +4568,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="203.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" ht="203.25" hidden="1" customHeight="1">
       <c r="A71" s="12">
         <v>70</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="142.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" ht="142.5" hidden="1" customHeight="1">
       <c r="A72" s="12">
         <v>71</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" hidden="1">
       <c r="A73" s="4"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -4644,7 +4644,7 @@
       <c r="I73" s="6"/>
       <c r="J73" s="7"/>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" hidden="1">
       <c r="A74" s="4"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -4656,7 +4656,7 @@
       <c r="I74" s="6"/>
       <c r="J74" s="7"/>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" hidden="1">
       <c r="A75" s="4"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -4668,7 +4668,7 @@
       <c r="I75" s="6"/>
       <c r="J75" s="7"/>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" hidden="1">
       <c r="A76" s="4"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -4680,7 +4680,7 @@
       <c r="I76" s="6"/>
       <c r="J76" s="7"/>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" hidden="1">
       <c r="A77" s="4"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -4692,7 +4692,7 @@
       <c r="I77" s="6"/>
       <c r="J77" s="7"/>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" hidden="1">
       <c r="A78" s="4"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -4704,7 +4704,7 @@
       <c r="I78" s="6"/>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" hidden="1">
       <c r="A79" s="4"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -4716,7 +4716,7 @@
       <c r="I79" s="6"/>
       <c r="J79" s="7"/>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" hidden="1">
       <c r="A80" s="4"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -4728,7 +4728,7 @@
       <c r="I80" s="6"/>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" hidden="1">
       <c r="A81" s="4"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -4740,7 +4740,7 @@
       <c r="I81" s="6"/>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" hidden="1">
       <c r="A82" s="4"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -4752,7 +4752,7 @@
       <c r="I82" s="6"/>
       <c r="J82" s="7"/>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" hidden="1">
       <c r="A83" s="4"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -4764,7 +4764,7 @@
       <c r="I83" s="6"/>
       <c r="J83" s="7"/>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" hidden="1">
       <c r="A84" s="4"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -4776,7 +4776,7 @@
       <c r="I84" s="6"/>
       <c r="J84" s="7"/>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" hidden="1">
       <c r="A85" s="4"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -4788,7 +4788,7 @@
       <c r="I85" s="6"/>
       <c r="J85" s="7"/>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" hidden="1">
       <c r="A86" s="4"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -4800,7 +4800,7 @@
       <c r="I86" s="6"/>
       <c r="J86" s="7"/>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" hidden="1">
       <c r="A87" s="4"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -4812,7 +4812,7 @@
       <c r="I87" s="6"/>
       <c r="J87" s="7"/>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" hidden="1">
       <c r="A88" s="4"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -4824,7 +4824,7 @@
       <c r="I88" s="6"/>
       <c r="J88" s="7"/>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" hidden="1">
       <c r="A89" s="4"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -4836,7 +4836,7 @@
       <c r="I89" s="6"/>
       <c r="J89" s="7"/>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" hidden="1">
       <c r="A90" s="4"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -4848,7 +4848,7 @@
       <c r="I90" s="6"/>
       <c r="J90" s="7"/>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" hidden="1">
       <c r="A91" s="4"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -4860,7 +4860,7 @@
       <c r="I91" s="6"/>
       <c r="J91" s="7"/>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" hidden="1">
       <c r="A92" s="4"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -4872,7 +4872,7 @@
       <c r="I92" s="6"/>
       <c r="J92" s="7"/>
     </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" hidden="1">
       <c r="A93" s="4"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -4884,7 +4884,7 @@
       <c r="I93" s="6"/>
       <c r="J93" s="7"/>
     </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" hidden="1">
       <c r="A94" s="4"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -4896,7 +4896,7 @@
       <c r="I94" s="6"/>
       <c r="J94" s="7"/>
     </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" hidden="1">
       <c r="A95" s="4"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -4908,7 +4908,7 @@
       <c r="I95" s="6"/>
       <c r="J95" s="7"/>
     </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" hidden="1">
       <c r="A96" s="4"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -4920,7 +4920,7 @@
       <c r="I96" s="6"/>
       <c r="J96" s="7"/>
     </row>
-    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" hidden="1">
       <c r="A97" s="4"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -4932,7 +4932,7 @@
       <c r="I97" s="6"/>
       <c r="J97" s="7"/>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" hidden="1">
       <c r="A98" s="4"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -4944,7 +4944,7 @@
       <c r="I98" s="6"/>
       <c r="J98" s="7"/>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" hidden="1">
       <c r="A99" s="4"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -4956,7 +4956,7 @@
       <c r="I99" s="6"/>
       <c r="J99" s="7"/>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" hidden="1">
       <c r="A100" s="4"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -4968,7 +4968,7 @@
       <c r="I100" s="6"/>
       <c r="J100" s="7"/>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" hidden="1">
       <c r="A101" s="4"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -4980,7 +4980,7 @@
       <c r="I101" s="6"/>
       <c r="J101" s="7"/>
     </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" hidden="1">
       <c r="A102" s="4"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -4992,7 +4992,7 @@
       <c r="I102" s="6"/>
       <c r="J102" s="7"/>
     </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" hidden="1">
       <c r="A103" s="4"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -5004,7 +5004,7 @@
       <c r="I103" s="6"/>
       <c r="J103" s="7"/>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" hidden="1">
       <c r="A104" s="4"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -5016,7 +5016,7 @@
       <c r="I104" s="6"/>
       <c r="J104" s="7"/>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" hidden="1">
       <c r="A105" s="4"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -5028,7 +5028,7 @@
       <c r="I105" s="6"/>
       <c r="J105" s="7"/>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" hidden="1">
       <c r="A106" s="4"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -5040,7 +5040,7 @@
       <c r="I106" s="6"/>
       <c r="J106" s="7"/>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" hidden="1">
       <c r="A107" s="4"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -5052,7 +5052,7 @@
       <c r="I107" s="6"/>
       <c r="J107" s="7"/>
     </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" hidden="1">
       <c r="A108" s="4"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -5064,7 +5064,7 @@
       <c r="I108" s="6"/>
       <c r="J108" s="7"/>
     </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" hidden="1">
       <c r="A109" s="4"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -5076,7 +5076,7 @@
       <c r="I109" s="6"/>
       <c r="J109" s="7"/>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" hidden="1">
       <c r="A110" s="4"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -5088,7 +5088,7 @@
       <c r="I110" s="6"/>
       <c r="J110" s="7"/>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" hidden="1">
       <c r="A111" s="4"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -5100,7 +5100,7 @@
       <c r="I111" s="6"/>
       <c r="J111" s="7"/>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" hidden="1">
       <c r="A112" s="4"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -5112,7 +5112,7 @@
       <c r="I112" s="6"/>
       <c r="J112" s="7"/>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" hidden="1">
       <c r="A113" s="4"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -5124,7 +5124,7 @@
       <c r="I113" s="6"/>
       <c r="J113" s="7"/>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" hidden="1">
       <c r="A114" s="4"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -5136,7 +5136,7 @@
       <c r="I114" s="6"/>
       <c r="J114" s="7"/>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" hidden="1">
       <c r="A115" s="4"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -5148,7 +5148,7 @@
       <c r="I115" s="6"/>
       <c r="J115" s="7"/>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" hidden="1">
       <c r="A116" s="4"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -5160,7 +5160,7 @@
       <c r="I116" s="6"/>
       <c r="J116" s="7"/>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" hidden="1">
       <c r="A117" s="4"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -5172,7 +5172,7 @@
       <c r="I117" s="6"/>
       <c r="J117" s="7"/>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" hidden="1">
       <c r="A118" s="4"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -5184,7 +5184,7 @@
       <c r="I118" s="6"/>
       <c r="J118" s="7"/>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" hidden="1">
       <c r="A119" s="4"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -5196,7 +5196,7 @@
       <c r="I119" s="6"/>
       <c r="J119" s="7"/>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" hidden="1">
       <c r="A120" s="4"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -5208,7 +5208,7 @@
       <c r="I120" s="6"/>
       <c r="J120" s="7"/>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" hidden="1">
       <c r="A121" s="4"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -5220,7 +5220,7 @@
       <c r="I121" s="6"/>
       <c r="J121" s="7"/>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" hidden="1">
       <c r="A122" s="4"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -5232,7 +5232,7 @@
       <c r="I122" s="6"/>
       <c r="J122" s="7"/>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" hidden="1">
       <c r="A123" s="4"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -5244,7 +5244,7 @@
       <c r="I123" s="6"/>
       <c r="J123" s="7"/>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" hidden="1">
       <c r="A124" s="4"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -5256,7 +5256,7 @@
       <c r="I124" s="6"/>
       <c r="J124" s="7"/>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" hidden="1">
       <c r="A125" s="4"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -5268,7 +5268,7 @@
       <c r="I125" s="6"/>
       <c r="J125" s="7"/>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" hidden="1">
       <c r="A126" s="4"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -5280,7 +5280,7 @@
       <c r="I126" s="6"/>
       <c r="J126" s="7"/>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" hidden="1">
       <c r="A127" s="4"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -5292,7 +5292,7 @@
       <c r="I127" s="6"/>
       <c r="J127" s="7"/>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" hidden="1">
       <c r="A128" s="4"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -5304,7 +5304,7 @@
       <c r="I128" s="6"/>
       <c r="J128" s="7"/>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" hidden="1">
       <c r="A129" s="4"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -5316,7 +5316,7 @@
       <c r="I129" s="6"/>
       <c r="J129" s="7"/>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" hidden="1">
       <c r="A130" s="4"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -5328,7 +5328,7 @@
       <c r="I130" s="6"/>
       <c r="J130" s="7"/>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" hidden="1">
       <c r="A131" s="4"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -5340,7 +5340,7 @@
       <c r="I131" s="6"/>
       <c r="J131" s="7"/>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" hidden="1">
       <c r="A132" s="4"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -5352,7 +5352,7 @@
       <c r="I132" s="6"/>
       <c r="J132" s="7"/>
     </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" hidden="1">
       <c r="A133" s="4"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -5364,7 +5364,7 @@
       <c r="I133" s="6"/>
       <c r="J133" s="7"/>
     </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" hidden="1">
       <c r="A134" s="4"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -5376,7 +5376,7 @@
       <c r="I134" s="6"/>
       <c r="J134" s="7"/>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" hidden="1">
       <c r="A135" s="4"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -5388,7 +5388,7 @@
       <c r="I135" s="6"/>
       <c r="J135" s="7"/>
     </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" hidden="1">
       <c r="A136" s="4"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -5400,7 +5400,7 @@
       <c r="I136" s="6"/>
       <c r="J136" s="7"/>
     </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" hidden="1">
       <c r="A137" s="4"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -5412,7 +5412,7 @@
       <c r="I137" s="6"/>
       <c r="J137" s="7"/>
     </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" hidden="1">
       <c r="A138" s="4"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -5424,7 +5424,7 @@
       <c r="I138" s="6"/>
       <c r="J138" s="7"/>
     </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" hidden="1">
       <c r="A139" s="4"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -5436,7 +5436,7 @@
       <c r="I139" s="6"/>
       <c r="J139" s="7"/>
     </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" hidden="1">
       <c r="A140" s="4"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -5448,7 +5448,7 @@
       <c r="I140" s="6"/>
       <c r="J140" s="7"/>
     </row>
-    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" hidden="1">
       <c r="A141" s="4"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -5460,7 +5460,7 @@
       <c r="I141" s="6"/>
       <c r="J141" s="7"/>
     </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" hidden="1">
       <c r="A142" s="4"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -5472,7 +5472,7 @@
       <c r="I142" s="6"/>
       <c r="J142" s="7"/>
     </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" hidden="1">
       <c r="A143" s="4"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -5484,7 +5484,7 @@
       <c r="I143" s="6"/>
       <c r="J143" s="7"/>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" hidden="1">
       <c r="A144" s="4"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -5496,7 +5496,7 @@
       <c r="I144" s="6"/>
       <c r="J144" s="7"/>
     </row>
-    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" hidden="1">
       <c r="A145" s="4"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -5508,7 +5508,7 @@
       <c r="I145" s="6"/>
       <c r="J145" s="7"/>
     </row>
-    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" hidden="1">
       <c r="A146" s="4"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -5520,7 +5520,7 @@
       <c r="I146" s="6"/>
       <c r="J146" s="7"/>
     </row>
-    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" hidden="1">
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -5532,7 +5532,7 @@
       <c r="I147" s="6"/>
       <c r="J147" s="7"/>
     </row>
-    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" hidden="1">
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -5544,7 +5544,7 @@
       <c r="I148" s="6"/>
       <c r="J148" s="7"/>
     </row>
-    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" hidden="1">
       <c r="A149" s="4"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -5556,7 +5556,7 @@
       <c r="I149" s="6"/>
       <c r="J149" s="7"/>
     </row>
-    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" hidden="1">
       <c r="A150" s="4"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -5568,7 +5568,7 @@
       <c r="I150" s="6"/>
       <c r="J150" s="7"/>
     </row>
-    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" hidden="1">
       <c r="A151" s="4"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -5580,7 +5580,7 @@
       <c r="I151" s="6"/>
       <c r="J151" s="7"/>
     </row>
-    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" hidden="1">
       <c r="A152" s="4"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -5592,7 +5592,7 @@
       <c r="I152" s="6"/>
       <c r="J152" s="7"/>
     </row>
-    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" hidden="1">
       <c r="A153" s="4"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -5604,7 +5604,7 @@
       <c r="I153" s="6"/>
       <c r="J153" s="7"/>
     </row>
-    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" hidden="1">
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -5616,7 +5616,7 @@
       <c r="I154" s="6"/>
       <c r="J154" s="7"/>
     </row>
-    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" hidden="1">
       <c r="A155" s="4"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -5628,7 +5628,7 @@
       <c r="I155" s="6"/>
       <c r="J155" s="7"/>
     </row>
-    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" hidden="1">
       <c r="A156" s="4"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -5640,7 +5640,7 @@
       <c r="I156" s="6"/>
       <c r="J156" s="7"/>
     </row>
-    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" hidden="1">
       <c r="A157" s="4"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -5652,7 +5652,7 @@
       <c r="I157" s="6"/>
       <c r="J157" s="7"/>
     </row>
-    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" hidden="1">
       <c r="A158" s="4"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -5664,7 +5664,7 @@
       <c r="I158" s="6"/>
       <c r="J158" s="7"/>
     </row>
-    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" hidden="1">
       <c r="A159" s="4"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -5676,7 +5676,7 @@
       <c r="I159" s="6"/>
       <c r="J159" s="7"/>
     </row>
-    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" hidden="1">
       <c r="A160" s="4"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -5688,7 +5688,7 @@
       <c r="I160" s="6"/>
       <c r="J160" s="7"/>
     </row>
-    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" hidden="1">
       <c r="A161" s="4"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -5700,7 +5700,7 @@
       <c r="I161" s="6"/>
       <c r="J161" s="7"/>
     </row>
-    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" hidden="1">
       <c r="A162" s="4"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -5712,7 +5712,7 @@
       <c r="I162" s="6"/>
       <c r="J162" s="7"/>
     </row>
-    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" hidden="1">
       <c r="A163" s="4"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -5724,7 +5724,7 @@
       <c r="I163" s="6"/>
       <c r="J163" s="7"/>
     </row>
-    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" hidden="1">
       <c r="A164" s="4"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -5736,7 +5736,7 @@
       <c r="I164" s="6"/>
       <c r="J164" s="7"/>
     </row>
-    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" hidden="1">
       <c r="A165" s="4"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -5748,7 +5748,7 @@
       <c r="I165" s="6"/>
       <c r="J165" s="7"/>
     </row>
-    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" hidden="1">
       <c r="A166" s="4"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -5760,7 +5760,7 @@
       <c r="I166" s="6"/>
       <c r="J166" s="7"/>
     </row>
-    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" hidden="1">
       <c r="A167" s="4"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -5772,7 +5772,7 @@
       <c r="I167" s="6"/>
       <c r="J167" s="7"/>
     </row>
-    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" hidden="1">
       <c r="A168" s="4"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -5784,7 +5784,7 @@
       <c r="I168" s="6"/>
       <c r="J168" s="7"/>
     </row>
-    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" hidden="1">
       <c r="A169" s="4"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -5796,7 +5796,7 @@
       <c r="I169" s="6"/>
       <c r="J169" s="7"/>
     </row>
-    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" hidden="1">
       <c r="A170" s="4"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -5808,7 +5808,7 @@
       <c r="I170" s="6"/>
       <c r="J170" s="7"/>
     </row>
-    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10" hidden="1">
       <c r="A171" s="4"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -5820,7 +5820,7 @@
       <c r="I171" s="6"/>
       <c r="J171" s="7"/>
     </row>
-    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" hidden="1">
       <c r="A172" s="4"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -5832,7 +5832,7 @@
       <c r="I172" s="6"/>
       <c r="J172" s="7"/>
     </row>
-    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" hidden="1">
       <c r="A173" s="4"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -5844,7 +5844,7 @@
       <c r="I173" s="6"/>
       <c r="J173" s="7"/>
     </row>
-    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" hidden="1">
       <c r="A174" s="4"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -5856,7 +5856,7 @@
       <c r="I174" s="6"/>
       <c r="J174" s="7"/>
     </row>
-    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" hidden="1">
       <c r="A175" s="4"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -5868,7 +5868,7 @@
       <c r="I175" s="6"/>
       <c r="J175" s="7"/>
     </row>
-    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" hidden="1">
       <c r="A176" s="4"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -5880,7 +5880,7 @@
       <c r="I176" s="6"/>
       <c r="J176" s="7"/>
     </row>
-    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" hidden="1">
       <c r="A177" s="4"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -5892,7 +5892,7 @@
       <c r="I177" s="6"/>
       <c r="J177" s="7"/>
     </row>
-    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" hidden="1">
       <c r="A178" s="4"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -5904,7 +5904,7 @@
       <c r="I178" s="6"/>
       <c r="J178" s="7"/>
     </row>
-    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" hidden="1">
       <c r="A179" s="4"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -5916,7 +5916,7 @@
       <c r="I179" s="6"/>
       <c r="J179" s="7"/>
     </row>
-    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" hidden="1">
       <c r="A180" s="4"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -5928,7 +5928,7 @@
       <c r="I180" s="6"/>
       <c r="J180" s="7"/>
     </row>
-    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" hidden="1">
       <c r="A181" s="4"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -5940,7 +5940,7 @@
       <c r="I181" s="6"/>
       <c r="J181" s="7"/>
     </row>
-    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" hidden="1">
       <c r="A182" s="4"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -5952,7 +5952,7 @@
       <c r="I182" s="6"/>
       <c r="J182" s="7"/>
     </row>
-    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" hidden="1">
       <c r="A183" s="4"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -5964,7 +5964,7 @@
       <c r="I183" s="6"/>
       <c r="J183" s="7"/>
     </row>
-    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" hidden="1">
       <c r="A184" s="4"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -5976,7 +5976,7 @@
       <c r="I184" s="6"/>
       <c r="J184" s="7"/>
     </row>
-    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" hidden="1">
       <c r="A185" s="4"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -5988,7 +5988,7 @@
       <c r="I185" s="6"/>
       <c r="J185" s="7"/>
     </row>
-    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" hidden="1">
       <c r="A186" s="4"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -6000,7 +6000,7 @@
       <c r="I186" s="6"/>
       <c r="J186" s="7"/>
     </row>
-    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" hidden="1">
       <c r="A187" s="4"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -6012,7 +6012,7 @@
       <c r="I187" s="6"/>
       <c r="J187" s="7"/>
     </row>
-    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" hidden="1">
       <c r="A188" s="4"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -6024,7 +6024,7 @@
       <c r="I188" s="6"/>
       <c r="J188" s="7"/>
     </row>
-    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" hidden="1">
       <c r="A189" s="4"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -6036,7 +6036,7 @@
       <c r="I189" s="6"/>
       <c r="J189" s="7"/>
     </row>
-    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" hidden="1">
       <c r="A190" s="4"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -6048,7 +6048,7 @@
       <c r="I190" s="6"/>
       <c r="J190" s="7"/>
     </row>
-    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" hidden="1">
       <c r="A191" s="4"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -6060,7 +6060,7 @@
       <c r="I191" s="6"/>
       <c r="J191" s="7"/>
     </row>
-    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" hidden="1">
       <c r="A192" s="4"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -6072,7 +6072,7 @@
       <c r="I192" s="6"/>
       <c r="J192" s="7"/>
     </row>
-    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" hidden="1">
       <c r="A193" s="4"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -6084,7 +6084,7 @@
       <c r="I193" s="6"/>
       <c r="J193" s="7"/>
     </row>
-    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" hidden="1">
       <c r="A194" s="4"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -6096,7 +6096,7 @@
       <c r="I194" s="6"/>
       <c r="J194" s="7"/>
     </row>
-    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" hidden="1">
       <c r="A195" s="4"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -6108,7 +6108,7 @@
       <c r="I195" s="6"/>
       <c r="J195" s="7"/>
     </row>
-    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" hidden="1">
       <c r="A196" s="4"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -6120,7 +6120,7 @@
       <c r="I196" s="6"/>
       <c r="J196" s="7"/>
     </row>
-    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" hidden="1">
       <c r="A197" s="4"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -6132,7 +6132,7 @@
       <c r="I197" s="6"/>
       <c r="J197" s="7"/>
     </row>
-    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" hidden="1">
       <c r="A198" s="4"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -6144,7 +6144,7 @@
       <c r="I198" s="6"/>
       <c r="J198" s="7"/>
     </row>
-    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" hidden="1">
       <c r="A199" s="4"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -6156,7 +6156,7 @@
       <c r="I199" s="6"/>
       <c r="J199" s="7"/>
     </row>
-    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" hidden="1">
       <c r="A200" s="4"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -6168,7 +6168,7 @@
       <c r="I200" s="6"/>
       <c r="J200" s="7"/>
     </row>
-    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" hidden="1">
       <c r="A201" s="4"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -6180,7 +6180,7 @@
       <c r="I201" s="6"/>
       <c r="J201" s="7"/>
     </row>
-    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" hidden="1">
       <c r="A202" s="4"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -6192,7 +6192,7 @@
       <c r="I202" s="6"/>
       <c r="J202" s="7"/>
     </row>
-    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" hidden="1">
       <c r="A203" s="4"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -6204,7 +6204,7 @@
       <c r="I203" s="6"/>
       <c r="J203" s="7"/>
     </row>
-    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" hidden="1">
       <c r="A204" s="4"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -6216,7 +6216,7 @@
       <c r="I204" s="6"/>
       <c r="J204" s="7"/>
     </row>
-    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" hidden="1">
       <c r="A205" s="4"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -6228,7 +6228,7 @@
       <c r="I205" s="6"/>
       <c r="J205" s="7"/>
     </row>
-    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" hidden="1">
       <c r="A206" s="4"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -6240,7 +6240,7 @@
       <c r="I206" s="6"/>
       <c r="J206" s="7"/>
     </row>
-    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" hidden="1">
       <c r="A207" s="4"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -6252,7 +6252,7 @@
       <c r="I207" s="6"/>
       <c r="J207" s="7"/>
     </row>
-    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" hidden="1">
       <c r="A208" s="4"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -6264,7 +6264,7 @@
       <c r="I208" s="6"/>
       <c r="J208" s="7"/>
     </row>
-    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" hidden="1">
       <c r="A209" s="4"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -6276,7 +6276,7 @@
       <c r="I209" s="6"/>
       <c r="J209" s="7"/>
     </row>
-    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" hidden="1">
       <c r="A210" s="4"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -6288,7 +6288,7 @@
       <c r="I210" s="6"/>
       <c r="J210" s="7"/>
     </row>
-    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" hidden="1">
       <c r="A211" s="4"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -6300,7 +6300,7 @@
       <c r="I211" s="6"/>
       <c r="J211" s="7"/>
     </row>
-    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" hidden="1">
       <c r="A212" s="4"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -6312,7 +6312,7 @@
       <c r="I212" s="6"/>
       <c r="J212" s="7"/>
     </row>
-    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" hidden="1">
       <c r="A213" s="4"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -6324,7 +6324,7 @@
       <c r="I213" s="6"/>
       <c r="J213" s="7"/>
     </row>
-    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" hidden="1">
       <c r="A214" s="4"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -6336,7 +6336,7 @@
       <c r="I214" s="6"/>
       <c r="J214" s="7"/>
     </row>
-    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" hidden="1">
       <c r="A215" s="4"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -6348,7 +6348,7 @@
       <c r="I215" s="6"/>
       <c r="J215" s="7"/>
     </row>
-    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" hidden="1">
       <c r="A216" s="4"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -6360,7 +6360,7 @@
       <c r="I216" s="6"/>
       <c r="J216" s="7"/>
     </row>
-    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" hidden="1">
       <c r="A217" s="4"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -6372,7 +6372,7 @@
       <c r="I217" s="6"/>
       <c r="J217" s="7"/>
     </row>
-    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" hidden="1">
       <c r="A218" s="4"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -6384,7 +6384,7 @@
       <c r="I218" s="6"/>
       <c r="J218" s="7"/>
     </row>
-    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" hidden="1">
       <c r="A219" s="4"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -6396,7 +6396,7 @@
       <c r="I219" s="6"/>
       <c r="J219" s="7"/>
     </row>
-    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" hidden="1">
       <c r="A220" s="4"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -6408,7 +6408,7 @@
       <c r="I220" s="6"/>
       <c r="J220" s="7"/>
     </row>
-    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" hidden="1">
       <c r="A221" s="4"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -6420,7 +6420,7 @@
       <c r="I221" s="6"/>
       <c r="J221" s="7"/>
     </row>
-    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" hidden="1">
       <c r="A222" s="4"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -6432,7 +6432,7 @@
       <c r="I222" s="6"/>
       <c r="J222" s="7"/>
     </row>
-    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" hidden="1">
       <c r="A223" s="4"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -6444,7 +6444,7 @@
       <c r="I223" s="6"/>
       <c r="J223" s="7"/>
     </row>
-    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" hidden="1">
       <c r="A224" s="4"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -6456,7 +6456,7 @@
       <c r="I224" s="6"/>
       <c r="J224" s="7"/>
     </row>
-    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" hidden="1">
       <c r="A225" s="4"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -6468,7 +6468,7 @@
       <c r="I225" s="6"/>
       <c r="J225" s="7"/>
     </row>
-    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" hidden="1">
       <c r="A226" s="4"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -6480,7 +6480,7 @@
       <c r="I226" s="6"/>
       <c r="J226" s="7"/>
     </row>
-    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" hidden="1">
       <c r="A227" s="4"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -6492,7 +6492,7 @@
       <c r="I227" s="6"/>
       <c r="J227" s="7"/>
     </row>
-    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" hidden="1">
       <c r="A228" s="4"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -6504,7 +6504,7 @@
       <c r="I228" s="6"/>
       <c r="J228" s="7"/>
     </row>
-    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" hidden="1">
       <c r="A229" s="4"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -6516,7 +6516,7 @@
       <c r="I229" s="6"/>
       <c r="J229" s="7"/>
     </row>
-    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" hidden="1">
       <c r="A230" s="4"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
@@ -6528,7 +6528,7 @@
       <c r="I230" s="6"/>
       <c r="J230" s="7"/>
     </row>
-    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" hidden="1">
       <c r="A231" s="4"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -6540,7 +6540,7 @@
       <c r="I231" s="6"/>
       <c r="J231" s="7"/>
     </row>
-    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" hidden="1">
       <c r="A232" s="4"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -6552,7 +6552,7 @@
       <c r="I232" s="6"/>
       <c r="J232" s="7"/>
     </row>
-    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" hidden="1">
       <c r="A233" s="4"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -6564,7 +6564,7 @@
       <c r="I233" s="6"/>
       <c r="J233" s="7"/>
     </row>
-    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" hidden="1">
       <c r="A234" s="4"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
@@ -6576,7 +6576,7 @@
       <c r="I234" s="6"/>
       <c r="J234" s="7"/>
     </row>
-    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" hidden="1">
       <c r="A235" s="4"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -6588,7 +6588,7 @@
       <c r="I235" s="6"/>
       <c r="J235" s="7"/>
     </row>
-    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" hidden="1">
       <c r="A236" s="4"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -6600,7 +6600,7 @@
       <c r="I236" s="6"/>
       <c r="J236" s="7"/>
     </row>
-    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" hidden="1">
       <c r="A237" s="4"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -6612,7 +6612,7 @@
       <c r="I237" s="6"/>
       <c r="J237" s="7"/>
     </row>
-    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" hidden="1">
       <c r="A238" s="4"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
@@ -6624,7 +6624,7 @@
       <c r="I238" s="6"/>
       <c r="J238" s="7"/>
     </row>
-    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" hidden="1">
       <c r="A239" s="4"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -6636,7 +6636,7 @@
       <c r="I239" s="6"/>
       <c r="J239" s="7"/>
     </row>
-    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" hidden="1">
       <c r="A240" s="4"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -6648,7 +6648,7 @@
       <c r="I240" s="6"/>
       <c r="J240" s="7"/>
     </row>
-    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10" hidden="1">
       <c r="A241" s="4"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -6660,7 +6660,7 @@
       <c r="I241" s="6"/>
       <c r="J241" s="7"/>
     </row>
-    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" hidden="1">
       <c r="A242" s="4"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
@@ -6672,7 +6672,7 @@
       <c r="I242" s="6"/>
       <c r="J242" s="7"/>
     </row>
-    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" hidden="1">
       <c r="A243" s="4"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -6684,7 +6684,7 @@
       <c r="I243" s="6"/>
       <c r="J243" s="7"/>
     </row>
-    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" hidden="1">
       <c r="A244" s="4"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
@@ -6696,7 +6696,7 @@
       <c r="I244" s="6"/>
       <c r="J244" s="7"/>
     </row>
-    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" hidden="1">
       <c r="A245" s="4"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
@@ -6708,7 +6708,7 @@
       <c r="I245" s="6"/>
       <c r="J245" s="7"/>
     </row>
-    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" hidden="1">
       <c r="A246" s="4"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
@@ -6720,7 +6720,7 @@
       <c r="I246" s="6"/>
       <c r="J246" s="7"/>
     </row>
-    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10" hidden="1">
       <c r="A247" s="4"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -6732,7 +6732,7 @@
       <c r="I247" s="6"/>
       <c r="J247" s="7"/>
     </row>
-    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" hidden="1">
       <c r="A248" s="4"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -6744,7 +6744,7 @@
       <c r="I248" s="6"/>
       <c r="J248" s="7"/>
     </row>
-    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10" hidden="1">
       <c r="A249" s="4"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -6756,7 +6756,7 @@
       <c r="I249" s="6"/>
       <c r="J249" s="7"/>
     </row>
-    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10" hidden="1">
       <c r="A250" s="4"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
@@ -6768,7 +6768,7 @@
       <c r="I250" s="6"/>
       <c r="J250" s="7"/>
     </row>
-    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" hidden="1">
       <c r="A251" s="4"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
@@ -6780,7 +6780,7 @@
       <c r="I251" s="6"/>
       <c r="J251" s="7"/>
     </row>
-    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10" hidden="1">
       <c r="A252" s="4"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -6792,7 +6792,7 @@
       <c r="I252" s="6"/>
       <c r="J252" s="7"/>
     </row>
-    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10" hidden="1">
       <c r="A253" s="4"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -6804,7 +6804,7 @@
       <c r="I253" s="6"/>
       <c r="J253" s="7"/>
     </row>
-    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10" hidden="1">
       <c r="A254" s="4"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -6816,7 +6816,7 @@
       <c r="I254" s="6"/>
       <c r="J254" s="7"/>
     </row>
-    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:10" hidden="1">
       <c r="A255" s="4"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -6828,7 +6828,7 @@
       <c r="I255" s="6"/>
       <c r="J255" s="7"/>
     </row>
-    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10" hidden="1">
       <c r="A256" s="4"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -6840,7 +6840,7 @@
       <c r="I256" s="6"/>
       <c r="J256" s="7"/>
     </row>
-    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10" hidden="1">
       <c r="A257" s="4"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -6852,7 +6852,7 @@
       <c r="I257" s="6"/>
       <c r="J257" s="7"/>
     </row>
-    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" hidden="1">
       <c r="A258" s="4"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -6864,7 +6864,7 @@
       <c r="I258" s="6"/>
       <c r="J258" s="7"/>
     </row>
-    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10" hidden="1">
       <c r="A259" s="4"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -6876,7 +6876,7 @@
       <c r="I259" s="6"/>
       <c r="J259" s="7"/>
     </row>
-    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" hidden="1">
       <c r="A260" s="4"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
@@ -6888,7 +6888,7 @@
       <c r="I260" s="6"/>
       <c r="J260" s="7"/>
     </row>
-    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" hidden="1">
       <c r="A261" s="4"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
@@ -6900,7 +6900,7 @@
       <c r="I261" s="6"/>
       <c r="J261" s="7"/>
     </row>
-    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" hidden="1">
       <c r="A262" s="4"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
@@ -6912,7 +6912,7 @@
       <c r="I262" s="6"/>
       <c r="J262" s="7"/>
     </row>
-    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10" hidden="1">
       <c r="A263" s="4"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
@@ -6924,7 +6924,7 @@
       <c r="I263" s="6"/>
       <c r="J263" s="7"/>
     </row>
-    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10" hidden="1">
       <c r="A264" s="4"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -6936,7 +6936,7 @@
       <c r="I264" s="6"/>
       <c r="J264" s="7"/>
     </row>
-    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10" hidden="1">
       <c r="A265" s="4"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -6948,7 +6948,7 @@
       <c r="I265" s="6"/>
       <c r="J265" s="7"/>
     </row>
-    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:10" hidden="1">
       <c r="A266" s="4"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -6960,7 +6960,7 @@
       <c r="I266" s="6"/>
       <c r="J266" s="7"/>
     </row>
-    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10" hidden="1">
       <c r="A267" s="4"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
@@ -6972,7 +6972,7 @@
       <c r="I267" s="6"/>
       <c r="J267" s="7"/>
     </row>
-    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" hidden="1">
       <c r="A268" s="4"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -6984,7 +6984,7 @@
       <c r="I268" s="6"/>
       <c r="J268" s="7"/>
     </row>
-    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" hidden="1">
       <c r="A269" s="4"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
@@ -6996,7 +6996,7 @@
       <c r="I269" s="6"/>
       <c r="J269" s="7"/>
     </row>
-    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:10" hidden="1">
       <c r="A270" s="4"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -7008,7 +7008,7 @@
       <c r="I270" s="6"/>
       <c r="J270" s="7"/>
     </row>
-    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10" hidden="1">
       <c r="A271" s="4"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
@@ -7020,7 +7020,7 @@
       <c r="I271" s="6"/>
       <c r="J271" s="7"/>
     </row>
-    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10" hidden="1">
       <c r="A272" s="4"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
@@ -7032,7 +7032,7 @@
       <c r="I272" s="6"/>
       <c r="J272" s="7"/>
     </row>
-    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10" hidden="1">
       <c r="A273" s="4"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
@@ -7044,7 +7044,7 @@
       <c r="I273" s="6"/>
       <c r="J273" s="7"/>
     </row>
-    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10" hidden="1">
       <c r="A274" s="4"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
@@ -7056,7 +7056,7 @@
       <c r="I274" s="6"/>
       <c r="J274" s="7"/>
     </row>
-    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10" hidden="1">
       <c r="A275" s="4"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
@@ -7068,7 +7068,7 @@
       <c r="I275" s="6"/>
       <c r="J275" s="7"/>
     </row>
-    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10" hidden="1">
       <c r="A276" s="4"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -7080,7 +7080,7 @@
       <c r="I276" s="6"/>
       <c r="J276" s="7"/>
     </row>
-    <row r="277" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10" hidden="1">
       <c r="A277" s="4"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -7092,7 +7092,7 @@
       <c r="I277" s="6"/>
       <c r="J277" s="7"/>
     </row>
-    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10" hidden="1">
       <c r="A278" s="4"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
@@ -7104,7 +7104,7 @@
       <c r="I278" s="6"/>
       <c r="J278" s="7"/>
     </row>
-    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10" hidden="1">
       <c r="A279" s="4"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -7116,7 +7116,7 @@
       <c r="I279" s="6"/>
       <c r="J279" s="7"/>
     </row>
-    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10" hidden="1">
       <c r="A280" s="4"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
@@ -7128,7 +7128,7 @@
       <c r="I280" s="6"/>
       <c r="J280" s="7"/>
     </row>
-    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10" hidden="1">
       <c r="A281" s="4"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
@@ -7140,7 +7140,7 @@
       <c r="I281" s="6"/>
       <c r="J281" s="7"/>
     </row>
-    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" hidden="1">
       <c r="A282" s="4"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
@@ -7152,7 +7152,7 @@
       <c r="I282" s="6"/>
       <c r="J282" s="7"/>
     </row>
-    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10" hidden="1">
       <c r="A283" s="4"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
@@ -7164,7 +7164,7 @@
       <c r="I283" s="6"/>
       <c r="J283" s="7"/>
     </row>
-    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:10" hidden="1">
       <c r="A284" s="4"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
@@ -7176,7 +7176,7 @@
       <c r="I284" s="6"/>
       <c r="J284" s="7"/>
     </row>
-    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10" hidden="1">
       <c r="A285" s="4"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -7188,7 +7188,7 @@
       <c r="I285" s="6"/>
       <c r="J285" s="7"/>
     </row>
-    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10" hidden="1">
       <c r="A286" s="4"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -7200,7 +7200,7 @@
       <c r="I286" s="6"/>
       <c r="J286" s="7"/>
     </row>
-    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10" hidden="1">
       <c r="A287" s="4"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -7212,7 +7212,7 @@
       <c r="I287" s="6"/>
       <c r="J287" s="7"/>
     </row>
-    <row r="288" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10" hidden="1">
       <c r="A288" s="4"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
@@ -7224,7 +7224,7 @@
       <c r="I288" s="6"/>
       <c r="J288" s="7"/>
     </row>
-    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10" hidden="1">
       <c r="A289" s="4"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
@@ -7236,7 +7236,7 @@
       <c r="I289" s="6"/>
       <c r="J289" s="7"/>
     </row>
-    <row r="290" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10" hidden="1">
       <c r="A290" s="4"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
@@ -7248,7 +7248,7 @@
       <c r="I290" s="6"/>
       <c r="J290" s="7"/>
     </row>
-    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" hidden="1">
       <c r="A291" s="4"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -7260,7 +7260,7 @@
       <c r="I291" s="6"/>
       <c r="J291" s="7"/>
     </row>
-    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" hidden="1">
       <c r="A292" s="4"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
@@ -7272,7 +7272,7 @@
       <c r="I292" s="6"/>
       <c r="J292" s="7"/>
     </row>
-    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" hidden="1">
       <c r="A293" s="4"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
@@ -7284,7 +7284,7 @@
       <c r="I293" s="6"/>
       <c r="J293" s="7"/>
     </row>
-    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10" hidden="1">
       <c r="A294" s="4"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
@@ -7296,7 +7296,7 @@
       <c r="I294" s="6"/>
       <c r="J294" s="7"/>
     </row>
-    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" hidden="1">
       <c r="A295" s="4"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
@@ -7308,7 +7308,7 @@
       <c r="I295" s="6"/>
       <c r="J295" s="7"/>
     </row>
-    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" hidden="1">
       <c r="A296" s="4"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
@@ -7320,7 +7320,7 @@
       <c r="I296" s="6"/>
       <c r="J296" s="7"/>
     </row>
-    <row r="297" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10" hidden="1">
       <c r="A297" s="8"/>
       <c r="B297" s="9"/>
       <c r="C297" s="9"/>
@@ -7336,7 +7336,7 @@
   <autoFilter ref="B1:B297" xr:uid="{BA66AA66-968F-43FC-BD0D-4CB9ADC09730}">
     <filterColumn colId="0">
       <filters>
-        <filter val="XGBoost"/>
+        <filter val="RandomForest"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/SantanderCS/results/ResultListByTestModel_Final.xlsx
+++ b/SantanderCS/results/ResultListByTestModel_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\big20\git\big20-ML-project2-team3\SantanderCS\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DA65EA-9762-4F70-9F38-A4891EFC7555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D11A273-9168-4B53-B352-B00D36344762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="1545" windowWidth="26760" windowHeight="11385" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
+    <workbookView xWindow="870" yWindow="1185" windowWidth="26760" windowHeight="11385" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -394,7 +394,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="158">
   <si>
     <t>NO</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1398,6 +1398,12 @@
   </si>
   <si>
     <t>Var3 / ZCR &gt; 99%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / ZCR &gt; 99% +
+Corr() &gt; 95% 컬럼 삭제
+undersampling</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2430,7 +2436,7 @@
       </c>
       <c r="K3" s="82"/>
     </row>
-    <row r="4" spans="1:11" ht="115.5">
+    <row r="4" spans="1:11" ht="115.5" hidden="1">
       <c r="A4" s="12">
         <v>3</v>
       </c>
@@ -2463,7 +2469,7 @@
       </c>
       <c r="K4" s="82"/>
     </row>
-    <row r="5" spans="1:11" ht="115.5">
+    <row r="5" spans="1:11" ht="115.5" hidden="1">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -2496,7 +2502,7 @@
       </c>
       <c r="K5" s="82"/>
     </row>
-    <row r="6" spans="1:11" ht="82.5">
+    <row r="6" spans="1:11" ht="82.5" hidden="1">
       <c r="A6" s="12">
         <v>5</v>
       </c>
@@ -2529,7 +2535,7 @@
       </c>
       <c r="K6" s="82"/>
     </row>
-    <row r="7" spans="1:11" ht="82.5">
+    <row r="7" spans="1:11" ht="82.5" hidden="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2562,7 +2568,7 @@
       </c>
       <c r="K7" s="82"/>
     </row>
-    <row r="8" spans="1:11" ht="66">
+    <row r="8" spans="1:11" ht="66" hidden="1">
       <c r="A8" s="12">
         <v>7</v>
       </c>
@@ -2595,7 +2601,7 @@
       </c>
       <c r="K8" s="82"/>
     </row>
-    <row r="9" spans="1:11" ht="115.5">
+    <row r="9" spans="1:11" ht="115.5" hidden="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2628,7 +2634,7 @@
       </c>
       <c r="K9" s="82"/>
     </row>
-    <row r="10" spans="1:11" ht="115.5">
+    <row r="10" spans="1:11" ht="115.5" hidden="1">
       <c r="A10" s="12">
         <v>9</v>
       </c>
@@ -2661,7 +2667,7 @@
       </c>
       <c r="K10" s="82"/>
     </row>
-    <row r="11" spans="1:11" ht="115.5">
+    <row r="11" spans="1:11" ht="115.5" hidden="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2694,7 +2700,7 @@
       </c>
       <c r="K11" s="82"/>
     </row>
-    <row r="12" spans="1:11" ht="66">
+    <row r="12" spans="1:11" ht="66" hidden="1">
       <c r="A12" s="12">
         <v>11</v>
       </c>
@@ -2727,7 +2733,7 @@
       </c>
       <c r="K12" s="82"/>
     </row>
-    <row r="13" spans="1:11" ht="82.5">
+    <row r="13" spans="1:11" ht="82.5" hidden="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2760,7 +2766,7 @@
       </c>
       <c r="K13" s="82"/>
     </row>
-    <row r="14" spans="1:11" ht="115.5">
+    <row r="14" spans="1:11" ht="115.5" hidden="1">
       <c r="A14" s="12">
         <v>13</v>
       </c>
@@ -2793,7 +2799,7 @@
       </c>
       <c r="K14" s="82"/>
     </row>
-    <row r="15" spans="1:11" ht="82.5">
+    <row r="15" spans="1:11" ht="82.5" hidden="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -2824,7 +2830,7 @@
       <c r="J15" s="7"/>
       <c r="K15" s="82"/>
     </row>
-    <row r="16" spans="1:11" ht="82.5">
+    <row r="16" spans="1:11" ht="82.5" hidden="1">
       <c r="A16" s="12">
         <v>15</v>
       </c>
@@ -2857,7 +2863,7 @@
       </c>
       <c r="K16" s="82"/>
     </row>
-    <row r="17" spans="1:11" ht="115.5">
+    <row r="17" spans="1:11" ht="115.5" hidden="1">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -2884,7 +2890,7 @@
       </c>
       <c r="K17" s="82"/>
     </row>
-    <row r="18" spans="1:11" ht="115.5">
+    <row r="18" spans="1:11" ht="115.5" hidden="1">
       <c r="A18" s="12">
         <v>17</v>
       </c>
@@ -2911,7 +2917,7 @@
       </c>
       <c r="K18" s="82"/>
     </row>
-    <row r="19" spans="1:11" ht="82.5">
+    <row r="19" spans="1:11" ht="82.5" hidden="1">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -2946,7 +2952,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="82.5">
+    <row r="20" spans="1:11" ht="82.5" hidden="1">
       <c r="A20" s="12">
         <v>19</v>
       </c>
@@ -2978,7 +2984,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="66">
+    <row r="21" spans="1:11" ht="66" hidden="1">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -3010,7 +3016,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="115.5" hidden="1">
+    <row r="22" spans="1:11" ht="115.5">
       <c r="A22" s="12">
         <v>21</v>
       </c>
@@ -3042,7 +3048,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="132" hidden="1">
+    <row r="23" spans="1:11" ht="132">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -3074,7 +3080,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="148.5" hidden="1">
+    <row r="24" spans="1:11" ht="148.5">
       <c r="A24" s="12">
         <v>23</v>
       </c>
@@ -3399,7 +3405,7 @@
       </c>
       <c r="K33" s="84"/>
     </row>
-    <row r="34" spans="1:11" ht="99" hidden="1">
+    <row r="34" spans="1:11" ht="99">
       <c r="A34" s="12">
         <v>33</v>
       </c>
@@ -3432,7 +3438,7 @@
       </c>
       <c r="K34" s="84"/>
     </row>
-    <row r="35" spans="1:11" ht="115.5" hidden="1">
+    <row r="35" spans="1:11" ht="115.5">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -3465,7 +3471,7 @@
       </c>
       <c r="K35" s="84"/>
     </row>
-    <row r="36" spans="1:11" ht="66">
+    <row r="36" spans="1:11" ht="66" hidden="1">
       <c r="A36" s="12">
         <v>35</v>
       </c>
@@ -3928,7 +3934,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="132" hidden="1">
+    <row r="51" spans="1:10" ht="132">
       <c r="A51" s="12">
         <v>50</v>
       </c>
@@ -3992,7 +3998,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="115.5" hidden="1">
+    <row r="53" spans="1:10" ht="115.5">
       <c r="A53" s="12">
         <v>52</v>
       </c>
@@ -4056,7 +4062,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="132" hidden="1">
+    <row r="55" spans="1:10" ht="132">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -4120,7 +4126,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="132" hidden="1">
+    <row r="57" spans="1:10" ht="132">
       <c r="A57" s="12">
         <v>56</v>
       </c>
@@ -4184,7 +4190,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="132" hidden="1">
+    <row r="59" spans="1:10" ht="132">
       <c r="A59" s="12">
         <v>58</v>
       </c>
@@ -4248,7 +4254,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="132" hidden="1">
+    <row r="61" spans="1:10" ht="132">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -4312,7 +4318,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="198" hidden="1">
+    <row r="63" spans="1:10" ht="198">
       <c r="A63" s="12">
         <v>62</v>
       </c>
@@ -4376,7 +4382,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="198" hidden="1">
+    <row r="65" spans="1:10" ht="198">
       <c r="A65" s="12">
         <v>64</v>
       </c>
@@ -4440,7 +4446,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="198" hidden="1">
+    <row r="67" spans="1:10" ht="198">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -4504,7 +4510,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="181.5" hidden="1">
+    <row r="69" spans="1:10" ht="181.5">
       <c r="A69" s="12">
         <v>68</v>
       </c>
@@ -4568,7 +4574,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="203.25" hidden="1" customHeight="1">
+    <row r="71" spans="1:10" ht="203.25" customHeight="1">
       <c r="A71" s="12">
         <v>70</v>
       </c>
@@ -4582,7 +4588,7 @@
         <v>149</v>
       </c>
       <c r="E71" s="72" t="s">
-        <v>27</v>
+        <v>157</v>
       </c>
       <c r="F71" s="72" t="s">
         <v>154</v>
@@ -7336,7 +7342,7 @@
   <autoFilter ref="B1:B297" xr:uid="{BA66AA66-968F-43FC-BD0D-4CB9ADC09730}">
     <filterColumn colId="0">
       <filters>
-        <filter val="RandomForest"/>
+        <filter val="XGBoost"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/SantanderCS/results/ResultListByTestModel_Final.xlsx
+++ b/SantanderCS/results/ResultListByTestModel_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\big20\git\big20-ML-project2-team3\SantanderCS\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D11A273-9168-4B53-B352-B00D36344762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C50715-1473-4FC6-AF96-8DE3F4ED68CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="1185" windowWidth="26760" windowHeight="11385" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
+    <workbookView xWindow="0" yWindow="210" windowWidth="28800" windowHeight="14190" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1411,7 +1411,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2318,7 +2318,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA66AA66-968F-43FC-BD0D-4CB9ADC09730}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:K297"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.125" style="2" customWidth="1"/>
@@ -2333,7 +2333,7 @@
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="132" hidden="1">
+    <row r="2" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>1</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="132" hidden="1">
+    <row r="3" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="K3" s="82"/>
     </row>
-    <row r="4" spans="1:11" ht="115.5" hidden="1">
+    <row r="4" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>3</v>
       </c>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="K4" s="82"/>
     </row>
-    <row r="5" spans="1:11" ht="115.5" hidden="1">
+    <row r="5" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K5" s="82"/>
     </row>
-    <row r="6" spans="1:11" ht="82.5" hidden="1">
+    <row r="6" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>5</v>
       </c>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="K6" s="82"/>
     </row>
-    <row r="7" spans="1:11" ht="82.5" hidden="1">
+    <row r="7" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="K7" s="82"/>
     </row>
-    <row r="8" spans="1:11" ht="66" hidden="1">
+    <row r="8" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>7</v>
       </c>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="K8" s="82"/>
     </row>
-    <row r="9" spans="1:11" ht="115.5" hidden="1">
+    <row r="9" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="K9" s="82"/>
     </row>
-    <row r="10" spans="1:11" ht="115.5" hidden="1">
+    <row r="10" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
         <v>9</v>
       </c>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="K10" s="82"/>
     </row>
-    <row r="11" spans="1:11" ht="115.5" hidden="1">
+    <row r="11" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="K11" s="82"/>
     </row>
-    <row r="12" spans="1:11" ht="66" hidden="1">
+    <row r="12" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12">
         <v>11</v>
       </c>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="K12" s="82"/>
     </row>
-    <row r="13" spans="1:11" ht="82.5" hidden="1">
+    <row r="13" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="K13" s="82"/>
     </row>
-    <row r="14" spans="1:11" ht="115.5" hidden="1">
+    <row r="14" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12">
         <v>13</v>
       </c>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="K14" s="82"/>
     </row>
-    <row r="15" spans="1:11" ht="82.5" hidden="1">
+    <row r="15" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -2830,7 +2830,7 @@
       <c r="J15" s="7"/>
       <c r="K15" s="82"/>
     </row>
-    <row r="16" spans="1:11" ht="82.5" hidden="1">
+    <row r="16" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12">
         <v>15</v>
       </c>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="K16" s="82"/>
     </row>
-    <row r="17" spans="1:11" ht="115.5" hidden="1">
+    <row r="17" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="K17" s="82"/>
     </row>
-    <row r="18" spans="1:11" ht="115.5" hidden="1">
+    <row r="18" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12">
         <v>17</v>
       </c>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="K18" s="82"/>
     </row>
-    <row r="19" spans="1:11" ht="82.5" hidden="1">
+    <row r="19" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="82.5" hidden="1">
+    <row r="20" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12">
         <v>19</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="66" hidden="1">
+    <row r="21" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="115.5">
+    <row r="22" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A22" s="12">
         <v>21</v>
       </c>
@@ -3048,7 +3048,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="132">
+    <row r="23" spans="1:11" ht="132" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="148.5">
+    <row r="24" spans="1:11" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A24" s="12">
         <v>23</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="66" hidden="1">
+    <row r="25" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="82.5" hidden="1">
+    <row r="26" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12">
         <v>25</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="66" hidden="1">
+    <row r="27" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="66" hidden="1">
+    <row r="28" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12">
         <v>27</v>
       </c>
@@ -3240,7 +3240,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="66" hidden="1">
+    <row r="29" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="66" hidden="1">
+    <row r="30" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12">
         <v>29</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="82.5" hidden="1">
+    <row r="31" spans="1:11" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="115.5" hidden="1">
+    <row r="32" spans="1:11" ht="115.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12">
         <v>31</v>
       </c>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="K32" s="84"/>
     </row>
-    <row r="33" spans="1:11" ht="132" hidden="1">
+    <row r="33" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="K33" s="84"/>
     </row>
-    <row r="34" spans="1:11" ht="99">
+    <row r="34" spans="1:11" ht="99" x14ac:dyDescent="0.3">
       <c r="A34" s="12">
         <v>33</v>
       </c>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="K34" s="84"/>
     </row>
-    <row r="35" spans="1:11" ht="115.5">
+    <row r="35" spans="1:11" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="K35" s="84"/>
     </row>
-    <row r="36" spans="1:11" ht="66" hidden="1">
+    <row r="36" spans="1:11" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="12">
         <v>35</v>
       </c>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="K36" s="84"/>
     </row>
-    <row r="37" spans="1:11" ht="132" hidden="1">
+    <row r="37" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="148.5" hidden="1">
+    <row r="38" spans="1:11" ht="148.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12">
         <v>37</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="99" hidden="1">
+    <row r="39" spans="1:11" ht="99" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="198" hidden="1">
+    <row r="40" spans="1:11" ht="198" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="12">
         <v>39</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="99" hidden="1">
+    <row r="41" spans="1:11" ht="99" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="181.5" hidden="1">
+    <row r="42" spans="1:11" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="12">
         <v>41</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="198" hidden="1">
+    <row r="43" spans="1:11" ht="198" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="132" hidden="1">
+    <row r="44" spans="1:11" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12">
         <v>43</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="181.5" hidden="1">
+    <row r="45" spans="1:11" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="181.5" hidden="1">
+    <row r="46" spans="1:11" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="12">
         <v>45</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="181.5" hidden="1">
+    <row r="47" spans="1:11" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="181.5" hidden="1">
+    <row r="48" spans="1:11" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="12">
         <v>47</v>
       </c>
@@ -3882,7 +3882,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="181.5" hidden="1">
+    <row r="49" spans="1:10" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="181.5" hidden="1">
+    <row r="50" spans="1:10" ht="181.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12">
         <v>49</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="132">
+    <row r="51" spans="1:10" ht="132" x14ac:dyDescent="0.3">
       <c r="A51" s="12">
         <v>50</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="99" hidden="1">
+    <row r="52" spans="1:10" ht="99" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="115.5">
+    <row r="53" spans="1:10" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A53" s="12">
         <v>52</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="66" hidden="1">
+    <row r="54" spans="1:10" ht="66" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="12">
         <v>53</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="132">
+    <row r="55" spans="1:10" ht="132" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="99" hidden="1">
+    <row r="56" spans="1:10" ht="99" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12">
         <v>55</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="132">
+    <row r="57" spans="1:10" ht="132" x14ac:dyDescent="0.3">
       <c r="A57" s="12">
         <v>56</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="82.5" hidden="1">
+    <row r="58" spans="1:10" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="132">
+    <row r="59" spans="1:10" ht="132" x14ac:dyDescent="0.3">
       <c r="A59" s="12">
         <v>58</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="82.5" hidden="1">
+    <row r="60" spans="1:10" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="12">
         <v>59</v>
       </c>
@@ -4254,7 +4254,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="132">
+    <row r="61" spans="1:10" ht="132" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="82.5" hidden="1">
+    <row r="62" spans="1:10" ht="82.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="12">
         <v>61</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="198">
+    <row r="63" spans="1:10" ht="198" x14ac:dyDescent="0.3">
       <c r="A63" s="12">
         <v>62</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="132" hidden="1">
+    <row r="64" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="198">
+    <row r="65" spans="1:10" ht="198" x14ac:dyDescent="0.3">
       <c r="A65" s="12">
         <v>64</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="132" hidden="1">
+    <row r="66" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12">
         <v>65</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="198">
+    <row r="67" spans="1:10" ht="198" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -4478,7 +4478,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="132" hidden="1">
+    <row r="68" spans="1:10" ht="132" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="12">
         <v>67</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="181.5">
+    <row r="69" spans="1:10" ht="181.5" x14ac:dyDescent="0.3">
       <c r="A69" s="12">
         <v>68</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="155.25" hidden="1" customHeight="1">
+    <row r="70" spans="1:10" ht="155.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="203.25" customHeight="1">
+    <row r="71" spans="1:10" ht="203.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="12">
         <v>70</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="142.5" hidden="1" customHeight="1">
+    <row r="72" spans="1:10" ht="142.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="12">
         <v>71</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -4650,7 +4650,7 @@
       <c r="I73" s="6"/>
       <c r="J73" s="7"/>
     </row>
-    <row r="74" spans="1:10" hidden="1">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -4662,7 +4662,7 @@
       <c r="I74" s="6"/>
       <c r="J74" s="7"/>
     </row>
-    <row r="75" spans="1:10" hidden="1">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -4674,7 +4674,7 @@
       <c r="I75" s="6"/>
       <c r="J75" s="7"/>
     </row>
-    <row r="76" spans="1:10" hidden="1">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -4686,7 +4686,7 @@
       <c r="I76" s="6"/>
       <c r="J76" s="7"/>
     </row>
-    <row r="77" spans="1:10" hidden="1">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -4698,7 +4698,7 @@
       <c r="I77" s="6"/>
       <c r="J77" s="7"/>
     </row>
-    <row r="78" spans="1:10" hidden="1">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -4710,7 +4710,7 @@
       <c r="I78" s="6"/>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" spans="1:10" hidden="1">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -4722,7 +4722,7 @@
       <c r="I79" s="6"/>
       <c r="J79" s="7"/>
     </row>
-    <row r="80" spans="1:10" hidden="1">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -4734,7 +4734,7 @@
       <c r="I80" s="6"/>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" spans="1:10" hidden="1">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -4746,7 +4746,7 @@
       <c r="I81" s="6"/>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" spans="1:10" hidden="1">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -4758,7 +4758,7 @@
       <c r="I82" s="6"/>
       <c r="J82" s="7"/>
     </row>
-    <row r="83" spans="1:10" hidden="1">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -4770,7 +4770,7 @@
       <c r="I83" s="6"/>
       <c r="J83" s="7"/>
     </row>
-    <row r="84" spans="1:10" hidden="1">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -4782,7 +4782,7 @@
       <c r="I84" s="6"/>
       <c r="J84" s="7"/>
     </row>
-    <row r="85" spans="1:10" hidden="1">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -4794,7 +4794,7 @@
       <c r="I85" s="6"/>
       <c r="J85" s="7"/>
     </row>
-    <row r="86" spans="1:10" hidden="1">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -4806,7 +4806,7 @@
       <c r="I86" s="6"/>
       <c r="J86" s="7"/>
     </row>
-    <row r="87" spans="1:10" hidden="1">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -4818,7 +4818,7 @@
       <c r="I87" s="6"/>
       <c r="J87" s="7"/>
     </row>
-    <row r="88" spans="1:10" hidden="1">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -4830,7 +4830,7 @@
       <c r="I88" s="6"/>
       <c r="J88" s="7"/>
     </row>
-    <row r="89" spans="1:10" hidden="1">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -4842,7 +4842,7 @@
       <c r="I89" s="6"/>
       <c r="J89" s="7"/>
     </row>
-    <row r="90" spans="1:10" hidden="1">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -4854,7 +4854,7 @@
       <c r="I90" s="6"/>
       <c r="J90" s="7"/>
     </row>
-    <row r="91" spans="1:10" hidden="1">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -4866,7 +4866,7 @@
       <c r="I91" s="6"/>
       <c r="J91" s="7"/>
     </row>
-    <row r="92" spans="1:10" hidden="1">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -4878,7 +4878,7 @@
       <c r="I92" s="6"/>
       <c r="J92" s="7"/>
     </row>
-    <row r="93" spans="1:10" hidden="1">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -4890,7 +4890,7 @@
       <c r="I93" s="6"/>
       <c r="J93" s="7"/>
     </row>
-    <row r="94" spans="1:10" hidden="1">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -4902,7 +4902,7 @@
       <c r="I94" s="6"/>
       <c r="J94" s="7"/>
     </row>
-    <row r="95" spans="1:10" hidden="1">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -4914,7 +4914,7 @@
       <c r="I95" s="6"/>
       <c r="J95" s="7"/>
     </row>
-    <row r="96" spans="1:10" hidden="1">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -4926,7 +4926,7 @@
       <c r="I96" s="6"/>
       <c r="J96" s="7"/>
     </row>
-    <row r="97" spans="1:10" hidden="1">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -4938,7 +4938,7 @@
       <c r="I97" s="6"/>
       <c r="J97" s="7"/>
     </row>
-    <row r="98" spans="1:10" hidden="1">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -4950,7 +4950,7 @@
       <c r="I98" s="6"/>
       <c r="J98" s="7"/>
     </row>
-    <row r="99" spans="1:10" hidden="1">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -4962,7 +4962,7 @@
       <c r="I99" s="6"/>
       <c r="J99" s="7"/>
     </row>
-    <row r="100" spans="1:10" hidden="1">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -4974,7 +4974,7 @@
       <c r="I100" s="6"/>
       <c r="J100" s="7"/>
     </row>
-    <row r="101" spans="1:10" hidden="1">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -4986,7 +4986,7 @@
       <c r="I101" s="6"/>
       <c r="J101" s="7"/>
     </row>
-    <row r="102" spans="1:10" hidden="1">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -4998,7 +4998,7 @@
       <c r="I102" s="6"/>
       <c r="J102" s="7"/>
     </row>
-    <row r="103" spans="1:10" hidden="1">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -5010,7 +5010,7 @@
       <c r="I103" s="6"/>
       <c r="J103" s="7"/>
     </row>
-    <row r="104" spans="1:10" hidden="1">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -5022,7 +5022,7 @@
       <c r="I104" s="6"/>
       <c r="J104" s="7"/>
     </row>
-    <row r="105" spans="1:10" hidden="1">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -5034,7 +5034,7 @@
       <c r="I105" s="6"/>
       <c r="J105" s="7"/>
     </row>
-    <row r="106" spans="1:10" hidden="1">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -5046,7 +5046,7 @@
       <c r="I106" s="6"/>
       <c r="J106" s="7"/>
     </row>
-    <row r="107" spans="1:10" hidden="1">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -5058,7 +5058,7 @@
       <c r="I107" s="6"/>
       <c r="J107" s="7"/>
     </row>
-    <row r="108" spans="1:10" hidden="1">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -5070,7 +5070,7 @@
       <c r="I108" s="6"/>
       <c r="J108" s="7"/>
     </row>
-    <row r="109" spans="1:10" hidden="1">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -5082,7 +5082,7 @@
       <c r="I109" s="6"/>
       <c r="J109" s="7"/>
     </row>
-    <row r="110" spans="1:10" hidden="1">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -5094,7 +5094,7 @@
       <c r="I110" s="6"/>
       <c r="J110" s="7"/>
     </row>
-    <row r="111" spans="1:10" hidden="1">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -5106,7 +5106,7 @@
       <c r="I111" s="6"/>
       <c r="J111" s="7"/>
     </row>
-    <row r="112" spans="1:10" hidden="1">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -5118,7 +5118,7 @@
       <c r="I112" s="6"/>
       <c r="J112" s="7"/>
     </row>
-    <row r="113" spans="1:10" hidden="1">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -5130,7 +5130,7 @@
       <c r="I113" s="6"/>
       <c r="J113" s="7"/>
     </row>
-    <row r="114" spans="1:10" hidden="1">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -5142,7 +5142,7 @@
       <c r="I114" s="6"/>
       <c r="J114" s="7"/>
     </row>
-    <row r="115" spans="1:10" hidden="1">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -5154,7 +5154,7 @@
       <c r="I115" s="6"/>
       <c r="J115" s="7"/>
     </row>
-    <row r="116" spans="1:10" hidden="1">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -5166,7 +5166,7 @@
       <c r="I116" s="6"/>
       <c r="J116" s="7"/>
     </row>
-    <row r="117" spans="1:10" hidden="1">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -5178,7 +5178,7 @@
       <c r="I117" s="6"/>
       <c r="J117" s="7"/>
     </row>
-    <row r="118" spans="1:10" hidden="1">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -5190,7 +5190,7 @@
       <c r="I118" s="6"/>
       <c r="J118" s="7"/>
     </row>
-    <row r="119" spans="1:10" hidden="1">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -5202,7 +5202,7 @@
       <c r="I119" s="6"/>
       <c r="J119" s="7"/>
     </row>
-    <row r="120" spans="1:10" hidden="1">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -5214,7 +5214,7 @@
       <c r="I120" s="6"/>
       <c r="J120" s="7"/>
     </row>
-    <row r="121" spans="1:10" hidden="1">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -5226,7 +5226,7 @@
       <c r="I121" s="6"/>
       <c r="J121" s="7"/>
     </row>
-    <row r="122" spans="1:10" hidden="1">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -5238,7 +5238,7 @@
       <c r="I122" s="6"/>
       <c r="J122" s="7"/>
     </row>
-    <row r="123" spans="1:10" hidden="1">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -5250,7 +5250,7 @@
       <c r="I123" s="6"/>
       <c r="J123" s="7"/>
     </row>
-    <row r="124" spans="1:10" hidden="1">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -5262,7 +5262,7 @@
       <c r="I124" s="6"/>
       <c r="J124" s="7"/>
     </row>
-    <row r="125" spans="1:10" hidden="1">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -5274,7 +5274,7 @@
       <c r="I125" s="6"/>
       <c r="J125" s="7"/>
     </row>
-    <row r="126" spans="1:10" hidden="1">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -5286,7 +5286,7 @@
       <c r="I126" s="6"/>
       <c r="J126" s="7"/>
     </row>
-    <row r="127" spans="1:10" hidden="1">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -5298,7 +5298,7 @@
       <c r="I127" s="6"/>
       <c r="J127" s="7"/>
     </row>
-    <row r="128" spans="1:10" hidden="1">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -5310,7 +5310,7 @@
       <c r="I128" s="6"/>
       <c r="J128" s="7"/>
     </row>
-    <row r="129" spans="1:10" hidden="1">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -5322,7 +5322,7 @@
       <c r="I129" s="6"/>
       <c r="J129" s="7"/>
     </row>
-    <row r="130" spans="1:10" hidden="1">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -5334,7 +5334,7 @@
       <c r="I130" s="6"/>
       <c r="J130" s="7"/>
     </row>
-    <row r="131" spans="1:10" hidden="1">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -5346,7 +5346,7 @@
       <c r="I131" s="6"/>
       <c r="J131" s="7"/>
     </row>
-    <row r="132" spans="1:10" hidden="1">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -5358,7 +5358,7 @@
       <c r="I132" s="6"/>
       <c r="J132" s="7"/>
     </row>
-    <row r="133" spans="1:10" hidden="1">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -5370,7 +5370,7 @@
       <c r="I133" s="6"/>
       <c r="J133" s="7"/>
     </row>
-    <row r="134" spans="1:10" hidden="1">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -5382,7 +5382,7 @@
       <c r="I134" s="6"/>
       <c r="J134" s="7"/>
     </row>
-    <row r="135" spans="1:10" hidden="1">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -5394,7 +5394,7 @@
       <c r="I135" s="6"/>
       <c r="J135" s="7"/>
     </row>
-    <row r="136" spans="1:10" hidden="1">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -5406,7 +5406,7 @@
       <c r="I136" s="6"/>
       <c r="J136" s="7"/>
     </row>
-    <row r="137" spans="1:10" hidden="1">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -5418,7 +5418,7 @@
       <c r="I137" s="6"/>
       <c r="J137" s="7"/>
     </row>
-    <row r="138" spans="1:10" hidden="1">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -5430,7 +5430,7 @@
       <c r="I138" s="6"/>
       <c r="J138" s="7"/>
     </row>
-    <row r="139" spans="1:10" hidden="1">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -5442,7 +5442,7 @@
       <c r="I139" s="6"/>
       <c r="J139" s="7"/>
     </row>
-    <row r="140" spans="1:10" hidden="1">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -5454,7 +5454,7 @@
       <c r="I140" s="6"/>
       <c r="J140" s="7"/>
     </row>
-    <row r="141" spans="1:10" hidden="1">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -5466,7 +5466,7 @@
       <c r="I141" s="6"/>
       <c r="J141" s="7"/>
     </row>
-    <row r="142" spans="1:10" hidden="1">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -5478,7 +5478,7 @@
       <c r="I142" s="6"/>
       <c r="J142" s="7"/>
     </row>
-    <row r="143" spans="1:10" hidden="1">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -5490,7 +5490,7 @@
       <c r="I143" s="6"/>
       <c r="J143" s="7"/>
     </row>
-    <row r="144" spans="1:10" hidden="1">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -5502,7 +5502,7 @@
       <c r="I144" s="6"/>
       <c r="J144" s="7"/>
     </row>
-    <row r="145" spans="1:10" hidden="1">
+    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -5514,7 +5514,7 @@
       <c r="I145" s="6"/>
       <c r="J145" s="7"/>
     </row>
-    <row r="146" spans="1:10" hidden="1">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -5526,7 +5526,7 @@
       <c r="I146" s="6"/>
       <c r="J146" s="7"/>
     </row>
-    <row r="147" spans="1:10" hidden="1">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -5538,7 +5538,7 @@
       <c r="I147" s="6"/>
       <c r="J147" s="7"/>
     </row>
-    <row r="148" spans="1:10" hidden="1">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -5550,7 +5550,7 @@
       <c r="I148" s="6"/>
       <c r="J148" s="7"/>
     </row>
-    <row r="149" spans="1:10" hidden="1">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -5562,7 +5562,7 @@
       <c r="I149" s="6"/>
       <c r="J149" s="7"/>
     </row>
-    <row r="150" spans="1:10" hidden="1">
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -5574,7 +5574,7 @@
       <c r="I150" s="6"/>
       <c r="J150" s="7"/>
     </row>
-    <row r="151" spans="1:10" hidden="1">
+    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -5586,7 +5586,7 @@
       <c r="I151" s="6"/>
       <c r="J151" s="7"/>
     </row>
-    <row r="152" spans="1:10" hidden="1">
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -5598,7 +5598,7 @@
       <c r="I152" s="6"/>
       <c r="J152" s="7"/>
     </row>
-    <row r="153" spans="1:10" hidden="1">
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -5610,7 +5610,7 @@
       <c r="I153" s="6"/>
       <c r="J153" s="7"/>
     </row>
-    <row r="154" spans="1:10" hidden="1">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -5622,7 +5622,7 @@
       <c r="I154" s="6"/>
       <c r="J154" s="7"/>
     </row>
-    <row r="155" spans="1:10" hidden="1">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -5634,7 +5634,7 @@
       <c r="I155" s="6"/>
       <c r="J155" s="7"/>
     </row>
-    <row r="156" spans="1:10" hidden="1">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -5646,7 +5646,7 @@
       <c r="I156" s="6"/>
       <c r="J156" s="7"/>
     </row>
-    <row r="157" spans="1:10" hidden="1">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -5658,7 +5658,7 @@
       <c r="I157" s="6"/>
       <c r="J157" s="7"/>
     </row>
-    <row r="158" spans="1:10" hidden="1">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -5670,7 +5670,7 @@
       <c r="I158" s="6"/>
       <c r="J158" s="7"/>
     </row>
-    <row r="159" spans="1:10" hidden="1">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -5682,7 +5682,7 @@
       <c r="I159" s="6"/>
       <c r="J159" s="7"/>
     </row>
-    <row r="160" spans="1:10" hidden="1">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -5694,7 +5694,7 @@
       <c r="I160" s="6"/>
       <c r="J160" s="7"/>
     </row>
-    <row r="161" spans="1:10" hidden="1">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -5706,7 +5706,7 @@
       <c r="I161" s="6"/>
       <c r="J161" s="7"/>
     </row>
-    <row r="162" spans="1:10" hidden="1">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -5718,7 +5718,7 @@
       <c r="I162" s="6"/>
       <c r="J162" s="7"/>
     </row>
-    <row r="163" spans="1:10" hidden="1">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -5730,7 +5730,7 @@
       <c r="I163" s="6"/>
       <c r="J163" s="7"/>
     </row>
-    <row r="164" spans="1:10" hidden="1">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="4"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -5742,7 +5742,7 @@
       <c r="I164" s="6"/>
       <c r="J164" s="7"/>
     </row>
-    <row r="165" spans="1:10" hidden="1">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -5754,7 +5754,7 @@
       <c r="I165" s="6"/>
       <c r="J165" s="7"/>
     </row>
-    <row r="166" spans="1:10" hidden="1">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -5766,7 +5766,7 @@
       <c r="I166" s="6"/>
       <c r="J166" s="7"/>
     </row>
-    <row r="167" spans="1:10" hidden="1">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -5778,7 +5778,7 @@
       <c r="I167" s="6"/>
       <c r="J167" s="7"/>
     </row>
-    <row r="168" spans="1:10" hidden="1">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -5790,7 +5790,7 @@
       <c r="I168" s="6"/>
       <c r="J168" s="7"/>
     </row>
-    <row r="169" spans="1:10" hidden="1">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -5802,7 +5802,7 @@
       <c r="I169" s="6"/>
       <c r="J169" s="7"/>
     </row>
-    <row r="170" spans="1:10" hidden="1">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -5814,7 +5814,7 @@
       <c r="I170" s="6"/>
       <c r="J170" s="7"/>
     </row>
-    <row r="171" spans="1:10" hidden="1">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -5826,7 +5826,7 @@
       <c r="I171" s="6"/>
       <c r="J171" s="7"/>
     </row>
-    <row r="172" spans="1:10" hidden="1">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -5838,7 +5838,7 @@
       <c r="I172" s="6"/>
       <c r="J172" s="7"/>
     </row>
-    <row r="173" spans="1:10" hidden="1">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -5850,7 +5850,7 @@
       <c r="I173" s="6"/>
       <c r="J173" s="7"/>
     </row>
-    <row r="174" spans="1:10" hidden="1">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -5862,7 +5862,7 @@
       <c r="I174" s="6"/>
       <c r="J174" s="7"/>
     </row>
-    <row r="175" spans="1:10" hidden="1">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -5874,7 +5874,7 @@
       <c r="I175" s="6"/>
       <c r="J175" s="7"/>
     </row>
-    <row r="176" spans="1:10" hidden="1">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -5886,7 +5886,7 @@
       <c r="I176" s="6"/>
       <c r="J176" s="7"/>
     </row>
-    <row r="177" spans="1:10" hidden="1">
+    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -5898,7 +5898,7 @@
       <c r="I177" s="6"/>
       <c r="J177" s="7"/>
     </row>
-    <row r="178" spans="1:10" hidden="1">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -5910,7 +5910,7 @@
       <c r="I178" s="6"/>
       <c r="J178" s="7"/>
     </row>
-    <row r="179" spans="1:10" hidden="1">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -5922,7 +5922,7 @@
       <c r="I179" s="6"/>
       <c r="J179" s="7"/>
     </row>
-    <row r="180" spans="1:10" hidden="1">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="4"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -5934,7 +5934,7 @@
       <c r="I180" s="6"/>
       <c r="J180" s="7"/>
     </row>
-    <row r="181" spans="1:10" hidden="1">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -5946,7 +5946,7 @@
       <c r="I181" s="6"/>
       <c r="J181" s="7"/>
     </row>
-    <row r="182" spans="1:10" hidden="1">
+    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -5958,7 +5958,7 @@
       <c r="I182" s="6"/>
       <c r="J182" s="7"/>
     </row>
-    <row r="183" spans="1:10" hidden="1">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -5970,7 +5970,7 @@
       <c r="I183" s="6"/>
       <c r="J183" s="7"/>
     </row>
-    <row r="184" spans="1:10" hidden="1">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -5982,7 +5982,7 @@
       <c r="I184" s="6"/>
       <c r="J184" s="7"/>
     </row>
-    <row r="185" spans="1:10" hidden="1">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -5994,7 +5994,7 @@
       <c r="I185" s="6"/>
       <c r="J185" s="7"/>
     </row>
-    <row r="186" spans="1:10" hidden="1">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -6006,7 +6006,7 @@
       <c r="I186" s="6"/>
       <c r="J186" s="7"/>
     </row>
-    <row r="187" spans="1:10" hidden="1">
+    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -6018,7 +6018,7 @@
       <c r="I187" s="6"/>
       <c r="J187" s="7"/>
     </row>
-    <row r="188" spans="1:10" hidden="1">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -6030,7 +6030,7 @@
       <c r="I188" s="6"/>
       <c r="J188" s="7"/>
     </row>
-    <row r="189" spans="1:10" hidden="1">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -6042,7 +6042,7 @@
       <c r="I189" s="6"/>
       <c r="J189" s="7"/>
     </row>
-    <row r="190" spans="1:10" hidden="1">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -6054,7 +6054,7 @@
       <c r="I190" s="6"/>
       <c r="J190" s="7"/>
     </row>
-    <row r="191" spans="1:10" hidden="1">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="4"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -6066,7 +6066,7 @@
       <c r="I191" s="6"/>
       <c r="J191" s="7"/>
     </row>
-    <row r="192" spans="1:10" hidden="1">
+    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -6078,7 +6078,7 @@
       <c r="I192" s="6"/>
       <c r="J192" s="7"/>
     </row>
-    <row r="193" spans="1:10" hidden="1">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="4"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -6090,7 +6090,7 @@
       <c r="I193" s="6"/>
       <c r="J193" s="7"/>
     </row>
-    <row r="194" spans="1:10" hidden="1">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -6102,7 +6102,7 @@
       <c r="I194" s="6"/>
       <c r="J194" s="7"/>
     </row>
-    <row r="195" spans="1:10" hidden="1">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -6114,7 +6114,7 @@
       <c r="I195" s="6"/>
       <c r="J195" s="7"/>
     </row>
-    <row r="196" spans="1:10" hidden="1">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="4"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -6126,7 +6126,7 @@
       <c r="I196" s="6"/>
       <c r="J196" s="7"/>
     </row>
-    <row r="197" spans="1:10" hidden="1">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -6138,7 +6138,7 @@
       <c r="I197" s="6"/>
       <c r="J197" s="7"/>
     </row>
-    <row r="198" spans="1:10" hidden="1">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -6150,7 +6150,7 @@
       <c r="I198" s="6"/>
       <c r="J198" s="7"/>
     </row>
-    <row r="199" spans="1:10" hidden="1">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -6162,7 +6162,7 @@
       <c r="I199" s="6"/>
       <c r="J199" s="7"/>
     </row>
-    <row r="200" spans="1:10" hidden="1">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="4"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -6174,7 +6174,7 @@
       <c r="I200" s="6"/>
       <c r="J200" s="7"/>
     </row>
-    <row r="201" spans="1:10" hidden="1">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -6186,7 +6186,7 @@
       <c r="I201" s="6"/>
       <c r="J201" s="7"/>
     </row>
-    <row r="202" spans="1:10" hidden="1">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -6198,7 +6198,7 @@
       <c r="I202" s="6"/>
       <c r="J202" s="7"/>
     </row>
-    <row r="203" spans="1:10" hidden="1">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -6210,7 +6210,7 @@
       <c r="I203" s="6"/>
       <c r="J203" s="7"/>
     </row>
-    <row r="204" spans="1:10" hidden="1">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="4"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -6222,7 +6222,7 @@
       <c r="I204" s="6"/>
       <c r="J204" s="7"/>
     </row>
-    <row r="205" spans="1:10" hidden="1">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -6234,7 +6234,7 @@
       <c r="I205" s="6"/>
       <c r="J205" s="7"/>
     </row>
-    <row r="206" spans="1:10" hidden="1">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -6246,7 +6246,7 @@
       <c r="I206" s="6"/>
       <c r="J206" s="7"/>
     </row>
-    <row r="207" spans="1:10" hidden="1">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -6258,7 +6258,7 @@
       <c r="I207" s="6"/>
       <c r="J207" s="7"/>
     </row>
-    <row r="208" spans="1:10" hidden="1">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -6270,7 +6270,7 @@
       <c r="I208" s="6"/>
       <c r="J208" s="7"/>
     </row>
-    <row r="209" spans="1:10" hidden="1">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -6282,7 +6282,7 @@
       <c r="I209" s="6"/>
       <c r="J209" s="7"/>
     </row>
-    <row r="210" spans="1:10" hidden="1">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -6294,7 +6294,7 @@
       <c r="I210" s="6"/>
       <c r="J210" s="7"/>
     </row>
-    <row r="211" spans="1:10" hidden="1">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -6306,7 +6306,7 @@
       <c r="I211" s="6"/>
       <c r="J211" s="7"/>
     </row>
-    <row r="212" spans="1:10" hidden="1">
+    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -6318,7 +6318,7 @@
       <c r="I212" s="6"/>
       <c r="J212" s="7"/>
     </row>
-    <row r="213" spans="1:10" hidden="1">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -6330,7 +6330,7 @@
       <c r="I213" s="6"/>
       <c r="J213" s="7"/>
     </row>
-    <row r="214" spans="1:10" hidden="1">
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -6342,7 +6342,7 @@
       <c r="I214" s="6"/>
       <c r="J214" s="7"/>
     </row>
-    <row r="215" spans="1:10" hidden="1">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -6354,7 +6354,7 @@
       <c r="I215" s="6"/>
       <c r="J215" s="7"/>
     </row>
-    <row r="216" spans="1:10" hidden="1">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -6366,7 +6366,7 @@
       <c r="I216" s="6"/>
       <c r="J216" s="7"/>
     </row>
-    <row r="217" spans="1:10" hidden="1">
+    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -6378,7 +6378,7 @@
       <c r="I217" s="6"/>
       <c r="J217" s="7"/>
     </row>
-    <row r="218" spans="1:10" hidden="1">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -6390,7 +6390,7 @@
       <c r="I218" s="6"/>
       <c r="J218" s="7"/>
     </row>
-    <row r="219" spans="1:10" hidden="1">
+    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -6402,7 +6402,7 @@
       <c r="I219" s="6"/>
       <c r="J219" s="7"/>
     </row>
-    <row r="220" spans="1:10" hidden="1">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -6414,7 +6414,7 @@
       <c r="I220" s="6"/>
       <c r="J220" s="7"/>
     </row>
-    <row r="221" spans="1:10" hidden="1">
+    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -6426,7 +6426,7 @@
       <c r="I221" s="6"/>
       <c r="J221" s="7"/>
     </row>
-    <row r="222" spans="1:10" hidden="1">
+    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -6438,7 +6438,7 @@
       <c r="I222" s="6"/>
       <c r="J222" s="7"/>
     </row>
-    <row r="223" spans="1:10" hidden="1">
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -6450,7 +6450,7 @@
       <c r="I223" s="6"/>
       <c r="J223" s="7"/>
     </row>
-    <row r="224" spans="1:10" hidden="1">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -6462,7 +6462,7 @@
       <c r="I224" s="6"/>
       <c r="J224" s="7"/>
     </row>
-    <row r="225" spans="1:10" hidden="1">
+    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -6474,7 +6474,7 @@
       <c r="I225" s="6"/>
       <c r="J225" s="7"/>
     </row>
-    <row r="226" spans="1:10" hidden="1">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -6486,7 +6486,7 @@
       <c r="I226" s="6"/>
       <c r="J226" s="7"/>
     </row>
-    <row r="227" spans="1:10" hidden="1">
+    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="4"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -6498,7 +6498,7 @@
       <c r="I227" s="6"/>
       <c r="J227" s="7"/>
     </row>
-    <row r="228" spans="1:10" hidden="1">
+    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -6510,7 +6510,7 @@
       <c r="I228" s="6"/>
       <c r="J228" s="7"/>
     </row>
-    <row r="229" spans="1:10" hidden="1">
+    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -6522,7 +6522,7 @@
       <c r="I229" s="6"/>
       <c r="J229" s="7"/>
     </row>
-    <row r="230" spans="1:10" hidden="1">
+    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
@@ -6534,7 +6534,7 @@
       <c r="I230" s="6"/>
       <c r="J230" s="7"/>
     </row>
-    <row r="231" spans="1:10" hidden="1">
+    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -6546,7 +6546,7 @@
       <c r="I231" s="6"/>
       <c r="J231" s="7"/>
     </row>
-    <row r="232" spans="1:10" hidden="1">
+    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -6558,7 +6558,7 @@
       <c r="I232" s="6"/>
       <c r="J232" s="7"/>
     </row>
-    <row r="233" spans="1:10" hidden="1">
+    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -6570,7 +6570,7 @@
       <c r="I233" s="6"/>
       <c r="J233" s="7"/>
     </row>
-    <row r="234" spans="1:10" hidden="1">
+    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
@@ -6582,7 +6582,7 @@
       <c r="I234" s="6"/>
       <c r="J234" s="7"/>
     </row>
-    <row r="235" spans="1:10" hidden="1">
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -6594,7 +6594,7 @@
       <c r="I235" s="6"/>
       <c r="J235" s="7"/>
     </row>
-    <row r="236" spans="1:10" hidden="1">
+    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -6606,7 +6606,7 @@
       <c r="I236" s="6"/>
       <c r="J236" s="7"/>
     </row>
-    <row r="237" spans="1:10" hidden="1">
+    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -6618,7 +6618,7 @@
       <c r="I237" s="6"/>
       <c r="J237" s="7"/>
     </row>
-    <row r="238" spans="1:10" hidden="1">
+    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
@@ -6630,7 +6630,7 @@
       <c r="I238" s="6"/>
       <c r="J238" s="7"/>
     </row>
-    <row r="239" spans="1:10" hidden="1">
+    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -6642,7 +6642,7 @@
       <c r="I239" s="6"/>
       <c r="J239" s="7"/>
     </row>
-    <row r="240" spans="1:10" hidden="1">
+    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -6654,7 +6654,7 @@
       <c r="I240" s="6"/>
       <c r="J240" s="7"/>
     </row>
-    <row r="241" spans="1:10" hidden="1">
+    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -6666,7 +6666,7 @@
       <c r="I241" s="6"/>
       <c r="J241" s="7"/>
     </row>
-    <row r="242" spans="1:10" hidden="1">
+    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
@@ -6678,7 +6678,7 @@
       <c r="I242" s="6"/>
       <c r="J242" s="7"/>
     </row>
-    <row r="243" spans="1:10" hidden="1">
+    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -6690,7 +6690,7 @@
       <c r="I243" s="6"/>
       <c r="J243" s="7"/>
     </row>
-    <row r="244" spans="1:10" hidden="1">
+    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
@@ -6702,7 +6702,7 @@
       <c r="I244" s="6"/>
       <c r="J244" s="7"/>
     </row>
-    <row r="245" spans="1:10" hidden="1">
+    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
@@ -6714,7 +6714,7 @@
       <c r="I245" s="6"/>
       <c r="J245" s="7"/>
     </row>
-    <row r="246" spans="1:10" hidden="1">
+    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
@@ -6726,7 +6726,7 @@
       <c r="I246" s="6"/>
       <c r="J246" s="7"/>
     </row>
-    <row r="247" spans="1:10" hidden="1">
+    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -6738,7 +6738,7 @@
       <c r="I247" s="6"/>
       <c r="J247" s="7"/>
     </row>
-    <row r="248" spans="1:10" hidden="1">
+    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -6750,7 +6750,7 @@
       <c r="I248" s="6"/>
       <c r="J248" s="7"/>
     </row>
-    <row r="249" spans="1:10" hidden="1">
+    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -6762,7 +6762,7 @@
       <c r="I249" s="6"/>
       <c r="J249" s="7"/>
     </row>
-    <row r="250" spans="1:10" hidden="1">
+    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
@@ -6774,7 +6774,7 @@
       <c r="I250" s="6"/>
       <c r="J250" s="7"/>
     </row>
-    <row r="251" spans="1:10" hidden="1">
+    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
@@ -6786,7 +6786,7 @@
       <c r="I251" s="6"/>
       <c r="J251" s="7"/>
     </row>
-    <row r="252" spans="1:10" hidden="1">
+    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -6798,7 +6798,7 @@
       <c r="I252" s="6"/>
       <c r="J252" s="7"/>
     </row>
-    <row r="253" spans="1:10" hidden="1">
+    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -6810,7 +6810,7 @@
       <c r="I253" s="6"/>
       <c r="J253" s="7"/>
     </row>
-    <row r="254" spans="1:10" hidden="1">
+    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -6822,7 +6822,7 @@
       <c r="I254" s="6"/>
       <c r="J254" s="7"/>
     </row>
-    <row r="255" spans="1:10" hidden="1">
+    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -6834,7 +6834,7 @@
       <c r="I255" s="6"/>
       <c r="J255" s="7"/>
     </row>
-    <row r="256" spans="1:10" hidden="1">
+    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -6846,7 +6846,7 @@
       <c r="I256" s="6"/>
       <c r="J256" s="7"/>
     </row>
-    <row r="257" spans="1:10" hidden="1">
+    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -6858,7 +6858,7 @@
       <c r="I257" s="6"/>
       <c r="J257" s="7"/>
     </row>
-    <row r="258" spans="1:10" hidden="1">
+    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -6870,7 +6870,7 @@
       <c r="I258" s="6"/>
       <c r="J258" s="7"/>
     </row>
-    <row r="259" spans="1:10" hidden="1">
+    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -6882,7 +6882,7 @@
       <c r="I259" s="6"/>
       <c r="J259" s="7"/>
     </row>
-    <row r="260" spans="1:10" hidden="1">
+    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
@@ -6894,7 +6894,7 @@
       <c r="I260" s="6"/>
       <c r="J260" s="7"/>
     </row>
-    <row r="261" spans="1:10" hidden="1">
+    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
@@ -6906,7 +6906,7 @@
       <c r="I261" s="6"/>
       <c r="J261" s="7"/>
     </row>
-    <row r="262" spans="1:10" hidden="1">
+    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
@@ -6918,7 +6918,7 @@
       <c r="I262" s="6"/>
       <c r="J262" s="7"/>
     </row>
-    <row r="263" spans="1:10" hidden="1">
+    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
@@ -6930,7 +6930,7 @@
       <c r="I263" s="6"/>
       <c r="J263" s="7"/>
     </row>
-    <row r="264" spans="1:10" hidden="1">
+    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -6942,7 +6942,7 @@
       <c r="I264" s="6"/>
       <c r="J264" s="7"/>
     </row>
-    <row r="265" spans="1:10" hidden="1">
+    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -6954,7 +6954,7 @@
       <c r="I265" s="6"/>
       <c r="J265" s="7"/>
     </row>
-    <row r="266" spans="1:10" hidden="1">
+    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -6966,7 +6966,7 @@
       <c r="I266" s="6"/>
       <c r="J266" s="7"/>
     </row>
-    <row r="267" spans="1:10" hidden="1">
+    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
@@ -6978,7 +6978,7 @@
       <c r="I267" s="6"/>
       <c r="J267" s="7"/>
     </row>
-    <row r="268" spans="1:10" hidden="1">
+    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -6990,7 +6990,7 @@
       <c r="I268" s="6"/>
       <c r="J268" s="7"/>
     </row>
-    <row r="269" spans="1:10" hidden="1">
+    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
@@ -7002,7 +7002,7 @@
       <c r="I269" s="6"/>
       <c r="J269" s="7"/>
     </row>
-    <row r="270" spans="1:10" hidden="1">
+    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -7014,7 +7014,7 @@
       <c r="I270" s="6"/>
       <c r="J270" s="7"/>
     </row>
-    <row r="271" spans="1:10" hidden="1">
+    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
@@ -7026,7 +7026,7 @@
       <c r="I271" s="6"/>
       <c r="J271" s="7"/>
     </row>
-    <row r="272" spans="1:10" hidden="1">
+    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
@@ -7038,7 +7038,7 @@
       <c r="I272" s="6"/>
       <c r="J272" s="7"/>
     </row>
-    <row r="273" spans="1:10" hidden="1">
+    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
@@ -7050,7 +7050,7 @@
       <c r="I273" s="6"/>
       <c r="J273" s="7"/>
     </row>
-    <row r="274" spans="1:10" hidden="1">
+    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="4"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
@@ -7062,7 +7062,7 @@
       <c r="I274" s="6"/>
       <c r="J274" s="7"/>
     </row>
-    <row r="275" spans="1:10" hidden="1">
+    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="4"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
@@ -7074,7 +7074,7 @@
       <c r="I275" s="6"/>
       <c r="J275" s="7"/>
     </row>
-    <row r="276" spans="1:10" hidden="1">
+    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -7086,7 +7086,7 @@
       <c r="I276" s="6"/>
       <c r="J276" s="7"/>
     </row>
-    <row r="277" spans="1:10" hidden="1">
+    <row r="277" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -7098,7 +7098,7 @@
       <c r="I277" s="6"/>
       <c r="J277" s="7"/>
     </row>
-    <row r="278" spans="1:10" hidden="1">
+    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
@@ -7110,7 +7110,7 @@
       <c r="I278" s="6"/>
       <c r="J278" s="7"/>
     </row>
-    <row r="279" spans="1:10" hidden="1">
+    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -7122,7 +7122,7 @@
       <c r="I279" s="6"/>
       <c r="J279" s="7"/>
     </row>
-    <row r="280" spans="1:10" hidden="1">
+    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
@@ -7134,7 +7134,7 @@
       <c r="I280" s="6"/>
       <c r="J280" s="7"/>
     </row>
-    <row r="281" spans="1:10" hidden="1">
+    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="4"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
@@ -7146,7 +7146,7 @@
       <c r="I281" s="6"/>
       <c r="J281" s="7"/>
     </row>
-    <row r="282" spans="1:10" hidden="1">
+    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
@@ -7158,7 +7158,7 @@
       <c r="I282" s="6"/>
       <c r="J282" s="7"/>
     </row>
-    <row r="283" spans="1:10" hidden="1">
+    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
@@ -7170,7 +7170,7 @@
       <c r="I283" s="6"/>
       <c r="J283" s="7"/>
     </row>
-    <row r="284" spans="1:10" hidden="1">
+    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
@@ -7182,7 +7182,7 @@
       <c r="I284" s="6"/>
       <c r="J284" s="7"/>
     </row>
-    <row r="285" spans="1:10" hidden="1">
+    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -7194,7 +7194,7 @@
       <c r="I285" s="6"/>
       <c r="J285" s="7"/>
     </row>
-    <row r="286" spans="1:10" hidden="1">
+    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -7206,7 +7206,7 @@
       <c r="I286" s="6"/>
       <c r="J286" s="7"/>
     </row>
-    <row r="287" spans="1:10" hidden="1">
+    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="4"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -7218,7 +7218,7 @@
       <c r="I287" s="6"/>
       <c r="J287" s="7"/>
     </row>
-    <row r="288" spans="1:10" hidden="1">
+    <row r="288" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
@@ -7230,7 +7230,7 @@
       <c r="I288" s="6"/>
       <c r="J288" s="7"/>
     </row>
-    <row r="289" spans="1:10" hidden="1">
+    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
@@ -7242,7 +7242,7 @@
       <c r="I289" s="6"/>
       <c r="J289" s="7"/>
     </row>
-    <row r="290" spans="1:10" hidden="1">
+    <row r="290" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
@@ -7254,7 +7254,7 @@
       <c r="I290" s="6"/>
       <c r="J290" s="7"/>
     </row>
-    <row r="291" spans="1:10" hidden="1">
+    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -7266,7 +7266,7 @@
       <c r="I291" s="6"/>
       <c r="J291" s="7"/>
     </row>
-    <row r="292" spans="1:10" hidden="1">
+    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="4"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
@@ -7278,7 +7278,7 @@
       <c r="I292" s="6"/>
       <c r="J292" s="7"/>
     </row>
-    <row r="293" spans="1:10" hidden="1">
+    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="4"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
@@ -7290,7 +7290,7 @@
       <c r="I293" s="6"/>
       <c r="J293" s="7"/>
     </row>
-    <row r="294" spans="1:10" hidden="1">
+    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
@@ -7302,7 +7302,7 @@
       <c r="I294" s="6"/>
       <c r="J294" s="7"/>
     </row>
-    <row r="295" spans="1:10" hidden="1">
+    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
@@ -7314,7 +7314,7 @@
       <c r="I295" s="6"/>
       <c r="J295" s="7"/>
     </row>
-    <row r="296" spans="1:10" hidden="1">
+    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
@@ -7326,7 +7326,7 @@
       <c r="I296" s="6"/>
       <c r="J296" s="7"/>
     </row>
-    <row r="297" spans="1:10" hidden="1">
+    <row r="297" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="8"/>
       <c r="B297" s="9"/>
       <c r="C297" s="9"/>
